--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307FE41F-5A1D-4DD2-9516-FACA64DB491B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80DA159B-58C3-4970-8FCC-FE18E2D70E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2358,6 +2358,9 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
     <t>ENG_01</t>
   </si>
   <si>
@@ -2401,9 +2404,6 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
-  </si>
-  <si>
-    <t>CNY</t>
   </si>
 </sst>
 </file>
@@ -4119,7 +4119,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4138,7 +4138,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4150,7 +4150,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4187,20 +4187,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>17.54</v>
+        <v>17.420000000000002</v>
       </c>
       <c r="D12" s="50">
         <v>25.72</v>
@@ -4218,23 +4218,23 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C13" s="48" t="s">
         <v>404</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>833675.39287936001</v>
+        <v>827971.79840128007</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.06</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4303,7 +4303,7 @@
         <v>355</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="D22" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E22" s="341">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.94339622641509424</v>
+        <v>0.92345791624048323</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4319,7 +4319,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>15.581396137654423</v>
+        <v>12.269404640272114</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.34266014643955889</v>
+        <v>0.23519139462656269</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
-        <v>165037.69629926985</v>
+        <v>122178.06382484984</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>694.67059819582528</v>
+        <v>801.81967938187529</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-2112.3294018041747</v>
+        <v>-2005.1803206181248</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-40731.341724366423</v>
+        <v>-30043.220876057931</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>215752.16223548091</v>
+        <v>141358.4276163358</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>121970.88571139777</v>
+        <v>89906.523166472296</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.15508330935322556</v>
+        <v>0.11758679413733134</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.9817559863169893E-2</v>
+        <v>8.0367393800229614E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>34.002015575694706</v>
+        <v>25.604524423403902</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0492386765783071</v>
+        <v>2.0934836341847864</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C95" s="338">
         <f>BS!C50</f>
-        <v>0.55676370950656873</v>
+        <v>0.75207444874659302</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>107884.62678694498</v>
+        <v>100741.35470787497</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.4060133622821915</v>
+        <v>2.2952145283504821</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11403318424891661</v>
+        <v>0.11649526612375691</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>34.472823445647499</v>
+        <v>25.922750583693354</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-0.44428159991714977</v>
+        <v>-0.45387405041027407</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>42.19 HKD</v>
+        <v>31.73 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>37.85 HKD</v>
+        <v>28.46 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>36.67 HKD</v>
+        <v>27.58 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>34.47 HKD</v>
+        <v>25.92 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>34.47 HKD</v>
+        <v>25.92 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>36.651351001723732</v>
+        <v>27.563246332906676</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>13.356906341736057</v>
+        <v>10.044914844353748</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5274,16 +5274,16 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>15.581396137654423</v>
+        <v>12.269404640272114</v>
       </c>
       <c r="D139" s="342">
         <f>IF($D$11="","",C139*$E$22)</f>
-        <v>14.699430318541907</v>
+        <v>11.330278842617002</v>
       </c>
     </row>
     <row r="140" spans="2:6">
       <c r="B140" s="290" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C140" s="340" t="str">
         <f>Market_currency</f>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5748752580246872</v>
+        <v>0.55486358565739202</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>21.210272570441976</v>
+        <v>15.950952738950622</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5343,16 +5343,16 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>24.159346644516049</v>
+        <v>18.900026813024695</v>
       </c>
       <c r="D147" s="342">
         <f>IF($D$11="","",C147*$E$22)</f>
-        <v>22.791836457090611</v>
+        <v>17.453379377645046</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="B148" s="290" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C148" s="340" t="str">
         <f>Market_currency</f>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3408333940165037</v>
+        <v>0.31430330866140765</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>29.095024102115186</v>
+        <v>21.880593606242279</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5412,16 +5412,16 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>32.702959884262221</v>
+        <v>25.48852938838931</v>
       </c>
       <c r="D155" s="342">
         <f>IF($D$11="","",C155*$E$22)</f>
-        <v>30.851848947417185</v>
+        <v>23.53758423703631</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="B156" s="290" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C156" s="340" t="str">
         <f>Market_currency</f>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.10772839225696806</v>
+        <v>7.5271138945648852E-2</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -5733,7 +5733,7 @@
         <v>132757</v>
       </c>
       <c r="G5" s="181">
-        <v>104581.49190000001</v>
+        <v>104581.49189999999</v>
       </c>
       <c r="H5" s="181">
         <v>138539.2739</v>
@@ -5769,7 +5769,7 @@
         <v>7912</v>
       </c>
       <c r="G6" s="181">
-        <v>7881.8547999999992</v>
+        <v>7881.8548000000001</v>
       </c>
       <c r="H6" s="181">
         <v>7386.8598000000002</v>
@@ -6309,7 +6309,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="G37" s="183">
         <f t="shared" si="2"/>
-        <v>-104581.49190000001</v>
+        <v>-104581.49189999999</v>
       </c>
       <c r="H37" s="183">
         <f t="shared" si="2"/>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="G38" s="184">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
-        <v>50791.179499999984</v>
+        <v>50791.179499999998</v>
       </c>
       <c r="H38" s="184">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="G39" s="183">
         <f t="shared" si="13"/>
-        <v>-7881.8547999999992</v>
+        <v>-7881.8548000000001</v>
       </c>
       <c r="H39" s="183">
         <f t="shared" si="13"/>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="G43" s="186">
         <f t="shared" si="17"/>
-        <v>41588.249299999981</v>
+        <v>41588.249299999996</v>
       </c>
       <c r="H43" s="186">
         <f t="shared" si="17"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="G44" s="187">
         <f t="shared" si="18"/>
-        <v>-4600.1271999999808</v>
+        <v>-4600.1271999999954</v>
       </c>
       <c r="H44" s="187">
         <f t="shared" si="18"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="G58" s="188">
         <f t="shared" si="28"/>
-        <v>-3967.7236999999809</v>
+        <v>-3967.7236999999955</v>
       </c>
       <c r="H58" s="188">
         <f t="shared" si="28"/>
@@ -7519,32 +7519,32 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
-        <v>0</v>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
+        <v>-74606</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
-        <v>0</v>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
+        <v>-68947</v>
       </c>
       <c r="E62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-62852</v>
       </c>
       <c r="F62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-55963</v>
       </c>
       <c r="G62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-51078.741900000001</v>
       </c>
       <c r="H62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-56363.515599999999</v>
       </c>
       <c r="I62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-50838.249000000003</v>
       </c>
       <c r="J62" s="183">
         <f t="shared" si="30"/>
@@ -7783,11 +7783,11 @@
       </c>
       <c r="F69" s="92">
         <f t="shared" si="35"/>
-        <v>1.2317654584099595</v>
+        <v>1.2317654584099587</v>
       </c>
       <c r="G69" s="92">
         <f t="shared" si="35"/>
-        <v>-0.46343160157258034</v>
+        <v>-0.46343160157258023</v>
       </c>
       <c r="H69" s="92">
         <f t="shared" si="35"/>
@@ -7833,11 +7833,11 @@
       </c>
       <c r="F70" s="101">
         <f t="shared" si="36"/>
-        <v>1.4991674751742927</v>
+        <v>1.4991674751742918</v>
       </c>
       <c r="G70" s="101">
         <f t="shared" si="36"/>
-        <v>-0.51802695682898614</v>
+        <v>-0.51802695682898592</v>
       </c>
       <c r="H70" s="101">
         <f t="shared" si="36"/>
@@ -7882,11 +7882,11 @@
       </c>
       <c r="F71" s="101">
         <f t="shared" si="37"/>
-        <v>0.36017977937654111</v>
+        <v>0.36017977937653689</v>
       </c>
       <c r="G71" s="101">
         <f t="shared" si="37"/>
-        <v>-4.3703644574709006</v>
+        <v>-4.3703644574709113</v>
       </c>
       <c r="H71" s="101">
         <f t="shared" si="37"/>
@@ -9021,11 +9021,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>16.671610502016176</v>
+        <v>17.031565986130452</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.44428159991714977</v>
+        <v>-0.45387405041027407</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
-        <v>0.55676370950656873</v>
+        <v>0.75207444874659302</v>
       </c>
       <c r="D50" s="95">
         <f>G31/Normalized_FCF!G8</f>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.19529424273821622</v>
+        <v>0.14457710564880843</v>
       </c>
       <c r="D54" s="92">
         <f>Normalized_FCF!G8/G35</f>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>107884.62678694498</v>
+        <v>100741.35470787497</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-23155.68660652751</v>
+        <v>-26727.322646062512</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.6590985886176517</v>
+        <v>5.769227319995565</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9316,7 +9316,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>46311.37321305502</v>
+        <v>53454.645292125024</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9431,11 +9431,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-97400.22</v>
+        <v>-99503.180799059992</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.0492386765783071</v>
+        <v>-2.0934836341847864</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9448,11 +9448,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>114357.70439416169</v>
+        <v>109091.44091590667</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.4060133622821915</v>
+        <v>2.2952145283504821</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9465,11 +9465,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>5419.9920000000002</v>
+        <v>5537.0146382159992</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11403318424891661</v>
+        <v>0.11649526612375691</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>22377.476394161684</v>
+        <v>15125.274755062677</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>0.47080786995280111</v>
+        <v>0.31822616028945261</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C5" s="191">
         <f>C25</f>
-        <v>-203289.30370073015</v>
+        <v>-245261.93617515016</v>
       </c>
       <c r="E5" s="302"/>
       <c r="G5" s="183">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="K5" s="183">
         <f t="shared" si="1"/>
-        <v>-107629.52360000001</v>
+        <v>-107629.5236</v>
       </c>
       <c r="L5" s="183">
         <f t="shared" si="1"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="C6" s="184">
         <f>C4+C5</f>
-        <v>173074.69629926985</v>
+        <v>131102.06382484984</v>
       </c>
       <c r="E6" s="302"/>
       <c r="G6" s="184">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="K6" s="184">
         <f t="shared" si="2"/>
-        <v>47743.147799999977</v>
+        <v>47743.147799999992</v>
       </c>
       <c r="L6" s="184">
         <f t="shared" si="2"/>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="C7" s="191">
         <f>C35</f>
-        <v>-8037</v>
+        <v>-8924</v>
       </c>
       <c r="E7" s="302"/>
       <c r="G7" s="191">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="C8" s="192">
         <f>C6+C7</f>
-        <v>165037.69629926985</v>
+        <v>122178.06382484984</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="308"/>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="K8" s="184">
         <f t="shared" si="4"/>
-        <v>41588.249299999981</v>
+        <v>41588.249299999996</v>
       </c>
       <c r="L8" s="184">
         <f t="shared" si="4"/>
@@ -9959,31 +9959,31 @@
       <c r="E10" s="302"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
-        <v>0</v>
+        <v>-74606</v>
       </c>
       <c r="H10" s="191">
         <f>Data!D62</f>
-        <v>0</v>
+        <v>-68947</v>
       </c>
       <c r="I10" s="191">
         <f>Data!E62</f>
-        <v>0</v>
+        <v>-62852</v>
       </c>
       <c r="J10" s="191">
         <f>Data!F62</f>
-        <v>0</v>
+        <v>-55963</v>
       </c>
       <c r="K10" s="191">
         <f>Data!G62</f>
-        <v>0</v>
+        <v>-51078.741900000001</v>
       </c>
       <c r="L10" s="191">
         <f>Data!H62</f>
-        <v>0</v>
+        <v>-56363.515599999999</v>
       </c>
       <c r="M10" s="191">
         <f>Data!I62</f>
-        <v>0</v>
+        <v>-50838.249000000003</v>
       </c>
       <c r="N10" s="191">
         <f>Data!J62</f>
@@ -10066,36 +10066,36 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-2112.3294018041747</v>
+        <v>-2005.1803206181248</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-1430.8377645190662</v>
+        <v>-1218.572383664188</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-979.86173254345545</v>
+        <v>-757.26567077835534</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-2233.9839673214356</v>
+        <v>-2095.9327156960453</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-2796.2427852946457</v>
+        <v>-2734.1197220632203</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>-3111.5736108670917</v>
+        <v>-3043.3370267115056</v>
       </c>
       <c r="L12" s="191">
         <f t="shared" si="6"/>
-        <v>-2749.5129872564653</v>
+        <v>-2700.0915842234122</v>
       </c>
       <c r="M12" s="191">
         <f t="shared" si="6"/>
-        <v>-2362.3088695752767</v>
+        <v>-2325.3405279380472</v>
       </c>
       <c r="N12" s="191">
         <f t="shared" si="6"/>
@@ -10121,36 +10121,36 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>162925.36689746569</v>
+        <v>120172.88350423172</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>267792.16223548091</v>
+        <v>193398.4276163358</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>241264.13826745655</v>
+        <v>172539.73432922165</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>256520.01603267857</v>
+        <v>193806.06728430395</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>157448.75721470534</v>
+        <v>101547.88027793678</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>88923.014089132892</v>
+        <v>37912.508773288486</v>
       </c>
       <c r="L13" s="184">
         <f t="shared" si="7"/>
-        <v>140904.2098127435</v>
+        <v>84590.115615776551</v>
       </c>
       <c r="M13" s="184">
         <f t="shared" si="7"/>
-        <v>124121.7042304247</v>
+        <v>73320.423572061918</v>
       </c>
       <c r="N13" s="184">
         <f t="shared" si="7"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-40731.341724366423</v>
+        <v>-30043.220876057931</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10288,38 +10288,38 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>121970.88571139777</v>
+        <v>89906.523166472296</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>215752.16223548091</v>
+        <v>141358.4276163358</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>192133.13826745655</v>
+        <v>123408.73432922165</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>203427.01603267857</v>
+        <v>140713.06728430395</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>131934.75721470534</v>
+        <v>76033.880277936783</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>78971.557889132891</v>
+        <v>27961.052573288485</v>
       </c>
       <c r="L16" s="184">
         <f t="shared" si="8"/>
-        <v>116300.3311127435</v>
+        <v>59986.23691577655</v>
       </c>
       <c r="M16" s="184">
         <f t="shared" si="8"/>
-        <v>101638.9275304247</v>
+        <v>50837.646872061916</v>
       </c>
       <c r="N16" s="184">
         <f t="shared" si="8"/>
@@ -10396,38 +10396,38 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>121970.88571139777</v>
+        <v>89906.523166472296</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>215752.16223548091</v>
+        <v>141358.4276163358</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>192133.13826745655</v>
+        <v>123408.73432922165</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>203427.01603267857</v>
+        <v>140713.06728430395</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>131934.75721470534</v>
+        <v>76033.880277936783</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>78971.557889132891</v>
+        <v>27961.052573288485</v>
       </c>
       <c r="L19" s="186">
         <f t="shared" si="9"/>
-        <v>116300.3311127435</v>
+        <v>59986.23691577655</v>
       </c>
       <c r="M19" s="186">
         <f t="shared" si="9"/>
-        <v>101638.9275304247</v>
+        <v>50837.646872061916</v>
       </c>
       <c r="N19" s="186">
         <f t="shared" si="9"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="C23" s="197">
         <f>-C4*C28</f>
-        <v>-199930.71094910003</v>
+        <v>-239590.97053351856</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="301"/>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="K23" s="183">
         <f>Data!G37</f>
-        <v>-104581.49190000001</v>
+        <v>-104581.49189999999</v>
       </c>
       <c r="L23" s="183">
         <f>Data!H37</f>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C24" s="191">
         <f>-C4*C29</f>
-        <v>-3358.5927516301235</v>
+        <v>-5670.965641631592</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="299"/>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="C25" s="184">
         <f>C23+C24</f>
-        <v>-203289.30370073015</v>
+        <v>-245261.93617515016</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="307"/>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="K25" s="184">
         <f t="shared" si="10"/>
-        <v>-107629.52360000001</v>
+        <v>-107629.5236</v>
       </c>
       <c r="L25" s="184">
         <f t="shared" si="10"/>
@@ -10697,8 +10697,8 @@
         <v>43</v>
       </c>
       <c r="C28" s="63">
-        <f>AVERAGE(G28:J28)</f>
-        <v>0.53121635158809033</v>
+        <f>AVERAGE(G28:P28)</f>
+        <v>0.6365937510854347</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="K28" s="13">
         <f t="shared" si="11"/>
-        <v>0.67310094470062654</v>
+        <v>0.67310094470062642</v>
       </c>
       <c r="L28" s="13">
         <f t="shared" si="11"/>
@@ -10757,8 +10757,8 @@
         <v>Selling Expenses</v>
       </c>
       <c r="C29" s="63">
-        <f>AVERAGE(G29:J29)</f>
-        <v>8.9237885441490784E-3</v>
+        <f>AVERAGE(G29:P29)</f>
+        <v>1.5067768547553942E-2</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
-        <v>0.54014014013223943</v>
+        <v>0.65166151963298868</v>
       </c>
       <c r="E30" s="302"/>
       <c r="G30" s="30">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K30" s="30">
         <f t="shared" si="13"/>
-        <v>0.69271849824164133</v>
+        <v>0.69271849824164122</v>
       </c>
       <c r="L30" s="30">
         <f t="shared" si="13"/>
@@ -10882,8 +10882,8 @@
         <v>175</v>
       </c>
       <c r="C33" s="198">
-        <f>AVERAGE(G33:J33)</f>
-        <v>-6449.75</v>
+        <f>G33</f>
+        <v>-7213</v>
       </c>
       <c r="E33" s="300" t="s">
         <v>341</v>
@@ -10939,8 +10939,8 @@
         <v>49</v>
       </c>
       <c r="C34" s="198">
-        <f>AVERAGE(G34:J34)</f>
-        <v>-1587.25</v>
+        <f>G34</f>
+        <v>-1711</v>
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="C35" s="184">
         <f>C33+C34</f>
-        <v>-8037</v>
+        <v>-8924</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="301"/>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>1.71370003507243E-2</v>
+        <v>1.9164957328543644E-2</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="299"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="C39" s="23">
         <f>ABS(C34/$C$4)</f>
-        <v>4.2173268431624708E-3</v>
+        <v>4.546130873303504E-3</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="299"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
-        <v>2.1354327193886771E-2</v>
+        <v>2.3711088201847148E-2</v>
       </c>
       <c r="E40" s="302"/>
       <c r="G40" s="30">
@@ -11257,31 +11257,31 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.26913935966398467</v>
+        <v>0.26884396445634917</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.28368623394920972</v>
+        <v>0.28332024614530149</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27414438939180003</v>
+        <v>0.27394911183103049</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.25140473599681634</v>
+        <v>0.2512509363087454</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.26295805479534612</v>
+        <v>0.26248477143805804</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.29102924016788195</v>
+        <v>0.29085920761421963</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30679198503001187</v>
+        <v>0.30663729974095316</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
@@ -11395,36 +11395,36 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>694.67059819582528</v>
+        <v>801.81967938187529</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>1376.1622354809338</v>
+        <v>1588.427616335812</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>1443.1382674565446</v>
+        <v>1665.7343292216447</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>895.01603267856456</v>
+        <v>1033.0672843039545</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>402.75721470535404</v>
+        <v>464.88027793677952</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>442.39248913290834</v>
+        <v>510.62907328849445</v>
       </c>
       <c r="L48" s="328">
         <f t="shared" si="19"/>
-        <v>320.40961274353464</v>
+        <v>369.83101577658761</v>
       </c>
       <c r="M48" s="328">
         <f t="shared" si="19"/>
-        <v>239.67373042472289</v>
+        <v>276.64207206195277</v>
       </c>
       <c r="N48" s="328">
         <f t="shared" si="19"/>
@@ -11507,36 +11507,36 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-2112.3294018041747</v>
+        <v>-2005.1803206181248</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-1430.8377645190662</v>
+        <v>-1218.572383664188</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-979.86173254345545</v>
+        <v>-757.26567077835534</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-2233.9839673214356</v>
+        <v>-2095.9327156960453</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-2796.2427852946457</v>
+        <v>-2734.1197220632203</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>-3111.5736108670917</v>
+        <v>-3043.3370267115056</v>
       </c>
       <c r="L50" s="184">
         <f t="shared" si="20"/>
-        <v>-2749.5129872564653</v>
+        <v>-2700.0915842234122</v>
       </c>
       <c r="M50" s="184">
         <f t="shared" si="20"/>
-        <v>-2362.3088695752767</v>
+        <v>-2325.3405279380472</v>
       </c>
       <c r="N50" s="184">
         <f t="shared" si="20"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>58.795046775657234</v>
+        <v>43.526207276398232</v>
       </c>
       <c r="E55" s="302"/>
       <c r="G55" s="42">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="K55" s="42">
         <f t="shared" si="21"/>
-        <v>11.70192627892539</v>
+        <v>11.701926278925393</v>
       </c>
       <c r="L55" s="42">
         <f t="shared" si="21"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="K62" s="191">
         <f>Data!G58</f>
-        <v>-3967.7236999999809</v>
+        <v>-3967.7236999999955</v>
       </c>
       <c r="L62" s="191">
         <f>Data!H58</f>
@@ -11995,7 +11995,7 @@
       </c>
       <c r="K63" s="184">
         <f t="shared" si="23"/>
-        <v>-4600.1271999999808</v>
+        <v>-4600.1271999999954</v>
       </c>
       <c r="L63" s="184">
         <f t="shared" si="23"/>
@@ -12148,7 +12148,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
-        <v>0.54014014013223943</v>
+        <v>0.65166151963298868</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="299"/>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="K73" s="6">
         <f t="shared" si="24"/>
-        <v>0.69271849824164133</v>
+        <v>0.69271849824164122</v>
       </c>
       <c r="L73" s="6">
         <f t="shared" si="24"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
-        <v>0.45985985986776062</v>
+        <v>0.34833848036701132</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="299"/>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="K74" s="65">
         <f t="shared" si="25"/>
-        <v>0.30728150175835867</v>
+        <v>0.30728150175835872</v>
       </c>
       <c r="L74" s="65">
         <f t="shared" si="25"/>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
-        <v>2.1354327193886771E-2</v>
+        <v>2.3711088201847148E-2</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="299"/>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
-        <v>0.43850553267387382</v>
+        <v>0.32462739216516417</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="299"/>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="K76" s="65">
         <f t="shared" si="27"/>
-        <v>0.26766772383627807</v>
+        <v>0.26766772383627818</v>
       </c>
       <c r="L76" s="65">
         <f t="shared" si="27"/>
@@ -12480,36 +12480,36 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>0</v>
+        <v>0.17741958497619534</v>
       </c>
       <c r="H78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>0.16549570460551741</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>0.14885725789261778</v>
       </c>
       <c r="J78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>0.22738926744436452</v>
       </c>
       <c r="K78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>0.3287498466734865</v>
       </c>
       <c r="L78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>0.24169753243094907</v>
       </c>
       <c r="M78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>0.22325853517222191</v>
       </c>
       <c r="N78" s="6">
         <f t="shared" si="29"/>
@@ -12592,38 +12592,38 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>5.6124640024130222E-3</v>
+        <v>5.3277686511412486E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>3.4026571904302583E-3</v>
+        <v>2.8978715729720576E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3519936740287787E-3</v>
+        <v>1.8176891780502949E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>5.2909171951813832E-3</v>
+        <v>4.9639597273903923E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1361713963596287E-2</v>
+        <v>1.110929508255714E-2</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>2.0026518066722846E-2</v>
+        <v>1.9587337974492119E-2</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1790437436921255E-2</v>
+        <v>1.1578509010612014E-2</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>1.0374189281100607E-2</v>
+        <v>1.0211841089256428E-2</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
@@ -12649,38 +12649,38 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.43289306867146082</v>
+        <v>0.31929962351402291</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.63683315395138451</v>
+        <v>0.4599183545926474</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.57911408123073804</v>
+        <v>0.41415268112119913</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.60753621493659515</v>
+        <v>0.45900591451176836</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.63974693213511524</v>
+        <v>0.41261008357178991</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.57232081606040341</v>
+        <v>0.24401014947914765</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.60422419464680843</v>
+        <v>0.36273859064216862</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.54508623752097352</v>
+        <v>0.32199005054059576</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>0.10822326716786521</v>
+        <v>7.9824905878505728E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12821,38 +12821,38 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>0.32407691944871925</v>
+        <v>0.2388818355806408</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.51307748815826859</v>
+        <v>0.33616268879953154</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>0.46118335961886697</v>
+        <v>0.29622195950932806</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.48179195233090633</v>
+        <v>0.33326165190607948</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.53607826230727329</v>
+        <v>0.30894141374394801</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>0.50827186774580291</v>
+        <v>0.17996120116454717</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.49871805815555692</v>
+        <v>0.25723245415091706</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.44635207787975223</v>
+        <v>0.22325589089937445</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
@@ -12928,38 +12928,38 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>0.32407691944871925</v>
+        <v>0.2388818355806408</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.51307748815826859</v>
+        <v>0.33616268879953154</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>0.46118335961886697</v>
+        <v>0.29622195950932806</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.48179195233090633</v>
+        <v>0.33326165190607948</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.53607826230727329</v>
+        <v>0.30894141374394801</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>0.50827186774580291</v>
+        <v>0.17996120116454717</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.49871805815555692</v>
+        <v>0.25723245415091706</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.44635207787975223</v>
+        <v>0.22325589089937445</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
@@ -13108,20 +13108,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.54555589384706649</v>
+        <v>0.74012355537751062</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.30841839492191675</v>
+        <v>0.47073200161933748</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.30922537889999818</v>
+        <v>0.48142818093817752</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.33878702357669604</v>
+        <v>0.48977990890891204</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
@@ -13163,20 +13163,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.9817559863169893E-2</v>
+        <v>8.0367393800229614E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.9817559863169893E-2</v>
+        <v>8.0367393800229614E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1265678449258837E-2</v>
+        <v>7.175660160734787E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>8.2668187001140259E-2</v>
+        <v>8.3237657864523529E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13300,38 +13300,38 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.39159770197382193</v>
+        <v>-0.37862533328021186</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>0.10995427732660534</v>
+        <v>0.12089211431909264</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-5.9472465350534409E-2</v>
+        <v>-0.10972996487197495</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.62922858567168283</v>
+        <v>0.90851908236642953</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.7706187630671737</v>
+        <v>1.6784795721427708</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.36891158747273556</v>
+        <v>-0.55180923329749443</v>
       </c>
       <c r="L97" s="6">
         <f t="shared" si="41"/>
-        <v>0.13521008019002911</v>
+        <v>0.15370467728733694</v>
       </c>
       <c r="M97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.62927940387314463</v>
+        <v>-0.78101016817777769</v>
       </c>
       <c r="N97" s="6">
         <f t="shared" si="41"/>
@@ -13911,31 +13911,31 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.0238182445602113</v>
+        <v>1.5626305677332901</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.0916544740347178</v>
+        <v>1.6995798647481588</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.0105540749168564</v>
+        <v>1.4609446298590569</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.1209555625992085</v>
+        <v>1.9450934170318153</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.0426290705268</v>
+        <v>2.9447404307897362</v>
       </c>
       <c r="L114" s="334">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.0620642677298928</v>
+        <v>2.059112762372902</v>
       </c>
       <c r="M114" s="334">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.2239118733593766</v>
+        <v>2.4469482333251551</v>
       </c>
       <c r="N114" s="334">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -14019,36 +14019,36 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.43289306867146082</v>
+        <v>0.31929962351402291</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.63683315395138451</v>
+        <v>0.4599183545926474</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.57911408123073804</v>
+        <v>0.41415268112119913</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.60753621493659515</v>
+        <v>0.45900591451176836</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.63974693213511524</v>
+        <v>0.41261008357178991</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>0.57232081606040341</v>
+        <v>0.24401014947914765</v>
       </c>
       <c r="L117" s="23">
         <f t="shared" si="45"/>
-        <v>0.60422419464680843</v>
+        <v>0.36273859064216862</v>
       </c>
       <c r="M117" s="23">
         <f t="shared" si="45"/>
-        <v>0.54508623752097352</v>
+        <v>0.32199005054059576</v>
       </c>
       <c r="N117" s="23">
         <f t="shared" si="45"/>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="C120" s="102">
         <f>C8/C105</f>
-        <v>0.22021586406213453</v>
+        <v>0.16302668116403515</v>
       </c>
       <c r="D120" s="103"/>
       <c r="E120" s="305"/>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="K120" s="102">
         <f t="shared" si="48"/>
-        <v>9.5840772518307402E-2</v>
+        <v>9.5840772518307429E-2</v>
       </c>
       <c r="L120" s="102">
         <f t="shared" si="48"/>
@@ -14305,50 +14305,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.720161246055576</v>
+        <v>2.0483619538723117</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>4.8116455582220024</v>
+        <v>3.2206030751781407</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>4.2849005625392014</v>
+        <v>2.8116508933111728</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>4.536773527431305</v>
+        <v>3.2058996754234332</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>2.9423727760112208</v>
+        <v>1.7322981924039971</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7612020283179761</v>
+        <v>0.63704338978048969</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>2.5936980923862722</v>
+        <v>1.3666808717175387</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>2.2667234901703832</v>
+        <v>1.158246343085823</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>6.6762000255001137</v>
+        <v>6.8203453563865333</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2797199446158851</v>
+        <v>6.4153049039989574</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>6.3249255427682263</v>
+        <v>6.4614865328092623</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14362,50 +14362,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.15508330935322556</v>
+        <v>0.11758679413733134</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.27432414813124301</v>
+        <v>0.1848796254407658</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.24429307654157364</v>
+        <v>0.16140361040821885</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.25865299472242331</v>
+        <v>0.18403557264198811</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.16775215370645502</v>
+        <v>9.9443065005969972E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10041060594743308</v>
+        <v>3.6569654981658414E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.14787332339716491</v>
+        <v>7.8454699868974659E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.12923166990709142</v>
+        <v>6.6489457123181564E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.38062713942417981</v>
+        <v>0.39152384365020276</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.35802280185951457</v>
+        <v>0.36827238254873462</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.36060008795713949</v>
+        <v>0.37092345194083015</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14419,43 +14419,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16551046267952782</v>
+        <v>0.16665060363943271</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14884690259528494</v>
+        <v>0.14987225439272661</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16994264339585932</v>
+        <v>0.17111331602545193</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4333783389207009E-2</v>
+        <v>8.4914727936090187E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9934513616634118E-2</v>
+        <v>3.0140721517552378E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.322449423529262E-2</v>
+        <v>7.3728910957923791E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3184498127105665E-2</v>
+        <v>6.3619752993652884E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4318189789934397E-2</v>
+        <v>8.4899026918223264E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0974866843122014E-2</v>
+        <v>7.1463786706564864E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.199385800544138E-2</v>
+        <v>5.2352024650714223E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15205,7 +15205,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>121970.88571139777</v>
+        <v>89906.523166472296</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1524636.0713924721</v>
+        <v>1123831.5395809037</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>107884.62678694498</v>
+        <v>100741.35470787497</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1545746.898179417</v>
+        <v>1137799.0942887787</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.06</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>34.472823445647499</v>
+        <v>25.922750583693354</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>36.650003108899789</v>
+        <v>27.562231329703277</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15419,11 +15419,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>124391.2173236755</v>
+        <v>91690.584985000663</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>115177.05307747731</v>
+        <v>84898.689800926528</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15441,11 +15441,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>126859.5768327683</v>
+        <v>93510.048868476399</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -15453,7 +15453,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>108761.63994578901</v>
+        <v>80169.794983261658</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15463,11 +15463,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>129376.9172811687</v>
+        <v>95365.617318454941</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15475,7 +15475,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>102703.56818159125</v>
+        <v>75704.301712180983</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15485,11 +15485,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>131944.21062308623</v>
+        <v>97258.006776594848</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>96982.933711631296</v>
+        <v>71487.538404276973</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15507,11 +15507,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>134562.44809972236</v>
+        <v>99187.947901278458</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>91580.941128397506</v>
+        <v>67505.650689869421</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15529,11 +15529,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>137232.64062199247</v>
+        <v>101156.18584972182</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>86479.841936944169</v>
+        <v>63745.555893837176</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15551,11 +15551,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>139955.81916084207</v>
+        <v>103163.48056568242</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>81662.876241395468</v>
+        <v>60194.900051887496</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15573,11 +15573,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>142733.03514530841</v>
+        <v>105210.6070728763</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>77114.217679537076</v>
+        <v>56842.017321038562</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15595,11 +15595,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>145565.36086848102</v>
+        <v>107298.35577421756</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>72818.921424575732</v>
+        <v>53675.89165095616</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15617,11 +15617,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>148453.88990151792</v>
+        <v>109427.53275699561</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>68762.875083223771</v>
+        <v>50686.120590213846</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1554890.2165459439</v>
+        <v>1146132.3123125082</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>720215.02299066575</v>
+        <v>530881.02354659536</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>1622259.8914012285</v>
+        <v>1195791.484645044</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16123,7 +16123,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>1622259.8914012285</v>
+        <v>1195791.484645044</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16153,19 +16153,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1524636.0713924719</v>
+        <v>1123831.5395809035</v>
       </c>
       <c r="C56" s="124">
-        <v>1524636.0713924719</v>
+        <v>1123831.5395809035</v>
       </c>
       <c r="D56" s="124">
-        <v>1573828.8121165438</v>
+        <v>1160092.2280044998</v>
       </c>
       <c r="E56" s="124">
-        <v>1598973.6761164423</v>
+        <v>1178626.8748961668</v>
       </c>
       <c r="F56" s="124">
-        <v>1624494.8539584514</v>
+        <v>1197438.9082228532</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16174,19 +16174,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>1524636.0713924717</v>
+        <v>1123831.5395809032</v>
       </c>
       <c r="C57" s="124">
-        <v>1524636.0713924717</v>
+        <v>1123831.5395809032</v>
       </c>
       <c r="D57" s="124">
-        <v>1623066.8515811446</v>
+        <v>1196386.3067920422</v>
       </c>
       <c r="E57" s="124">
-        <v>1675910.9333224401</v>
+        <v>1235338.4520648608</v>
       </c>
       <c r="F57" s="124">
-        <v>1731363.0610599834</v>
+        <v>1276213.0261731616</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16195,19 +16195,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>1524636.0713924714</v>
+        <v>1123831.539580903</v>
       </c>
       <c r="C58" s="124">
-        <v>1524636.0713924714</v>
+        <v>1123831.539580903</v>
       </c>
       <c r="D58" s="124">
-        <v>1684012.5778476135</v>
+        <v>1241310.2926966697</v>
       </c>
       <c r="E58" s="124">
-        <v>1773618.7866755913</v>
+        <v>1307360.3393357873</v>
       </c>
       <c r="F58" s="124">
-        <v>1870679.3215235178</v>
+        <v>1378905.0786722163</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16216,19 +16216,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>1524636.0713924714</v>
+        <v>1123831.5395809032</v>
       </c>
       <c r="C59" s="124">
-        <v>1524636.0713924714</v>
+        <v>1123831.5395809032</v>
       </c>
       <c r="D59" s="124">
-        <v>1746106.4991967347</v>
+        <v>1287080.6299842198</v>
       </c>
       <c r="E59" s="124">
-        <v>1875894.0312901761</v>
+        <v>1382748.9174843063</v>
       </c>
       <c r="F59" s="124">
-        <v>2020629.042536262</v>
+        <v>1489435.2104115037</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16237,19 +16237,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>1524636.0713924712</v>
+        <v>1123831.539580903</v>
       </c>
       <c r="C60" s="124">
-        <v>1524636.0713924712</v>
+        <v>1123831.539580903</v>
       </c>
       <c r="D60" s="124">
-        <v>1803857.2916437099</v>
+        <v>1329649.5834580972</v>
       </c>
       <c r="E60" s="124">
-        <v>1973728.207555155</v>
+        <v>1454863.9192204799</v>
       </c>
       <c r="F60" s="124">
-        <v>2168334.6189155849</v>
+        <v>1598311.1503303675</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16258,19 +16258,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>1524636.0713924712</v>
+        <v>1123831.539580903</v>
       </c>
       <c r="C61" s="124">
-        <v>1524636.0713924712</v>
+        <v>1123831.539580903</v>
       </c>
       <c r="D61" s="124">
-        <v>1854801.5241895404</v>
+        <v>1367201.3221116753</v>
       </c>
       <c r="E61" s="124">
-        <v>2062583.3984379612</v>
+        <v>1520360.3795517492</v>
       </c>
       <c r="F61" s="124">
-        <v>2306662.2001948259</v>
+        <v>1700274.4329474259</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16320,23 +16320,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>34.472823445647499</v>
+        <v>25.922750583693354</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>34.472823445647499</v>
+        <v>25.922750583693354</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>34.472823445647499</v>
+        <v>25.922750583693354</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>34.472823445647499</v>
+        <v>25.922750583693354</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>34.472823445647499</v>
+        <v>25.922750583693354</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16347,23 +16347,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>34.472823445647492</v>
+        <v>25.922750583693347</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647492</v>
+        <v>25.922750583693347</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>35.569906459552151</v>
+        <v>26.748886574410999</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>36.130680321207151</v>
+        <v>27.171165895023261</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>36.699846630975443</v>
+        <v>27.599764977539355</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16374,23 +16374,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647492</v>
+        <v>25.922750583693343</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647492</v>
+        <v>25.922750583693343</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>36.66799971354618</v>
+        <v>27.575783305826029</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>37.846513933539512</v>
+        <v>28.463239405655539</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>39.083192080158021</v>
+        <v>29.394494664288434</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16401,23 +16401,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647485</v>
+        <v>25.922750583693336</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647485</v>
+        <v>25.922750583693336</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>38.027194588092115</v>
+        <v>28.599297287931069</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>40.025567685394719</v>
+        <v>30.104131395869455</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>42.190185117455272</v>
+        <v>31.734152409863064</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16428,23 +16428,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647485</v>
+        <v>25.922750583693343</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647485</v>
+        <v>25.922750583693343</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>39.411996194511197</v>
+        <v>29.642093897273018</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>42.306482144684004</v>
+        <v>31.821727514562909</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>45.534322675993934</v>
+        <v>34.252387001051005</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16455,23 +16455,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647485</v>
+        <v>25.922750583693336</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647485</v>
+        <v>25.922750583693336</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>40.699938531135402</v>
+        <v>30.611952608754905</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>44.488353115478283</v>
+        <v>33.46474095404713</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>48.828411936311504</v>
+        <v>36.732933741902563</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16481,23 +16481,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647485</v>
+        <v>25.922750583693336</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>34.472823445647485</v>
+        <v>25.922750583693336</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>41.836082835351611</v>
+        <v>31.467502907561592</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>46.4699772165132</v>
+        <v>34.956962571909784</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>51.913355721558055</v>
+        <v>39.055987747872614</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>42.190185117455272</v>
+        <v>31.734152409863064</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>37.846513933539512</v>
+        <v>28.463239405655539</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>36.66799971354618</v>
+        <v>27.575783305826029</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>34.472823445647492</v>
+        <v>25.922750583693343</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16623,7 +16623,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>34.472823445647485</v>
+        <v>25.922750583693336</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-17.54</v>
+        <v>-17.420000000000002</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>38.051351001723731</v>
+        <v>28.963246332906674</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>215752.16223548091</v>
+        <v>141358.4276163358</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>121970.88571139777</v>
+        <v>89906.523166472296</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.17814472984231577</v>
+        <v>0.22962169479662209</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>17.54</v>
+        <v>17.420000000000002</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>34.472823445647499</v>
+        <v>25.922750583693354</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>36.66799971354618</v>
+        <v>27.575783305826029</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>34.472823445647492</v>
+        <v>25.922750583693343</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>37.846513933539512</v>
+        <v>28.463239405655539</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>36.464667303965108</v>
+        <v>27.422667981365397</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>34.472823445647485</v>
+        <v>25.922750583693336</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>42.190185117455272</v>
+        <v>31.734152409863064</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>36.651351001723732</v>
+        <v>27.563246332906676</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17376,7 +17376,7 @@
         <v>135</v>
       </c>
       <c r="C65" s="152">
-        <v>1.9843519198545507E-2</v>
+        <v>1.98435191985455E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>36.650003108899789</v>
+        <v>27.562231329703277</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>1.2845580233335976E-2</v>
+        <v>1.1545307705991617E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>13.356906341736057</v>
+        <v>10.044914844353748</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>15.581396137654423</v>
+        <v>12.269404640272114</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.5748752580246872</v>
+        <v>0.55486358565739202</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>17.54</v>
+        <v>17.420000000000002</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17575,7 +17575,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.34266014643955889</v>
+        <v>0.23519139462656269</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>21.210272570441976</v>
+        <v>15.950952738950622</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>24.159346644516049</v>
+        <v>18.900026813024695</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.3408333940165037</v>
+        <v>0.31430330866140765</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>29.095024102115186</v>
+        <v>21.880593606242279</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>32.702959884262221</v>
+        <v>25.48852938838931</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.10772839225696806</v>
+        <v>7.5271138945648852E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80DA159B-58C3-4970-8FCC-FE18E2D70E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6791163-6410-4998-8D0E-D2E88A453DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4273,13 +4273,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E22" s="341">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.92345791624048323</v>
+        <v>0.92351705994132738</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>12.269404640272114</v>
+        <v>12.26876134577943</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23519139462656269</v>
+        <v>0.23516781868501524</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4379,22 +4379,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4406,13 +4406,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4432,13 +4432,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4467,13 +4467,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4489,13 +4489,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4559,13 +4559,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4581,7 +4581,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4603,22 +4603,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11758679413733134</v>
+        <v>0.11757926366661527</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4679,22 +4679,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4752,22 +4752,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>25.604524423403902</v>
+        <v>25.602884663405479</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4804,13 +4804,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4823,13 +4823,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0934836341847864</v>
+        <v>2.0933495637109938</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.2952145283504821</v>
+        <v>2.2950675386658017</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11649526612375691</v>
+        <v>0.11648780555646665</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4960,13 +4960,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>25.922750583693354</v>
+        <v>25.921090443916754</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-0.45387405041027407</v>
+        <v>-0.45384498349616631</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5005,13 +5005,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>27.58 HKD</v>
+        <v>27.57 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>27.563246332906676</v>
+        <v>27.561481132818752</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5154,13 +5154,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5173,22 +5173,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>10.044914844353748</v>
+        <v>10.044271549861064</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5274,11 +5274,11 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>12.269404640272114</v>
+        <v>12.26876134577943</v>
       </c>
       <c r="D139" s="342">
         <f>IF($D$11="","",C139*$E$22)</f>
-        <v>11.330278842617002</v>
+        <v>11.330410407176021</v>
       </c>
     </row>
     <row r="140" spans="2:6">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55486358565739202</v>
+        <v>0.55485841683702408</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>15.950952738950622</v>
+        <v>15.949931211121964</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5343,11 +5343,11 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>18.900026813024695</v>
+        <v>18.899005285196036</v>
       </c>
       <c r="D147" s="342">
         <f>IF($D$11="","",C147*$E$22)</f>
-        <v>17.453379377645046</v>
+        <v>17.453553796799852</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31430330866140765</v>
+        <v>0.31429645619835356</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>21.880593606242279</v>
+        <v>21.879192333500633</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5412,11 +5412,11 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>25.48852938838931</v>
+        <v>25.487128115647664</v>
       </c>
       <c r="D155" s="342">
         <f>IF($D$11="","",C155*$E$22)</f>
-        <v>23.53758423703631</v>
+        <v>23.537797623710873</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>7.5271138945648852E-2</v>
+        <v>7.5262755552750749E-2</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -5452,13 +5452,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5495,13 +5495,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5509,22 +5509,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5548,6 +5548,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5564,17 +5575,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -9021,11 +9021,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.031565986130452</v>
+        <v>17.030475253877324</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45387405041027407</v>
+        <v>-0.45384498349616631</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9431,11 +9431,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-99503.180799059992</v>
+        <v>-99496.808435610001</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.0934836341847864</v>
+        <v>-2.0933495637109938</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9448,11 +9448,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>109091.44091590667</v>
+        <v>109084.45450295768</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.2952145283504821</v>
+        <v>2.2950675386658017</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9465,11 +9465,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>5537.0146382159992</v>
+        <v>5536.6600377959994</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11649526612375691</v>
+        <v>0.11648780555646665</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>15125.274755062677</v>
+        <v>15124.306105143682</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>0.31822616028945261</v>
+        <v>0.31820578051127457</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -14305,50 +14305,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0483619538723117</v>
+        <v>2.0482307730724378</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2206030751781407</v>
+        <v>3.2203968219392149</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.8116508933111728</v>
+        <v>2.8114708301087425</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>3.2058996754234332</v>
+        <v>3.2056943638167894</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7322981924039971</v>
+        <v>1.7321872528983739</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.63704338978048969</v>
+        <v>0.63700259237099488</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3666808717175387</v>
+        <v>1.3665933470056169</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>1.158246343085823</v>
+        <v>1.1581721668976499</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>6.8203453563865333</v>
+        <v>6.8199085691490158</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4153049039989574</v>
+        <v>6.4148940562837131</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4614865328092623</v>
+        <v>6.4610727275390829</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14362,50 +14362,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11758679413733134</v>
+        <v>0.11757926366661527</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1848796254407658</v>
+        <v>0.18486778541556914</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.16140361040821885</v>
+        <v>0.16139327382943411</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18403557264198811</v>
+        <v>0.18402378667145747</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.9443065005969972E-2</v>
+        <v>9.9436696492443966E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6569654981658414E-2</v>
+        <v>3.6567312994890633E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.8454699868974659E-2</v>
+        <v>7.8449675488267326E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.6489457123181564E-2</v>
+        <v>6.648519901823477E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.39152384365020276</v>
+        <v>0.39149876975597103</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.36827238254873462</v>
+        <v>0.36824879772007535</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.37092345194083015</v>
+        <v>0.37089969733289796</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>25.922750583693354</v>
+        <v>25.921090443916754</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>27.562231329703277</v>
+        <v>27.560466194617995</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16320,23 +16320,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>25.922750583693354</v>
+        <v>25.921090443916754</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>25.922750583693354</v>
+        <v>25.921090443916754</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>25.922750583693354</v>
+        <v>25.921090443916754</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>25.922750583693354</v>
+        <v>25.921090443916754</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>25.922750583693354</v>
+        <v>25.921090443916754</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16347,23 +16347,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>25.922750583693347</v>
+        <v>25.921090443916746</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693347</v>
+        <v>25.921090443916746</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>26.748886574410999</v>
+        <v>26.747173527393144</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>27.171165895023261</v>
+        <v>27.169425804474869</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>27.599764977539355</v>
+        <v>27.597997438731461</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16374,23 +16374,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693343</v>
+        <v>25.921090443916743</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693343</v>
+        <v>25.921090443916743</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>27.575783305826029</v>
+        <v>27.574017302847714</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>28.463239405655539</v>
+        <v>28.46141656838541</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>29.394494664288434</v>
+        <v>29.392612187749236</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16401,23 +16401,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693336</v>
+        <v>25.921090443916736</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693336</v>
+        <v>25.921090443916736</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>28.599297287931069</v>
+        <v>28.597465737268369</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>30.104131395869455</v>
+        <v>30.102203472912013</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>31.734152409863064</v>
+        <v>31.732120097415269</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16428,23 +16428,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693343</v>
+        <v>25.921090443916743</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693343</v>
+        <v>25.921090443916743</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>29.642093897273018</v>
+        <v>29.640195564031654</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>31.821727514562909</v>
+        <v>31.819689593647201</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>34.252387001051005</v>
+        <v>34.250193416310822</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16455,23 +16455,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693336</v>
+        <v>25.921090443916736</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693336</v>
+        <v>25.921090443916736</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>30.611952608754905</v>
+        <v>30.609992164009615</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>33.46474095404713</v>
+        <v>33.462597811582668</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>36.732933741902563</v>
+        <v>36.73058129846801</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16481,23 +16481,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693336</v>
+        <v>25.921090443916736</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>25.922750583693336</v>
+        <v>25.921090443916736</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>31.467502907561592</v>
+        <v>31.465487671829621</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>34.956962571909784</v>
+        <v>34.954723864877231</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>39.055987747872614</v>
+        <v>39.053486531862937</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.734152409863064</v>
+        <v>31.732120097415269</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.463239405655539</v>
+        <v>28.46141656838541</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>27.575783305826029</v>
+        <v>27.574017302847714</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>25.922750583693343</v>
+        <v>25.921090443916743</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16623,7 +16623,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>25.922750583693336</v>
+        <v>25.921090443916736</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16773,7 +16773,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>28.963246332906674</v>
+        <v>28.961481132818751</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>25.922750583693354</v>
+        <v>25.921090443916754</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>27.575783305826029</v>
+        <v>27.574017302847714</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>25.922750583693343</v>
+        <v>25.921090443916743</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>28.463239405655539</v>
+        <v>28.46141656838541</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>27.422667981365397</v>
+        <v>27.420911784169057</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>25.922750583693336</v>
+        <v>25.921090443916736</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>31.734152409863064</v>
+        <v>31.732120097415269</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>27.563246332906676</v>
+        <v>27.561481132818752</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17389,7 +17389,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>27.562231329703277</v>
+        <v>27.560466194617995</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>1.1545307705991617E-2</v>
+        <v>1.1545307705991605E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.044914844353748</v>
+        <v>10.044271549861064</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.269404640272114</v>
+        <v>12.26876134577943</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.55486358565739202</v>
+        <v>0.55485841683702408</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23519139462656269</v>
+        <v>0.23516781868501524</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>15.950952738950622</v>
+        <v>15.949931211121964</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>18.900026813024695</v>
+        <v>18.899005285196036</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31430330866140765</v>
+        <v>0.31429645619835356</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>21.880593606242279</v>
+        <v>21.879192333500633</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>25.48852938838931</v>
+        <v>25.487128115647664</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.5271138945648852E-2</v>
+        <v>7.5262755552750749E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6791163-6410-4998-8D0E-D2E88A453DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23600D2-3347-4051-AAE0-67C8CD540BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="444">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2380,6 +2380,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3785,29 +3797,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4097,7 +4109,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4119,7 +4131,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4162,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4197,10 +4209,10 @@
         <v>428</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4209,7 +4221,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>17.420000000000002</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="D12" s="50">
         <v>25.72</v>
@@ -4234,7 +4246,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>827971.79840128007</v>
+        <v>819416.40668415988</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4261,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4273,13 +4285,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4311,7 +4323,7 @@
       </c>
       <c r="E22" s="341">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.92351705994132738</v>
+        <v>0.92202497485361268</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4344,7 +4356,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>12.26876134577943</v>
+        <v>12.285015686177186</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4359,10 +4371,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23516781868501524</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.240328434530378</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4379,22 +4395,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4406,13 +4422,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4432,13 +4448,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4467,13 +4483,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4489,13 +4505,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4559,13 +4575,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4581,7 +4597,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4603,22 +4619,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4652,7 +4668,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11757926366661527</v>
+        <v>0.11899915097966768</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4661,7 +4677,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>8.0367393800229614E-2</v>
+        <v>8.1206496519721574E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4679,22 +4695,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4718,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4730,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4752,22 +4768,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4783,7 +4799,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>25.602884663405479</v>
+        <v>25.644317036118387</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4804,13 +4820,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4823,13 +4839,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4850,7 +4866,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0933495637109938</v>
+        <v>2.0967371679002214</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4921,7 +4937,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.2950675386658017</v>
+        <v>2.2987815769436528</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4952,7 +4968,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11648780555646665</v>
+        <v>0.11667631424366247</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4960,13 +4976,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4974,7 +4990,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>25.921090443916754</v>
+        <v>25.963037759405481</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4987,7 +5003,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-0.45384498349616631</v>
+        <v>-0.45457942708552379</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5005,13 +5021,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5045,7 +5061,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>31.73 HKD</v>
+        <v>31.78 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5067,7 +5083,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>28.46 HKD</v>
+        <v>28.51 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5089,7 +5105,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>27.57 HKD</v>
+        <v>27.62 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5111,7 +5127,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>25.92 HKD</v>
+        <v>25.96 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5133,7 +5149,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>25.92 HKD</v>
+        <v>25.96 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5146,7 +5162,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>27.561481132818752</v>
+        <v>27.606083042870196</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5154,13 +5170,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5173,22 +5189,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5265,7 +5281,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>10.044271549861064</v>
+        <v>10.06052589025882</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5274,11 +5290,11 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>12.26876134577943</v>
+        <v>12.285015686177186</v>
       </c>
       <c r="D139" s="342">
         <f>IF($D$11="","",C139*$E$22)</f>
-        <v>11.330410407176021</v>
+        <v>11.327091279123756</v>
       </c>
     </row>
     <row r="140" spans="2:6">
@@ -5300,7 +5316,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55485841683702408</v>
+        <v>0.55498881651919008</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5317,7 +5333,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5327,30 +5343,30 @@
         <v>2.9490740740740735</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>15.949931211121964</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>15.975742501660994</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>18.899005285196036</v>
+        <v>18.924816575735068</v>
       </c>
       <c r="D147" s="342">
         <f>IF($D$11="","",C147*$E$22)</f>
-        <v>17.453553796799852</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
+        <v>17.44915352735136</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>427</v>
       </c>
@@ -5363,21 +5379,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31429645619835356</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>0.31446933104032782</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5386,7 +5402,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5396,30 +5412,30 @@
         <v>3.6079357821470319</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>21.879192333500633</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>21.914598767710551</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>25.487128115647664</v>
+        <v>25.522534549857582</v>
       </c>
       <c r="D155" s="342">
         <f>IF($D$11="","",C155*$E$22)</f>
-        <v>23.537797623710873</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
+        <v>23.532414276532897</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>427</v>
       </c>
@@ -5432,133 +5448,191 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>7.5262755552750749E-2</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+        <v>7.5474252894806471E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>3.3776443763141084</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>19.78694693140692</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>23.164591307721029</v>
+      </c>
+      <c r="D163" s="342">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v>21.358331717995696</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>427</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.1608572528010731</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="345"/>
+      <c r="D169" s="345"/>
+      <c r="E169" s="345"/>
+      <c r="F169" s="345"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="346"/>
+      <c r="D178" s="346"/>
+      <c r="E178" s="346"/>
+      <c r="F178" s="346"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="343"/>
+      <c r="D181" s="343"/>
+      <c r="E181" s="343"/>
+      <c r="F181" s="343"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="343"/>
+      <c r="D182" s="343"/>
+      <c r="E182" s="343"/>
+      <c r="F182" s="343"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5575,6 +5649,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6309,7 +6394,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9021,11 +9106,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.030475253877324</v>
+        <v>17.058035156109948</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45384498349616631</v>
+        <v>-0.45457942708552379</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9431,11 +9516,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-99496.808435610001</v>
+        <v>-99657.821106840012</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.0933495637109938</v>
+        <v>-2.0967371679002214</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9448,11 +9533,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>109084.45450295768</v>
+        <v>109260.98257139877</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.2950675386658017</v>
+        <v>2.2987815769436528</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9465,11 +9550,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>5536.6600377959994</v>
+        <v>5545.6198470240006</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11648780555646665</v>
+        <v>0.11667631424366245</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9482,11 +9567,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>15124.306105143682</v>
+        <v>15148.781311582756</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>0.31820578051127457</v>
+        <v>0.31872072328709389</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12148,7 +12233,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12480,7 +12565,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13163,20 +13248,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.0367393800229614E-2</v>
+        <v>8.1206496519721574E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.0367393800229614E-2</v>
+        <v>8.1206496519721574E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.175660160734787E-2</v>
+        <v>7.2505800464037123E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>8.3237657864523529E-2</v>
+        <v>8.4106728538283063E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14305,50 +14390,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0482307730724378</v>
+        <v>2.0515453628894704</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2203968219392149</v>
+        <v>3.2256082925670055</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.8114708301087425</v>
+        <v>2.8160205481907457</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>3.2056943638167894</v>
+        <v>3.2108820419019533</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7321872528983739</v>
+        <v>1.7349903990599942</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.63700259237099488</v>
+        <v>0.63803343437076088</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3665933470056169</v>
+        <v>1.368804863623549</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1581721668976499</v>
+        <v>1.1600464018331065</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>6.8199085691490158</v>
+        <v>6.8309450206043794</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4148940562837131</v>
+        <v>6.4252750850212159</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4610727275390829</v>
+        <v>6.4715284858214774</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14362,50 +14447,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11757926366661527</v>
+        <v>0.11899915097966768</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18486778541556914</v>
+        <v>0.18710024898880545</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.16139327382943411</v>
+        <v>0.16334225917579734</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18402378667145747</v>
+        <v>0.1862460581149625</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.9436696492443966E-2</v>
+        <v>0.10063749414501127</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6567312994890633E-2</v>
+        <v>3.7008899905496571E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.8449675488267326E-2</v>
+        <v>7.9397033852874083E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.648519901823477E-2</v>
+        <v>6.7288074352268357E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.39149876975597103</v>
+        <v>0.39622650931579928</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.36824879772007535</v>
+        <v>0.37269577059287801</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.37089969733289796</v>
+        <v>0.37537868247224349</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14419,43 +14504,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16665060363943271</v>
+        <v>0.16839057513914837</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14987225439272661</v>
+        <v>0.15143704591190824</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17111331602545193</v>
+        <v>0.17289988197003323</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4914727936090187E-2</v>
+        <v>8.5801308622197855E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0140721517552378E-2</v>
+        <v>3.0455415825740285E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3728910957923791E-2</v>
+        <v>7.4498702371637623E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3619752993652884E-2</v>
+        <v>6.4283996354375497E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4899026918223264E-2</v>
+        <v>8.5785443672589876E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1463786706564864E-2</v>
+        <v>7.2209928331111381E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2352024650714223E-2</v>
+        <v>5.2898623515976906E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15317,7 +15402,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15331,7 +15416,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>25.921090443916754</v>
+        <v>25.963037759405481</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15384,7 +15469,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>27.560466194617995</v>
+        <v>27.605066462225693</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16320,23 +16405,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>25.921090443916754</v>
+        <v>25.963037759405481</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>25.921090443916754</v>
+        <v>25.963037759405481</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>25.921090443916754</v>
+        <v>25.963037759405481</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>25.921090443916754</v>
+        <v>25.963037759405481</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>25.921090443916754</v>
+        <v>25.963037759405481</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16347,23 +16432,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>25.921090443916746</v>
+        <v>25.963037759405474</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916746</v>
+        <v>25.963037759405474</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>26.747173527393144</v>
+        <v>26.79045766811295</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>27.169425804474869</v>
+        <v>27.213393263264216</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>27.597997438731461</v>
+        <v>27.642658442014646</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16374,23 +16459,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916743</v>
+        <v>25.96303775940547</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916743</v>
+        <v>25.96303775940547</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>27.574017302847714</v>
+        <v>27.618639499803383</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>28.46141656838541</v>
+        <v>28.507474816692255</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>29.392612187749236</v>
+        <v>29.440177361720021</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16401,23 +16486,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916736</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916736</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>28.597465737268369</v>
+        <v>28.643744149824148</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>30.102203472912013</v>
+        <v>30.150916956965322</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>31.732120097415269</v>
+        <v>31.78347122617015</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16428,23 +16513,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916743</v>
+        <v>25.96303775940547</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916743</v>
+        <v>25.96303775940547</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>29.640195564031654</v>
+        <v>29.688161394680719</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>31.819689593647201</v>
+        <v>31.871182433465265</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>34.250193416310822</v>
+        <v>34.305619466842622</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16455,23 +16540,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916736</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916736</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>30.609992164009615</v>
+        <v>30.659527387120281</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>33.462597811582668</v>
+        <v>33.516749320004429</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>36.73058129846801</v>
+        <v>36.790021285575989</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16481,23 +16566,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916736</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>25.921090443916736</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>31.465487671829621</v>
+        <v>31.516407317406749</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>34.954723864877231</v>
+        <v>35.011290035692987</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>39.053486531862937</v>
+        <v>39.116685606146916</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16532,7 +16617,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.732120097415269</v>
+        <v>31.78347122617015</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16554,7 +16639,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.46141656838541</v>
+        <v>28.507474816692255</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16577,7 +16662,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>27.574017302847714</v>
+        <v>27.618639499803383</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16600,7 +16685,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>25.921090443916743</v>
+        <v>25.96303775940547</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16623,7 +16708,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>25.921090443916736</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16691,7 +16776,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16724,7 +16809,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-17.420000000000002</v>
+        <v>-17.239999999999998</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16773,7 +16858,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>28.961481132818751</v>
+        <v>29.006083042870195</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16964,7 +17049,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>17.420000000000002</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16979,7 +17064,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>25.921090443916754</v>
+        <v>25.963037759405481</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -17026,7 +17111,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>27.574017302847714</v>
+        <v>27.618639499803383</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17084,7 +17169,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>25.921090443916743</v>
+        <v>25.96303775940547</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17142,7 +17227,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>28.46141656838541</v>
+        <v>28.507474816692255</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17169,7 +17254,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>27.420911784169057</v>
+        <v>27.465286215101575</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17243,7 +17328,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>25.921090443916736</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17301,7 +17386,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>31.732120097415269</v>
+        <v>31.78347122617015</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17327,7 +17412,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>27.561481132818752</v>
+        <v>27.606083042870196</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17389,7 +17474,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>27.560466194617995</v>
+        <v>27.605066462225693</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17452,7 +17537,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>1.1545307705991605E-2</v>
+        <v>1.1545307705991621E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17524,7 +17609,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.044271549861064</v>
+        <v>10.06052589025882</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17534,7 +17619,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.26876134577943</v>
+        <v>12.285015686177186</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17545,7 +17630,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.55485841683702408</v>
+        <v>0.55498881651919008</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17562,7 +17647,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>17.420000000000002</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17575,7 +17660,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23516781868501524</v>
+        <v>0.240328434530378</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17613,7 +17698,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>15.949931211121964</v>
+        <v>15.975742501660994</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17623,7 +17708,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>18.899005285196036</v>
+        <v>18.924816575735068</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17634,7 +17719,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31429645619835356</v>
+        <v>0.31446933104032782</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17673,7 +17758,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>21.879192333500633</v>
+        <v>21.914598767710551</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17685,7 +17770,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>25.487128115647664</v>
+        <v>25.522534549857582</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17695,39 +17780,95 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.5262755552750749E-2</v>
+        <v>7.5474252894806471E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>432</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>3.3776443763141084</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>19.78694693140692</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>23.164591307721029</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.1608572528010731</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23600D2-3347-4051-AAE0-67C8CD540BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDBB912-A795-4FD8-858D-86D44005FD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="454">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2385,13 +2362,61 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
   </si>
   <si>
     <t>Y</t>
@@ -3089,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3603,14 +3628,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3668,9 +3687,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3678,7 +3694,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3770,9 +3785,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3787,9 +3799,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3797,29 +3806,56 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4109,10 +4145,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4127,11 +4163,11 @@
         <v>45792</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>436</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4186,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4159,10 +4195,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>437</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4176,9 +4212,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4199,20 +4235,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4230,19 +4266,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4256,14 +4292,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>CNY/HKD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v>CNY</v>
       </c>
       <c r="E15" s="5"/>
@@ -4273,36 +4309,36 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0845693200000002</v>
+        <v>1.0845693199999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
       </c>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4310,286 +4346,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>424</v>
-      </c>
-      <c r="D22" s="32" t="str">
+        <v>419</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v>HKD/CNY:</v>
       </c>
-      <c r="E22" s="341">
+      <c r="E25" s="335">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.92202497485361268</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>425</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (HKD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>12.285015686177186</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+        <v>0.9220249748536129</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (HKD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>27.606083042870189</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.240328434530378</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>438</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0883.HK (HKD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v>600938.SS (CNY)</v>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>434</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>12.285015686177184</v>
+      </c>
+      <c r="D29" s="339">
+        <f>D144</f>
+        <v>11.327091279123758</v>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>429</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>18.924816575735061</v>
+      </c>
+      <c r="D30" s="148">
+        <f>D152</f>
+        <v>17.449153527351356</v>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>442</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>25.522534549857575</v>
+      </c>
+      <c r="D31" s="148">
+        <f>D160</f>
+        <v>23.532414276532897</v>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>23.164591307721022</v>
+      </c>
+      <c r="D32" s="148">
+        <f>D168</f>
+        <v>21.358331717995696</v>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>443</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>122178.06382484984</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>74606</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-74606</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>801.81967938187529</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>801.81967938187529</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-2807</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>-2005.1803206181248</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-223.13946170149947</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-30043.220876057931</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4597,1080 +4685,1109 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-223.13946170149947</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>141358.4276163358</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-30043.220876057931</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>89906.523166472296</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>141358.4276163358</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>89906.523166472296</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.11899915097966768</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>8.1206496519721574E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>25.644317036118387</v>
-      </c>
-      <c r="D82" s="1" t="str">
+        <v>25.64431703611838</v>
+      </c>
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>91887</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>2.0967371679002214</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>0.40943456145688223</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>0.12260820136742831</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>0.75207444874659302</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>154196</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>100741.35470787497</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.2987815769436528</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>5113.2</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11667631424366247</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>100741.35470787497</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.2987815769436524</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>25.963037759405481</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>5113.2</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>-0.45457942708552379</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.11667631424366245</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>25.963037759405474</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>-0.45457942708552368</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.04</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>31.78 HKD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.03</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>28.51 HKD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.02</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>27.62 HKD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>25.96 HKD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>25.96 HKD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>27.606083042870196</v>
-      </c>
-      <c r="D122" s="236" t="str">
+        <v>27.606083042870189</v>
+      </c>
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>1.4</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>0883.HK</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v>600938.SS</v>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>2.2244897959183665</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>10.06052589025882</v>
-      </c>
-    </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+        <v>10.060525890258818</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>12.285015686177186</v>
-      </c>
-      <c r="D139" s="342">
-        <f>IF($D$11="","",C139*$E$22)</f>
-        <v>11.327091279123756</v>
-      </c>
-    </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>427</v>
-      </c>
-      <c r="C140" s="340" t="str">
+        <v>12.285015686177184</v>
+      </c>
+      <c r="D144" s="336">
+        <f>IF($D$11="","",C144*$E$25)</f>
+        <v>11.327091279123758</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>421</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55498881651919008</v>
-      </c>
-    </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+        <v>0.55498881651918996</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>2.9490740740740735</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>15.975742501660994</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+        <v>15.975742501660989</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>18.924816575735068</v>
-      </c>
-      <c r="D147" s="342">
-        <f>IF($D$11="","",C147*$E$22)</f>
-        <v>17.44915352735136</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>427</v>
-      </c>
-      <c r="C148" s="340" t="str">
+        <v>18.924816575735061</v>
+      </c>
+      <c r="D152" s="336">
+        <f>IF($D$11="","",C152*$E$25)</f>
+        <v>17.449153527351356</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>421</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31446933104032782</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+        <v>0.31446933104032793</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>3.6079357821470319</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>21.914598767710551</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+        <v>21.914598767710544</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>25.522534549857582</v>
-      </c>
-      <c r="D155" s="342">
-        <f>IF($D$11="","",C155*$E$22)</f>
+        <v>25.522534549857575</v>
+      </c>
+      <c r="D160" s="336">
+        <f>IF($D$11="","",C160*$E$25)</f>
         <v>23.532414276532897</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>427</v>
-      </c>
-      <c r="C156" s="340" t="str">
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>421</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>7.5474252894806471E-2</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>3.3776443763141084</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>19.78694693140692</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+        <v>19.786946931406913</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>23.164591307721029</v>
-      </c>
-      <c r="D163" s="342">
-        <f>IF($D$11="","",C163*$E$22)</f>
+        <v>23.164591307721022</v>
+      </c>
+      <c r="D168" s="336">
+        <f>IF($D$11="","",C168*$E$25)</f>
         <v>21.358331717995696</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>427</v>
-      </c>
-      <c r="C164" s="340" t="str">
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>421</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.1608572528010731</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+        <v>0.16085725280107321</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="344" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="345"/>
-      <c r="D169" s="345"/>
-      <c r="E169" s="345"/>
-      <c r="F169" s="345"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="346" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="346"/>
-      <c r="D178" s="346"/>
-      <c r="E178" s="346"/>
-      <c r="F178" s="346"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="343" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="343"/>
-      <c r="D181" s="343"/>
-      <c r="E181" s="343"/>
-      <c r="F181" s="343"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="343" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="343"/>
-      <c r="D182" s="343"/>
-      <c r="E182" s="343"/>
-      <c r="F182" s="343"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5684,17 +5801,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -6257,7 +6374,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>220891</v>
@@ -6293,7 +6410,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-175426</v>
@@ -6329,7 +6446,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-97935</v>
@@ -6394,7 +6511,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7699,7 +7816,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8147,11 +8264,11 @@
         <f t="shared" si="40"/>
         <v>31381.7863</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8181,11 +8298,11 @@
         <f t="shared" si="40"/>
         <v>6313.6594999999998</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8317,15 +8434,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8382,7 +8499,7 @@
       <c r="C4" s="19">
         <v>33661</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8393,7 +8510,7 @@
         <f>72912+81284</f>
         <v>154196</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8405,7 +8522,7 @@
         <f>45771+4</f>
         <v>45775</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8415,7 +8532,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8426,7 +8543,7 @@
       <c r="C6" s="19">
         <v>5732</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8436,7 +8553,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8447,7 +8564,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8457,7 +8574,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8468,7 +8585,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8478,7 +8595,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8489,7 +8606,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8499,7 +8616,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8510,10 +8627,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8523,10 +8640,10 @@
         <f>12837+12408</f>
         <v>25245</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8584,7 +8701,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8593,7 +8710,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8604,7 +8721,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8613,7 +8730,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8624,7 +8741,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8634,7 +8751,7 @@
         <f>8504+18</f>
         <v>8522</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8645,7 +8762,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8655,7 +8772,7 @@
         <f>25047+23444</f>
         <v>48491</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8667,7 +8784,7 @@
         <f>632410+12755</f>
         <v>645165</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8676,7 +8793,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8687,7 +8804,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8696,7 +8813,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8707,7 +8824,7 @@
       <c r="C21" s="19">
         <v>16961</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8716,7 +8833,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8727,10 +8844,10 @@
       <c r="C22" s="19">
         <v>25465</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8739,10 +8856,10 @@
       <c r="C23" s="19">
         <v>47068</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9075,13 +9192,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9097,7 +9214,7 @@
         <f>H29</f>
         <v>-19921.400000000023</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9106,29 +9223,29 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.058035156109948</v>
+        <v>17.058035156109945</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45457942708552379</v>
-      </c>
-      <c r="F47" s="283"/>
+        <v>-0.45457942708552368</v>
+      </c>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9142,7 +9259,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.47663929536624461</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9153,22 +9270,22 @@
         <f>G29/G32</f>
         <v>0.70771698061406008</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9182,7 +9299,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.22812375750231934</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9196,22 +9313,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>8.692811385878442E-3</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9233,22 +9350,22 @@
         <f>G39/G32</f>
         <v>0.61078917447156578</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9262,7 +9379,7 @@
         <f>G28/G29</f>
         <v>2.5255903299854993E-3</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9281,13 +9398,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9315,7 +9432,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9325,7 +9442,7 @@
         <f>G18</f>
         <v>48491</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9335,7 +9452,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9345,26 +9462,26 @@
         <f>SUM(C66:C69)</f>
         <v>202687</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9375,65 +9492,65 @@
         <v>-26727.322646062512</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>6.2880051282963478</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>5.769227319995565</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>53454.645292125024</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9447,7 +9564,7 @@
         <f>G7*H7+G17*H17</f>
         <v>5113.2</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9461,7 +9578,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9475,7 +9592,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9489,11 +9606,11 @@
         <f>SUM(D79:D81)</f>
         <v>5113.2</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9504,76 +9621,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-99657.821106840012</v>
+        <v>-99657.821106839998</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-2.0967371679002214</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>109260.98257139877</v>
+        <v>109260.98257139875</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.2987815769436528</v>
-      </c>
-      <c r="E87" s="269" t="str">
+        <v>2.2987815769436524</v>
+      </c>
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>5545.6198470240006</v>
+        <v>5545.6198470239997</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11667631424366245</v>
-      </c>
-      <c r="E88" s="269" t="str">
+        <v>0.11667631424366243</v>
+      </c>
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>15148.781311582756</v>
-      </c>
-      <c r="D89" s="271">
+        <v>15148.781311582754</v>
+      </c>
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>0.31872072328709389</v>
-      </c>
-      <c r="E89" s="269" t="str">
+        <v>0.31872072328709344</v>
+      </c>
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9592,22 +9709,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9694,7 +9811,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9708,7 +9825,7 @@
         <v>376364</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9764,7 +9881,7 @@
         <f>C25</f>
         <v>-245261.93617515016</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-218801</v>
@@ -9819,7 +9936,7 @@
         <f>C4+C5</f>
         <v>131102.06382484984</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>201705</v>
@@ -9874,7 +9991,7 @@
         <f>C35</f>
         <v>-8924</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-8924</v>
@@ -9930,7 +10047,7 @@
         <v>122178.06382484984</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9986,7 +10103,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>74606</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>74606</v>
@@ -10041,7 +10158,7 @@
         <f>-C4*C78</f>
         <v>-74606</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-74606</v>
@@ -10097,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10153,7 +10270,7 @@
         <f>C50</f>
         <v>-2005.1803206181248</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-1218.572383664188</v>
@@ -10208,7 +10325,7 @@
         <f>SUM(C8:C12)</f>
         <v>120172.88350423172</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>193398.4276163358</v>
@@ -10263,7 +10380,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-30043.220876057931</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-51994</v>
@@ -10319,7 +10436,7 @@
         <v>-223.13946170149947</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10376,7 +10493,7 @@
         <v>89906.523166472296</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10433,8 +10550,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10458,8 +10575,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10484,7 +10601,7 @@
         <v>89906.523166472296</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10580,7 +10697,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10604,7 +10721,7 @@
         <v>-239590.97053351856</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10661,7 +10778,7 @@
         <v>-5670.965641631592</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10718,7 +10835,7 @@
         <v>-245261.93617515016</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10767,14 +10884,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10786,8 +10903,8 @@
         <v>0.6365937510854347</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10846,8 +10963,8 @@
         <v>1.5067768547553942E-2</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10904,7 +11021,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.65166151963298868</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.52032789068408059</v>
@@ -10952,14 +11069,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10970,8 +11087,8 @@
         <f>G33</f>
         <v>-7213</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11028,8 +11145,8 @@
         <v>-1711</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11087,7 +11204,7 @@
         <v>-8924</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11136,14 +11253,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11156,7 +11273,7 @@
         <v>1.9164957328543644E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11214,7 +11331,7 @@
         <v>4.546130873303504E-3</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11270,7 +11387,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>2.3711088201847148E-2</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>2.1222051528396742E-2</v>
@@ -11318,26 +11435,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11416,7 +11533,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11427,7 +11544,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-2807</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-2807</v>
@@ -11476,111 +11593,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>801.81967938187529</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>1588.427616335812</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>1665.7343292216447</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>1033.0672843039545</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>464.88027793677952</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>510.62907328849445</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>369.83101577658761</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>276.64207206195277</v>
       </c>
-      <c r="N48" s="328">
+      <c r="N48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="328">
+      <c r="O48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="328">
+      <c r="P48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>2312.94</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>4582</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>4805</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>2980</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>1341</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>1472.9675999999999</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>1066.8196</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>798.00549999999998</v>
       </c>
-      <c r="N49" s="324">
+      <c r="N49" s="320">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="324">
+      <c r="O49" s="320">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="324">
+      <c r="P49" s="320">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11594,7 +11711,7 @@
         <f>C47+C48</f>
         <v>-2005.1803206181248</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-1218.572383664188</v>
@@ -11642,14 +11759,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11662,8 +11779,8 @@
       <c r="C53" s="87">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11689,8 +11806,8 @@
         <f>G54</f>
         <v>3.0548390958459848E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11716,7 +11833,7 @@
         <f>-C8/C47</f>
         <v>43.526207276398232</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>68.678660491628079</v>
@@ -11764,14 +11881,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11785,7 +11902,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11840,7 +11957,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>1836</v>
@@ -11895,7 +12012,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11950,7 +12067,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>1836</v>
@@ -12001,11 +12118,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12061,7 +12178,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-4580</v>
@@ -12109,14 +12226,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12130,7 +12247,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12154,7 +12271,7 @@
       <c r="C67" s="177">
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>3.7862696170423378E-2</v>
@@ -12179,7 +12296,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12205,7 +12322,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12233,7 +12350,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12255,7 +12372,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12279,7 +12396,7 @@
         <v>0.65166151963298868</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12336,7 +12453,7 @@
         <v>0.34833848036701132</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12393,7 +12510,7 @@
         <v>2.3711088201847148E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12450,7 +12567,7 @@
         <v>0.32462739216516417</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12507,7 +12624,7 @@
         <v>0.19822831089052087</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12564,8 +12681,8 @@
         <v>0.19822831089052087</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>443</v>
+      <c r="E78" s="296" t="s">
+        <v>453</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12623,7 +12740,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12680,7 +12797,7 @@
         <v>5.3277686511412486E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12737,7 +12854,7 @@
         <v>0.31929962351402291</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12794,7 +12911,7 @@
         <v>7.9824905878505728E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12847,12 +12964,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>5.9288205487639486E-4</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12909,7 +13026,7 @@
         <v>0.2388818355806408</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12961,26 +13078,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12990,7 +13107,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -13016,7 +13133,7 @@
         <v>0.2388818355806408</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13065,14 +13182,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13084,7 +13201,7 @@
         <f>G90</f>
         <v>1.4</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>1.4</v>
@@ -13140,7 +13257,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>66541.935577600001</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>66541.935577600001</v>
@@ -13195,7 +13312,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.74012355537751062</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.47073200161933748</v>
@@ -13244,13 +13361,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>8.1206496519721574E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>8.1206496519721574E-2</v>
@@ -13298,7 +13415,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13307,7 +13424,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13331,7 +13448,7 @@
         <v>-0.10497353188777325</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13388,7 +13505,7 @@
         <v>-0.37862533328021186</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13466,7 +13583,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13481,7 +13598,7 @@
         <v>1056281</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13538,7 +13655,7 @@
         <v>33661</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13595,7 +13712,7 @@
         <v>5732</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13652,7 +13769,7 @@
         <v>306845</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13709,7 +13826,7 @@
         <v>749436</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13758,7 +13875,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13767,7 +13884,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13793,7 +13910,7 @@
         <v>8.9437353200624931E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13850,7 +13967,7 @@
         <v>1.5229936975906303E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13907,7 +14024,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13926,63 +14043,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.6008682291893146</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.6902490128132808</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.4510047502417471</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.1035316540316042</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>3.2993724703992493</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>2.023384343788782</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>2.361580198596569</v>
       </c>
-      <c r="N113" s="334">
+      <c r="N113" s="329">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.716234671522463</v>
       </c>
-      <c r="O113" s="334">
+      <c r="O113" s="329">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>3.6258745986141627</v>
       </c>
-      <c r="P113" s="334">
+      <c r="P113" s="329">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>3.8254510220089513</v>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13990,58 +14107,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.5626305677332901</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6995798647481588</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.4609446298590569</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.9450934170318153</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.9447404307897362</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.059112762372902</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>2.4469482333251551</v>
       </c>
-      <c r="N114" s="334">
+      <c r="N114" s="329">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.63781492393722561</v>
       </c>
-      <c r="O114" s="334">
+      <c r="O114" s="329">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>0.76192556289509195</v>
       </c>
-      <c r="P114" s="334">
+      <c r="P114" s="329">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.58467527247211815</v>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14050,7 +14167,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14106,7 +14223,7 @@
         <f>C81</f>
         <v>0.31929962351402291</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.4599183545926474</v>
@@ -14160,7 +14277,7 @@
         <f>C4/C101</f>
         <v>0.35631048934895165</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.39810050545262105</v>
@@ -14215,7 +14332,7 @@
         <v>1.4094345614568822</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14272,7 +14389,7 @@
         <v>0.16302668116403515</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14368,7 +14485,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14390,50 +14507,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0515453628894704</v>
+        <v>2.05154536288947</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2256082925670055</v>
+        <v>3.2256082925670051</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.8160205481907457</v>
+        <v>2.8160205481907452</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>3.2108820419019533</v>
+        <v>3.2108820419019528</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7349903990599942</v>
+        <v>1.734990399059994</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.63803343437076088</v>
+        <v>0.63803343437076077</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>1.368804863623549</v>
+        <v>1.3688048636235486</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1600464018331065</v>
+        <v>1.1600464018331063</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>6.8309450206043794</v>
+        <v>6.8309450206043776</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4252750850212159</v>
+        <v>6.4252750850212141</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4715284858214774</v>
+        <v>6.4715284858214766</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14450,31 +14567,31 @@
         <v>0.11899915097966768</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18710024898880545</v>
+        <v>0.18710024898880542</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.16334225917579734</v>
+        <v>0.16334225917579731</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.1862460581149625</v>
+        <v>0.18624605811496248</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10063749414501127</v>
+        <v>0.10063749414501126</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.7008899905496571E-2</v>
+        <v>3.7008899905496564E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.9397033852874083E-2</v>
+        <v>7.9397033852874055E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
@@ -14482,15 +14599,15 @@
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.39622650931579928</v>
+        <v>0.39622650931579922</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.37269577059287801</v>
+        <v>0.3726957705928779</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.37537868247224349</v>
+        <v>0.37537868247224343</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14499,7 +14616,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15250,13 +15367,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15300,7 +15417,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15310,7 +15427,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15328,10 +15445,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15346,8 +15463,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15362,8 +15479,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15378,8 +15495,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15402,7 +15519,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0845693200000002</v>
+        <v>1.0845693199999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15416,7 +15533,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>25.963037759405481</v>
+        <v>25.963037759405474</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15443,7 +15560,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15453,7 +15570,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15463,13 +15580,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>27.605066462225693</v>
+        <v>27.605066462225686</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16405,23 +16522,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>25.963037759405481</v>
+        <v>25.963037759405474</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>25.963037759405481</v>
+        <v>25.963037759405474</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>25.963037759405481</v>
+        <v>25.963037759405474</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>25.963037759405481</v>
+        <v>25.963037759405474</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>25.963037759405481</v>
+        <v>25.963037759405474</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16432,23 +16549,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>25.963037759405474</v>
+        <v>25.963037759405466</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405474</v>
+        <v>25.963037759405466</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>26.79045766811295</v>
+        <v>26.790457668112943</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>27.213393263264216</v>
+        <v>27.213393263264212</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>27.642658442014646</v>
+        <v>27.642658442014643</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16459,23 +16576,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>25.96303775940547</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>25.96303775940547</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>27.618639499803383</v>
+        <v>27.618639499803376</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>28.507474816692255</v>
+        <v>28.507474816692248</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>29.440177361720021</v>
+        <v>29.440177361720014</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16486,23 +16603,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.963037759405456</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.963037759405456</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>28.643744149824148</v>
+        <v>28.643744149824144</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>30.150916956965322</v>
+        <v>30.150916956965315</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>31.78347122617015</v>
+        <v>31.783471226170143</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16513,23 +16630,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>25.96303775940547</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>25.96303775940547</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>29.688161394680719</v>
+        <v>29.688161394680712</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>31.871182433465265</v>
+        <v>31.871182433465258</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>34.305619466842622</v>
+        <v>34.305619466842614</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16540,23 +16657,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.963037759405456</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.963037759405456</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>30.659527387120281</v>
+        <v>30.659527387120274</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>33.516749320004429</v>
+        <v>33.516749320004422</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>36.790021285575989</v>
+        <v>36.790021285575982</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16566,23 +16683,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.963037759405456</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.963037759405456</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>31.516407317406749</v>
+        <v>31.516407317406742</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>35.011290035692987</v>
+        <v>35.01129003569298</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>39.116685606146916</v>
+        <v>39.116685606146909</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16617,7 +16734,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.78347122617015</v>
+        <v>31.783471226170143</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16639,7 +16756,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.507474816692255</v>
+        <v>28.507474816692248</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16662,7 +16779,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>27.618639499803383</v>
+        <v>27.618639499803376</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16685,7 +16802,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>25.96303775940547</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16708,7 +16825,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>25.963037759405463</v>
+        <v>25.963037759405456</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16724,7 +16841,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16777,12 +16894,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16795,19 +16912,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-17.239999999999998</v>
       </c>
@@ -16824,19 +16941,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>1.4</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
@@ -16850,15 +16967,15 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>29.006083042870195</v>
+        <v>29.006083042870188</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16873,15 +16990,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国海油(0883.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16898,12 +17015,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16920,37 +17037,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16964,12 +17081,12 @@
         <v>0.19549305441006948</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16982,12 +17099,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22866289579809873</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17000,8 +17117,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22962169479662209</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17017,7 +17134,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -17027,25 +17144,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17055,23 +17172,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>25.963037759405481</v>
+        <v>25.963037759405474</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17091,8 +17208,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17102,8 +17219,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17111,14 +17228,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>27.618639499803383</v>
+        <v>27.618639499803376</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17128,8 +17245,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17149,8 +17266,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17160,8 +17277,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17169,14 +17286,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>25.96303775940547</v>
+        <v>25.963037759405463</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17186,8 +17303,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17207,8 +17324,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17218,8 +17335,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17227,14 +17344,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>28.507474816692255</v>
+        <v>28.507474816692248</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17245,8 +17362,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17254,7 +17371,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>27.465286215101575</v>
+        <v>27.465286215101568</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17308,8 +17425,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17319,8 +17436,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17328,14 +17445,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>25.963037759405463</v>
+        <v>25.963037759405456</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17345,12 +17462,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17366,8 +17483,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17377,8 +17494,8 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17386,14 +17503,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>31.78347122617015</v>
+        <v>31.783471226170143</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17403,8 +17520,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17412,23 +17529,23 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>27.606083042870196</v>
+        <v>27.606083042870189</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17437,10 +17554,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17452,8 +17569,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17464,8 +17581,8 @@
         <v>1.98435191985455E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17474,29 +17591,29 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>27.605066462225693</v>
+        <v>27.605066462225686</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17504,40 +17621,40 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
-        <v>1.1545307705991621E-2</v>
+        <v>1.1545307705991608E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17555,10 +17672,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17579,15 +17696,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17609,7 +17726,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.06052589025882</v>
+        <v>10.060525890258818</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17619,7 +17736,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.285015686177186</v>
+        <v>12.285015686177184</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17628,9 +17745,9 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
-        <v>0.55498881651919008</v>
+        <v>0.55498881651918996</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17638,14 +17755,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>17.239999999999998</v>
       </c>
@@ -17656,9 +17773,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.240328434530378</v>
       </c>
@@ -17668,15 +17785,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17698,7 +17815,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>15.975742501660994</v>
+        <v>15.975742501660989</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17708,7 +17825,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>18.924816575735068</v>
+        <v>18.924816575735061</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17717,28 +17834,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.31446933104032782</v>
+        <v>0.31446933104032793</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17750,7 +17867,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17758,27 +17875,27 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>21.914598767710551</v>
+        <v>21.914598767710544</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>25.522534549857582</v>
+        <v>25.522534549857575</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>7.5474252894806471E-2</v>
       </c>
@@ -17788,15 +17905,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17816,60 +17933,60 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>19.78694693140692</v>
+        <v>19.786946931406913</v>
       </c>
       <c r="D104" s="117"/>
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>23.164591307721029</v>
+        <v>23.164591307721022</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>0.1608572528010731</v>
+        <v>0.16085725280107321</v>
       </c>
     </row>
     <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDBB912-A795-4FD8-858D-86D44005FD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07980542-F9FD-4A43-984E-74E0B28BFDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3833,29 +3833,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4309,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0845693199999999</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4321,13 +4321,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="E25" s="335">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.9220249748536129</v>
+        <v>0.922701545375611</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="C26" s="341">
         <f>C127</f>
-        <v>27.606083042870189</v>
+        <v>27.585840894032092</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
-        <v>0.240328434530378</v>
+        <v>0.2400573713891494</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4438,11 +4438,11 @@
       </c>
       <c r="C29" s="339">
         <f>C144</f>
-        <v>12.285015686177184</v>
+        <v>12.277638809778461</v>
       </c>
       <c r="D29" s="339">
         <f>D144</f>
-        <v>11.327091279123758</v>
+        <v>11.328596303346163</v>
       </c>
       <c r="E29" s="343" t="s">
         <v>429</v>
@@ -4457,17 +4457,17 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>18.924816575735061</v>
+        <v>18.159816530624241</v>
       </c>
       <c r="D30" s="148">
         <f>D152</f>
-        <v>17.449153527351356</v>
+        <v>16.756090776544553</v>
       </c>
       <c r="E30" s="344" t="s">
         <v>442</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4476,11 +4476,11 @@
       </c>
       <c r="C31" s="148">
         <f>C160</f>
-        <v>25.522534549857575</v>
+        <v>25.506465679482364</v>
       </c>
       <c r="D31" s="148">
         <f>D160</f>
-        <v>23.532414276532897</v>
+        <v>23.53485529952836</v>
       </c>
       <c r="E31" s="344" t="s">
         <v>441</v>
@@ -4495,11 +4495,11 @@
       </c>
       <c r="C32" s="148">
         <f>C168</f>
-        <v>23.164591307721022</v>
+        <v>23.150082537164366</v>
       </c>
       <c r="D32" s="148">
         <f>D168</f>
-        <v>21.358331717995696</v>
+        <v>21.360616932614505</v>
       </c>
       <c r="E32" s="344" t="s">
         <v>443</v>
@@ -4523,22 +4523,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4576,13 +4576,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4611,13 +4611,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4633,13 +4633,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4703,13 +4703,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4725,7 +4725,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4747,22 +4747,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11899915097966768</v>
+        <v>0.1189118949020127</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4823,22 +4823,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4882,22 +4882,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>25.64431703611838</v>
+        <v>25.625513351383738</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4934,13 +4934,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4953,13 +4953,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0967371679002214</v>
+        <v>2.0951997362493384</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.2987815769436524</v>
+        <v>2.2970959963143938</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="C109" s="248">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11667631424366245</v>
+        <v>0.11659076138507206</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>25.963037759405474</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>-0.45457942708552368</v>
+        <v>-0.45424610691085376</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5135,13 +5135,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>31.78 HKD</v>
+        <v>31.76 HKD</v>
       </c>
       <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>28.51 HKD</v>
+        <v>28.49 HKD</v>
       </c>
       <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>27.62 HKD</v>
+        <v>27.6 HKD</v>
       </c>
       <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>25.96 HKD</v>
+        <v>25.94 HKD</v>
       </c>
       <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>25.96 HKD</v>
+        <v>25.94 HKD</v>
       </c>
       <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>27.606083042870189</v>
+        <v>27.585840894032092</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5284,13 +5284,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5303,22 +5303,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>10.060525890258818</v>
+        <v>10.053149013860095</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5404,11 +5404,11 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>12.285015686177184</v>
+        <v>12.277638809778461</v>
       </c>
       <c r="D144" s="336">
         <f>IF($D$11="","",C144*$E$25)</f>
-        <v>11.327091279123758</v>
+        <v>11.328596303346163</v>
       </c>
     </row>
     <row r="145" spans="2:4">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55498881651918996</v>
+        <v>0.55492968813451693</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>2.9490740740740735</v>
+        <v>2.870561153410911</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>15.975742501660989</v>
+        <v>15.289255377213328</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5473,11 +5473,11 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>18.924816575735061</v>
+        <v>18.159816530624241</v>
       </c>
       <c r="D152" s="336">
         <f>IF($D$11="","",C152*$E$25)</f>
-        <v>17.449153527351356</v>
+        <v>16.756090776544553</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31446933104032793</v>
+        <v>0.34169791668185379</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>21.914598767710544</v>
+        <v>21.898529897335333</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5542,11 +5542,11 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>25.522534549857575</v>
+        <v>25.506465679482364</v>
       </c>
       <c r="D160" s="336">
         <f>IF($D$11="","",C160*$E$25)</f>
-        <v>23.532414276532897</v>
+        <v>23.53485529952836</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>7.5474252894806471E-2</v>
+        <v>7.5378351616592565E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>19.786946931406913</v>
+        <v>19.772438160850257</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5611,11 +5611,11 @@
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>23.164591307721022</v>
+        <v>23.150082537164366</v>
       </c>
       <c r="D168" s="336">
         <f>IF($D$11="","",C168*$E$25)</f>
-        <v>21.358331717995696</v>
+        <v>21.360616932614505</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.16085725280107321</v>
+        <v>0.16076746951188714</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5651,13 +5651,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5694,13 +5694,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5708,22 +5708,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5747,17 +5747,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5774,6 +5763,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9223,11 +9223,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.058035156109945</v>
+        <v>17.045527358970478</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45457942708552368</v>
+        <v>-0.45424610691085376</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9633,11 +9633,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-99657.821106839998</v>
+        <v>-99584.747051219994</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.0967371679002214</v>
+        <v>-2.0951997362493384</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9650,11 +9650,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>109260.98257139875</v>
+        <v>109180.86700165375</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.2987815769436524</v>
+        <v>2.2970959963143933</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9667,11 +9667,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>5545.6198470239997</v>
+        <v>5541.5535235919988</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11667631424366243</v>
+        <v>0.11659076138507206</v>
       </c>
       <c r="E88" s="267" t="str">
         <f>Market_currency</f>
@@ -9684,11 +9684,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>15148.781311582754</v>
+        <v>15137.673474025756</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>0.31872072328709344</v>
+        <v>0.31848702145012697</v>
       </c>
       <c r="E89" s="267" t="str">
         <f>Market_currency</f>
@@ -14507,50 +14507,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.05154536288947</v>
+        <v>2.0500410681106986</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2256082925670051</v>
+        <v>3.2232431166363904</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.8160205481907452</v>
+        <v>2.8139557023022825</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>3.2108820419019528</v>
+        <v>3.2085276639884754</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.734990399059994</v>
+        <v>1.7337182180759729</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.63803343437076077</v>
+        <v>0.63756559662202394</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3688048636235486</v>
+        <v>1.3678011880301386</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1600464018331063</v>
+        <v>1.1591957982944392</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>6.8309450206043776</v>
+        <v>6.8259362330267557</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4252750850212141</v>
+        <v>6.4205637547540864</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4715284858214766</v>
+        <v>6.4667832402675689</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14564,50 +14564,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11899915097966768</v>
+        <v>0.1189118949020127</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18710024898880542</v>
+        <v>0.18696305780953543</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.16334225917579731</v>
+        <v>0.16322248853261501</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18624605811496248</v>
+        <v>0.18610949327079326</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10063749414501126</v>
+        <v>0.100563701744546</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.7008899905496564E-2</v>
+        <v>3.6981763145129E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.9397033852874055E-2</v>
+        <v>7.9338816011028934E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.7288074352268357E-2</v>
+        <v>6.7238735399909474E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.39622650931579922</v>
+        <v>0.39593597639366335</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.3726957705928779</v>
+        <v>0.37242249157506307</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.37537868247224343</v>
+        <v>0.37510343621041586</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0845693199999999</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>25.963037759405474</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>27.605066462225686</v>
+        <v>27.58482505879492</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16522,23 +16522,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>25.963037759405474</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>25.963037759405474</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>25.963037759405474</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>25.963037759405474</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>25.963037759405474</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16549,23 +16549,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>25.963037759405466</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405466</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>26.790457668112943</v>
+        <v>26.770813576239547</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>27.213393263264212</v>
+        <v>27.19343905404267</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>27.642658442014643</v>
+        <v>27.622389474280428</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16576,23 +16576,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>27.618639499803376</v>
+        <v>27.598388143948487</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>28.507474816692248</v>
+        <v>28.486571722713226</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>29.440177361720014</v>
+        <v>29.418590363990184</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16603,23 +16603,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405456</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405456</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>28.643744149824144</v>
+        <v>28.62274113641363</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>30.150916956965315</v>
+        <v>30.128808809724717</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>31.783471226170143</v>
+        <v>31.760166009194865</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16630,23 +16630,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405463</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>29.688161394680712</v>
+        <v>29.666392562762493</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>31.871182433465258</v>
+        <v>31.847812902283941</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>34.305619466842614</v>
+        <v>34.28046488572538</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16657,23 +16657,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405456</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405456</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>30.659527387120274</v>
+        <v>30.637046301494614</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>33.516749320004422</v>
+        <v>33.492173177592214</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>36.790021285575982</v>
+        <v>36.763045017864876</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16683,23 +16683,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405456</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>25.963037759405456</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>31.516407317406742</v>
+        <v>31.4932979249308</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>35.01129003569298</v>
+        <v>34.985618021926463</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>39.116685606146909</v>
+        <v>39.088003312796452</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.783471226170143</v>
+        <v>31.760166009194865</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.507474816692248</v>
+        <v>28.486571722713226</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16779,7 +16779,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>27.618639499803376</v>
+        <v>27.598388143948487</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>25.963037759405463</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>25.963037759405456</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>29.006083042870188</v>
+        <v>28.985840894032091</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -17181,7 +17181,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>25.963037759405474</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>27.618639499803376</v>
+        <v>27.598388143948487</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17286,7 +17286,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>25.963037759405463</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>28.507474816692248</v>
+        <v>28.486571722713226</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>27.465286215101568</v>
+        <v>27.445147305478507</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17445,7 +17445,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>25.963037759405456</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>31.783471226170143</v>
+        <v>31.760166009194865</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17529,7 +17529,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>27.606083042870189</v>
+        <v>27.585840894032092</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17591,7 +17591,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>27.605066462225686</v>
+        <v>27.58482505879492</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="F72" s="325">
         <f>BS!D89/C60</f>
-        <v>1.1545307705991608E-2</v>
+        <v>1.1545307705991601E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.060525890258818</v>
+        <v>10.053149013860095</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.285015686177184</v>
+        <v>12.277638809778461</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17747,7 +17747,7 @@
       </c>
       <c r="F83" s="325">
         <f>(1-C83/C60)</f>
-        <v>0.55498881651918996</v>
+        <v>0.55492968813451693</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.240328434530378</v>
+        <v>0.2400573713891494</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17803,7 +17803,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.9490740740740735</v>
+        <v>2.870561153410911</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>15.975742501660989</v>
+        <v>15.289255377213328</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>18.924816575735061</v>
+        <v>18.159816530624241</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.31446933104032793</v>
+        <v>0.34169791668185379</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17875,7 +17875,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>21.914598767710544</v>
+        <v>21.898529897335333</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>25.522534549857575</v>
+        <v>25.506465679482364</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17897,7 +17897,7 @@
       </c>
       <c r="F99" s="325">
         <f>(1-C99/C60)</f>
-        <v>7.5474252894806471E-2</v>
+        <v>7.5378351616592565E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>19.786946931406913</v>
+        <v>19.772438160850257</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -17943,7 +17943,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>23.164591307721022</v>
+        <v>23.150082537164366</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>0.16085725280107321</v>
+        <v>0.16076746951188714</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07980542-F9FD-4A43-984E-74E0B28BFDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61484DF-61EF-4FF7-8CB2-6BEA0BB43B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3114,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3748,7 +3748,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3812,9 +3811,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3833,29 +3829,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4163,7 +4169,7 @@
         <v>45792</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4197,7 +4203,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>447</v>
       </c>
     </row>
@@ -4309,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0837740599999999</v>
+        <v>1.0837740600000001</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4356,7 +4362,7 @@
       <c r="D22" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>444</v>
       </c>
     </row>
@@ -4387,9 +4393,9 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v>HKD/CNY:</v>
       </c>
-      <c r="E25" s="335">
+      <c r="E25" s="334">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.922701545375611</v>
+        <v>0.92270154537561078</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -4397,16 +4403,16 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
-        <v>27.585840894032092</v>
+        <v>27.585840894032099</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2400573713891494</v>
+        <v>0.24005737138914962</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4417,18 +4423,18 @@
       <c r="B28" s="45" t="s">
         <v>438</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>0883.HK (HKD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v>600938.SS (CNY)</v>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>434</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4436,18 +4442,18 @@
       <c r="B29" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
-        <v>12.277638809778461</v>
-      </c>
-      <c r="D29" s="339">
+        <v>12.277638809778463</v>
+      </c>
+      <c r="D29" s="345">
         <f>D144</f>
-        <v>11.328596303346163</v>
-      </c>
-      <c r="E29" s="343" t="s">
+        <v>11.328596303346162</v>
+      </c>
+      <c r="E29" s="341" t="s">
         <v>429</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4455,18 +4461,18 @@
       <c r="B30" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
         <v>18.159816530624241</v>
       </c>
-      <c r="D30" s="148">
+      <c r="D30" s="346">
         <f>D152</f>
-        <v>16.756090776544553</v>
-      </c>
-      <c r="E30" s="344" t="s">
+        <v>16.75609077654455</v>
+      </c>
+      <c r="E30" s="342" t="s">
         <v>442</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4474,18 +4480,18 @@
       <c r="B31" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
-        <v>25.506465679482364</v>
-      </c>
-      <c r="D31" s="148">
+        <v>25.506465679482371</v>
+      </c>
+      <c r="D31" s="346">
         <f>D160</f>
-        <v>23.53485529952836</v>
-      </c>
-      <c r="E31" s="344" t="s">
+        <v>23.534855299528363</v>
+      </c>
+      <c r="E31" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4493,18 +4499,18 @@
       <c r="B32" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
-        <v>23.150082537164366</v>
-      </c>
-      <c r="D32" s="148">
+        <v>23.150082537164369</v>
+      </c>
+      <c r="D32" s="346">
         <f>D168</f>
         <v>21.360616932614505</v>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>443</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4532,13 +4538,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4645,7 +4651,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>801.81967938187529</v>
       </c>
@@ -4653,14 +4659,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-2807</v>
       </c>
@@ -4668,8 +4674,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4728,10 +4734,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4796,7 +4802,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.1189118949020127</v>
+        <v>0.11891189490201272</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4832,13 +4838,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4876,7 +4882,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4913,7 +4919,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>25.625513351383738</v>
+        <v>25.625513351383745</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4988,28 +4994,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>0.40943456145688223</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>0.12260820136742831</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>0.75207444874659302</v>
       </c>
@@ -5082,7 +5088,7 @@
       </c>
       <c r="C109" s="248">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11659076138507206</v>
+        <v>0.11659076138507207</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5104,7 +5110,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>25.944000372833866</v>
+        <v>25.944000372833873</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5112,12 +5118,12 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>-0.45424610691085376</v>
+        <v>-0.45424610691085382</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5276,7 +5282,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>27.585840894032092</v>
+        <v>27.585840894032099</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5284,13 +5290,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5303,13 +5309,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5373,7 +5379,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5395,7 +5401,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>10.053149013860095</v>
+        <v>10.053149013860097</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5404,22 +5410,22 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>12.277638809778461</v>
-      </c>
-      <c r="D144" s="336">
+        <v>12.277638809778463</v>
+      </c>
+      <c r="D144" s="335">
         <f>IF($D$11="","",C144*$E$25)</f>
-        <v>11.328596303346163</v>
+        <v>11.328596303346162</v>
       </c>
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="286" t="s">
         <v>421</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5442,7 +5448,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5464,7 +5470,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>15.289255377213328</v>
+        <v>15.289255377213331</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5475,20 +5481,20 @@
         <f>Scenarios!C93</f>
         <v>18.159816530624241</v>
       </c>
-      <c r="D152" s="336">
+      <c r="D152" s="335">
         <f>IF($D$11="","",C152*$E$25)</f>
-        <v>16.756090776544553</v>
+        <v>16.75609077654455</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="286" t="s">
         <v>421</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5499,7 +5505,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34169791668185379</v>
+        <v>0.3416979166818539</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5533,7 +5539,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>21.898529897335333</v>
+        <v>21.89852989733534</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5542,22 +5548,22 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>25.506465679482364</v>
-      </c>
-      <c r="D160" s="336">
+        <v>25.506465679482371</v>
+      </c>
+      <c r="D160" s="335">
         <f>IF($D$11="","",C160*$E$25)</f>
-        <v>23.53485529952836</v>
+        <v>23.534855299528363</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="B161" s="286" t="s">
         <v>421</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5568,7 +5574,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>7.5378351616592565E-2</v>
+        <v>7.5378351616592454E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5602,7 +5608,7 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>19.772438160850257</v>
+        <v>19.77243816085026</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5611,9 +5617,9 @@
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>23.150082537164366</v>
-      </c>
-      <c r="D168" s="336">
+        <v>23.150082537164369</v>
+      </c>
+      <c r="D168" s="335">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v>21.360616932614505</v>
       </c>
@@ -5622,11 +5628,11 @@
       <c r="B169" s="286" t="s">
         <v>421</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5651,7 +5657,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5665,13 +5671,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5708,22 +5714,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5747,6 +5753,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5763,17 +5780,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8264,11 +8270,11 @@
         <f t="shared" si="40"/>
         <v>31381.7863</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8298,11 +8304,11 @@
         <f t="shared" si="40"/>
         <v>6313.6594999999998</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9223,11 +9229,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.045527358970478</v>
+        <v>17.045527358970482</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45424610691085376</v>
+        <v>-0.45424610691085382</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9529,7 +9535,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
@@ -9633,11 +9639,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-99584.747051219994</v>
+        <v>-99584.747051220009</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.0951997362493384</v>
+        <v>-2.0951997362493389</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9650,11 +9656,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>109180.86700165375</v>
+        <v>109180.86700165378</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.2970959963143933</v>
+        <v>2.2970959963143938</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9667,11 +9673,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>5541.5535235919988</v>
+        <v>5541.5535235920006</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11659076138507206</v>
+        <v>0.1165907613850721</v>
       </c>
       <c r="E88" s="267" t="str">
         <f>Market_currency</f>
@@ -9684,7 +9690,7 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>15137.673474025756</v>
+        <v>15137.673474025771</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
@@ -11600,104 +11606,104 @@
         <v>801.81967938187529</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>1588.427616335812</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>1665.7343292216447</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>1033.0672843039545</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>464.88027793677952</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>510.62907328849445</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>369.83101577658761</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>276.64207206195277</v>
       </c>
-      <c r="N48" s="324">
+      <c r="N48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="324">
+      <c r="O48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="324">
+      <c r="P48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>2312.94</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>4582</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>4805</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>2980</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>1341</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>1472.9675999999999</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>1066.8196</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>798.00549999999998</v>
       </c>
-      <c r="N49" s="320">
+      <c r="N49" s="319">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="320">
+      <c r="O49" s="319">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="320">
+      <c r="P49" s="319">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -14059,47 +14065,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.6008682291893146</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.6902490128132808</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.4510047502417471</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.1035316540316042</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>3.2993724703992493</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>2.023384343788782</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>2.361580198596569</v>
       </c>
-      <c r="N113" s="329">
+      <c r="N113" s="328">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.716234671522463</v>
       </c>
-      <c r="O113" s="329">
+      <c r="O113" s="328">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>3.6258745986141627</v>
       </c>
-      <c r="P113" s="329">
+      <c r="P113" s="328">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>3.8254510220089513</v>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14111,47 +14117,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.5626305677332901</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6995798647481588</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.4609446298590569</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.9450934170318153</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.9447404307897362</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.059112762372902</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>2.4469482333251551</v>
       </c>
-      <c r="N114" s="329">
+      <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.63781492393722561</v>
       </c>
-      <c r="O114" s="329">
+      <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>0.76192556289509195</v>
       </c>
-      <c r="P114" s="329">
+      <c r="P114" s="328">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.58467527247211815</v>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -14507,50 +14513,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0500410681106986</v>
+        <v>2.0500410681106991</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2232431166363904</v>
+        <v>3.2232431166363908</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.8139557023022825</v>
+        <v>2.8139557023022834</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>3.2085276639884754</v>
+        <v>3.2085276639884759</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7337182180759729</v>
+        <v>1.7337182180759734</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.63756559662202394</v>
+        <v>0.63756559662202417</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3678011880301386</v>
+        <v>1.3678011880301388</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1591957982944392</v>
+        <v>1.1591957982944394</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>6.8259362330267557</v>
+        <v>6.8259362330267566</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4205637547540864</v>
+        <v>6.4205637547540872</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4667832402675689</v>
+        <v>6.4667832402675698</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14564,42 +14570,42 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1189118949020127</v>
+        <v>0.11891189490201272</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18696305780953543</v>
+        <v>0.18696305780953545</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.16322248853261501</v>
+        <v>0.16322248853261506</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18610949327079326</v>
+        <v>0.18610949327079329</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.100563701744546</v>
+        <v>0.10056370174454603</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6981763145129E-2</v>
+        <v>3.6981763145129014E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.9338816011028934E-2</v>
+        <v>7.9338816011028948E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.7238735399909474E-2</v>
+        <v>6.7238735399909488E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.39593597639366335</v>
+        <v>0.3959359763936634</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
@@ -14607,7 +14613,7 @@
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.37510343621041586</v>
+        <v>0.37510343621041592</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15445,10 +15451,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15463,8 +15469,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15479,8 +15485,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15495,8 +15501,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15519,7 +15525,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0837740599999999</v>
+        <v>1.0837740600000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15533,7 +15539,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>25.944000372833866</v>
+        <v>25.944000372833873</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15586,7 +15592,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>27.58482505879492</v>
+        <v>27.584825058794923</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16522,23 +16528,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>25.944000372833873</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>25.944000372833873</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>25.944000372833873</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>25.944000372833873</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>25.944000372833873</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16549,23 +16555,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>25.944000372833859</v>
+        <v>25.944000372833862</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833859</v>
+        <v>25.944000372833862</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>26.770813576239547</v>
+        <v>26.770813576239554</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>27.19343905404267</v>
+        <v>27.193439054042674</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>27.622389474280428</v>
+        <v>27.622389474280432</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16576,23 +16582,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833855</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833855</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>27.598388143948487</v>
+        <v>27.598388143948494</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>28.486571722713226</v>
+        <v>28.486571722713233</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>29.418590363990184</v>
+        <v>29.418590363990191</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16603,23 +16609,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>25.944000372833852</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>25.944000372833852</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>28.62274113641363</v>
+        <v>28.622741136413637</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>30.128808809724717</v>
+        <v>30.12880880972472</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>31.760166009194865</v>
+        <v>31.760166009194872</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16630,23 +16636,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833855</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833855</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>29.666392562762493</v>
+        <v>29.6663925627625</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>31.847812902283941</v>
+        <v>31.847812902283948</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>34.28046488572538</v>
+        <v>34.280464885725387</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16657,23 +16663,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>25.944000372833852</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>25.944000372833852</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>30.637046301494614</v>
+        <v>30.637046301494621</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>33.492173177592214</v>
+        <v>33.492173177592221</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>36.763045017864876</v>
+        <v>36.763045017864883</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16683,23 +16689,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>25.944000372833852</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>25.944000372833852</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>31.4932979249308</v>
+        <v>31.493297924930808</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>34.985618021926463</v>
+        <v>34.98561802192647</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>39.088003312796452</v>
+        <v>39.088003312796459</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16734,7 +16740,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.760166009194865</v>
+        <v>31.760166009194872</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16756,7 +16762,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.486571722713226</v>
+        <v>28.486571722713233</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16779,7 +16785,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>27.598388143948487</v>
+        <v>27.598388143948494</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16802,7 +16808,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>25.944000372833855</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16825,7 +16831,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>25.944000372833848</v>
+        <v>25.944000372833852</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16975,7 +16981,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>28.985840894032091</v>
+        <v>28.985840894032098</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16990,11 +16996,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国海油(0883.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -17015,8 +17021,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -17037,8 +17043,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -17048,8 +17054,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -17062,8 +17068,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -17081,8 +17087,8 @@
         <v>0.19549305441006948</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -17099,8 +17105,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22866289579809873</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -17117,8 +17123,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22962169479662209</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17144,21 +17150,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17172,8 +17178,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17181,14 +17187,14 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>25.944000372833866</v>
+        <v>25.944000372833873</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17208,8 +17214,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17219,8 +17225,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17228,14 +17234,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>27.598388143948487</v>
+        <v>27.598388143948494</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17245,8 +17251,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17266,8 +17272,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17277,8 +17283,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17286,14 +17292,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>25.944000372833855</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17303,8 +17309,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17324,8 +17330,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17335,8 +17341,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17344,14 +17350,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>28.486571722713226</v>
+        <v>28.486571722713233</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17362,8 +17368,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17371,7 +17377,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>27.445147305478507</v>
+        <v>27.445147305478514</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17425,8 +17431,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17436,8 +17442,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17445,14 +17451,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>25.944000372833848</v>
+        <v>25.944000372833852</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17462,8 +17468,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17483,8 +17489,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17494,8 +17500,8 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17503,14 +17509,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>31.760166009194865</v>
+        <v>31.760166009194872</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17520,8 +17526,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17529,7 +17535,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>27.585840894032092</v>
+        <v>27.585840894032099</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17538,7 +17544,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17591,7 +17597,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>27.58482505879492</v>
+        <v>27.584825058794923</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17652,9 +17658,9 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
-        <v>1.1545307705991601E-2</v>
+        <v>1.15453077059916E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17726,7 +17732,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.053149013860095</v>
+        <v>10.053149013860097</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17736,7 +17742,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.277638809778461</v>
+        <v>12.277638809778463</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17745,7 +17751,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.55492968813451693</v>
       </c>
@@ -17777,7 +17783,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2400573713891494</v>
+        <v>0.24005737138914962</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17815,7 +17821,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>15.289255377213328</v>
+        <v>15.289255377213331</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17834,9 +17840,9 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
-        <v>0.34169791668185379</v>
+        <v>0.3416979166818539</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17844,7 +17850,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17855,7 +17861,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17867,7 +17873,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17875,11 +17881,11 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>21.898529897335333</v>
+        <v>21.89852989733534</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17887,7 +17893,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>25.506465679482364</v>
+        <v>25.506465679482371</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17895,9 +17901,9 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
-        <v>7.5378351616592565E-2</v>
+        <v>7.5378351616592454E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -17933,7 +17939,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>19.772438160850257</v>
+        <v>19.77243816085026</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -17943,7 +17949,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>23.150082537164366</v>
+        <v>23.150082537164369</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -17951,7 +17957,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.16076746951188714</v>
       </c>
@@ -17960,32 +17966,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61484DF-61EF-4FF7-8CB2-6BEA0BB43B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43C9900-2D9A-4A05-8BA5-5C74AFF9ED53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4918,7 +4918,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>25.625513351383745</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4972,7 +4972,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>91887</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5043,7 +5043,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>100741.35470787497</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5074,7 +5074,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>5113.2</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5109,7 +5109,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>25.944000372833873</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5168,111 +5168,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.04</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>15</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>31.76 HKD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.03</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>10</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>28.49 HKD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.02</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>10</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>27.6 HKD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>10</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>25.94 HKD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>0</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>15</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>25.94 HKD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-99584.747051220009</v>
       </c>
       <c r="D86" s="248">
@@ -9655,7 +9655,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>109180.86700165378</v>
       </c>
       <c r="D87" s="248">
@@ -9672,7 +9672,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>5541.5535235920006</v>
       </c>
       <c r="D88" s="248">
@@ -15630,7 +15630,7 @@
         <v>91690.584985000663</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E21" s="125">
@@ -15652,7 +15652,7 @@
         <v>93510.048868476399</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E22" s="125">
@@ -15674,7 +15674,7 @@
         <v>95365.617318454941</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E23" s="125">
@@ -15696,7 +15696,7 @@
         <v>97258.006776594848</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E24" s="125">
@@ -15718,7 +15718,7 @@
         <v>99187.947901278458</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E25" s="125">
@@ -15740,7 +15740,7 @@
         <v>101156.18584972182</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E26" s="125">
@@ -15762,7 +15762,7 @@
         <v>103163.48056568242</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E27" s="125">
@@ -15784,7 +15784,7 @@
         <v>105210.6070728763</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E28" s="125">
@@ -15806,7 +15806,7 @@
         <v>107298.35577421756</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E29" s="125">
@@ -15828,7 +15828,7 @@
         <v>109427.53275699561</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>1.98435191985455E-2</v>
       </c>
       <c r="E30" s="125">
@@ -15850,7 +15850,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15872,7 +15872,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15894,7 +15894,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15916,7 +15916,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15938,7 +15938,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15960,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15982,7 +15982,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -16004,7 +16004,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -16026,7 +16026,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -16048,7 +16048,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -16070,7 +16070,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -16092,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -16114,7 +16114,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -16136,7 +16136,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16158,7 +16158,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16180,7 +16180,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16202,7 +16202,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16224,7 +16224,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16246,7 +16246,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16268,7 +16268,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16969,7 +16969,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17186,7 +17186,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>25.944000372833873</v>
       </c>
       <c r="D22" t="str">
@@ -17233,7 +17233,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>27.598388143948494</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17291,7 +17291,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>25.944000372833859</v>
       </c>
       <c r="D33" t="str">
@@ -17349,7 +17349,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>28.486571722713233</v>
       </c>
       <c r="D39" t="str">
@@ -17450,7 +17450,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>25.944000372833852</v>
       </c>
       <c r="D51" t="str">
@@ -17508,7 +17508,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>31.760166009194872</v>
       </c>
       <c r="D57" t="str">
@@ -17596,7 +17596,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>27.584825058794923</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43C9900-2D9A-4A05-8BA5-5C74AFF9ED53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9FEC2A-FBB6-466E-B06F-C224BCC09D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9FEC2A-FBB6-466E-B06F-C224BCC09D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB9A132-AE13-4A7F-8329-26C45391FC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="462">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2338,100 +2333,130 @@
     <t>CNY</t>
   </si>
   <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>中国海油</t>
+  </si>
+  <si>
+    <t>0883.HK</t>
+  </si>
+  <si>
+    <t>600938.SS</t>
+  </si>
+  <si>
     <t>ENG_01</t>
   </si>
   <si>
-    <t>Company Information</t>
-  </si>
-  <si>
-    <t>Market Currency</t>
-  </si>
-  <si>
-    <t>Symbol:</t>
-  </si>
-  <si>
-    <t>Listing Information</t>
-  </si>
-  <si>
-    <t>Forex Symbol:</t>
-  </si>
-  <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
+    <t>N</t>
   </si>
   <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>中国海油</t>
-  </si>
-  <si>
-    <t>0883.HK</t>
-  </si>
-  <si>
-    <t>600938.SS</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2447,7 +2472,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2466,6 +2491,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3114,7 +3140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3620,9 +3646,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3839,29 +3862,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3880,7 +3910,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3927,8 +3971,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4169,15 +4213,15 @@
         <v>45792</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>446</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4192,7 +4236,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4201,10 +4245,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>447</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4218,9 +4262,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4241,20 +4285,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4272,19 +4316,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4298,7 +4342,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4327,73 +4371,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>419</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>444</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>450</v>
+        <v>436</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>450</v>
+        <v>437</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v>HKD/CNY:</v>
       </c>
-      <c r="E25" s="334">
+      <c r="E25" s="333">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v>0.92270154537561078</v>
       </c>
@@ -4403,14 +4451,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>27.585840894032099</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.24005737138914962</v>
       </c>
@@ -4421,96 +4469,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>438</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>435</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>0883.HK (HKD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v>600938.SS (CNY)</v>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>434</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>431</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C29" s="345">
+        <v>427</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>12.277638809778463</v>
       </c>
-      <c r="D29" s="345">
+      <c r="D29" s="344">
         <f>D144</f>
         <v>11.328596303346162</v>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>429</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>426</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C30" s="346">
+        <v>428</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>18.159816530624241</v>
       </c>
-      <c r="D30" s="346">
+      <c r="D30" s="345">
         <f>D152</f>
         <v>16.75609077654455</v>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>442</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C31" s="346">
+        <v>429</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>25.506465679482371</v>
       </c>
-      <c r="D31" s="346">
+      <c r="D31" s="345">
         <f>D160</f>
         <v>23.534855299528363</v>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C32" s="346">
+        <v>430</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>23.150082537164369</v>
       </c>
-      <c r="D32" s="346">
+      <c r="D32" s="345">
         <f>D168</f>
         <v>21.360616932614505</v>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>443</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>440</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4519,8 +4567,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4529,22 +4577,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4556,13 +4604,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4582,13 +4630,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4617,13 +4665,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4639,19 +4687,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>801.81967938187529</v>
       </c>
@@ -4659,14 +4707,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-2807</v>
       </c>
@@ -4674,8 +4722,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4709,13 +4757,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4731,13 +4779,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4753,22 +4801,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4797,26 +4845,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.11891189490201272</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>8.1206496519721574E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0.74012355537751062</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4829,22 +4885,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4853,7 +4909,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4862,7 +4918,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4873,7 +4929,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4882,42 +4938,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>25.625513351383745</v>
       </c>
@@ -4927,8 +4983,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4940,13 +4996,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4959,13 +5015,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4982,9 +5038,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>2.0951997362493384</v>
       </c>
@@ -4994,28 +5050,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>0.40943456145688223</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>0.12260820136742831</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>0.75207444874659302</v>
       </c>
@@ -5053,9 +5109,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>2.2970959963143938</v>
       </c>
@@ -5084,9 +5140,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.11659076138507207</v>
       </c>
@@ -5096,20 +5152,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>451</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>25.944000372833873</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5118,10 +5174,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>-0.45424610691085382</v>
       </c>
@@ -5131,8 +5187,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5141,49 +5197,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.04</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>15</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>31.76 HKD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5201,11 +5257,11 @@
         <f>DCF!D75</f>
         <v>10</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>28.49 HKD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
@@ -5223,11 +5279,11 @@
         <f>DCF!D76</f>
         <v>10</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>27.6 HKD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
@@ -5245,11 +5301,11 @@
         <f>DCF!D77</f>
         <v>10</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>25.94 HKD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5267,11 +5323,11 @@
         <f>DCF!D78</f>
         <v>15</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>25.94 HKD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5290,17 +5346,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5309,22 +5365,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5335,7 +5391,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5344,7 +5400,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5364,22 +5420,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>0883.HK</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v>600938.SS</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5412,20 +5468,20 @@
         <f>Scenarios!C83</f>
         <v>12.277638809778463</v>
       </c>
-      <c r="D144" s="335">
+      <c r="D144" s="334">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v>11.328596303346162</v>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>421</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5441,14 +5497,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5481,20 +5537,20 @@
         <f>Scenarios!C93</f>
         <v>18.159816530624241</v>
       </c>
-      <c r="D152" s="335">
+      <c r="D152" s="334">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v>16.75609077654455</v>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>421</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5510,12 +5566,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5544,26 +5600,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>25.506465679482371</v>
       </c>
-      <c r="D160" s="335">
+      <c r="D160" s="334">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v>23.534855299528363</v>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>421</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5579,12 +5635,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5613,26 +5669,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>23.150082537164369</v>
       </c>
-      <c r="D168" s="335">
+      <c r="D168" s="334">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v>21.360616932614505</v>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>421</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v>CNY</v>
       </c>
@@ -5647,8 +5703,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5657,113 +5713,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5780,6 +5825,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5792,7 +5848,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6380,7 +6436,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>220891</v>
@@ -6416,7 +6472,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-175426</v>
@@ -6452,7 +6508,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-97935</v>
@@ -6517,7 +6573,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7822,7 +7878,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8270,11 +8326,11 @@
         <f t="shared" si="40"/>
         <v>31381.7863</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8304,11 +8360,11 @@
         <f t="shared" si="40"/>
         <v>6313.6594999999998</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8411,17 +8467,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8505,7 +8561,7 @@
       <c r="C4" s="19">
         <v>33661</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8516,7 +8572,7 @@
         <f>72912+81284</f>
         <v>154196</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8528,7 +8584,7 @@
         <f>45771+4</f>
         <v>45775</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8538,7 +8594,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8549,7 +8605,7 @@
       <c r="C6" s="19">
         <v>5732</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8559,7 +8615,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8570,7 +8626,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8580,7 +8636,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8591,7 +8647,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8601,7 +8657,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8612,7 +8668,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8622,7 +8678,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8633,10 +8689,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8646,10 +8702,10 @@
         <f>12837+12408</f>
         <v>25245</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8707,7 +8763,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8716,7 +8772,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8727,7 +8783,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8736,7 +8792,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8747,7 +8803,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8757,7 +8813,7 @@
         <f>8504+18</f>
         <v>8522</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8768,7 +8824,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8778,7 +8834,7 @@
         <f>25047+23444</f>
         <v>48491</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8790,7 +8846,7 @@
         <f>632410+12755</f>
         <v>645165</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8799,7 +8855,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8810,7 +8866,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8819,7 +8875,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8830,7 +8886,7 @@
       <c r="C21" s="19">
         <v>16961</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8839,7 +8895,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8850,10 +8906,10 @@
       <c r="C22" s="19">
         <v>25465</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8862,10 +8918,10 @@
       <c r="C23" s="19">
         <v>47068</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9198,13 +9254,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9220,7 +9276,7 @@
         <f>H29</f>
         <v>-19921.400000000023</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9235,23 +9291,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-0.45424610691085382</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9265,7 +9321,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.47663929536624461</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9276,22 +9332,22 @@
         <f>G29/G32</f>
         <v>0.70771698061406008</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9305,7 +9361,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.22812375750231934</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9319,22 +9375,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>8.692811385878442E-3</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9356,22 +9412,22 @@
         <f>G39/G32</f>
         <v>0.61078917447156578</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9385,7 +9441,7 @@
         <f>G28/G29</f>
         <v>2.5255903299854993E-3</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9404,13 +9460,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9438,7 +9494,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9448,7 +9504,7 @@
         <f>G18</f>
         <v>48491</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9458,7 +9514,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9468,26 +9524,26 @@
         <f>SUM(C66:C69)</f>
         <v>202687</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9498,65 +9554,65 @@
         <v>-26727.322646062512</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>6.2880051282963478</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>5.769227319995565</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>53454.645292125024</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9570,7 +9626,7 @@
         <f>G7*H7+G17*H17</f>
         <v>5113.2</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9584,7 +9640,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9598,7 +9654,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9612,11 +9668,11 @@
         <f>SUM(D79:D81)</f>
         <v>5113.2</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9627,76 +9683,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-99584.747051220009</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-2.0951997362493389</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>109180.86700165378</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>2.2970959963143938</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>5541.5535235920006</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>0.1165907613850721</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>15137.673474025771</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>0.31848702145012697</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9817,7 +9873,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9831,7 +9887,7 @@
         <v>376364</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9887,7 +9943,7 @@
         <f>C25</f>
         <v>-245261.93617515016</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-218801</v>
@@ -9942,7 +9998,7 @@
         <f>C4+C5</f>
         <v>131102.06382484984</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>201705</v>
@@ -9997,7 +10053,7 @@
         <f>C35</f>
         <v>-8924</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-8924</v>
@@ -10053,7 +10109,7 @@
         <v>122178.06382484984</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -10109,7 +10165,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>74606</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>74606</v>
@@ -10164,7 +10220,7 @@
         <f>-C4*C78</f>
         <v>-74606</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-74606</v>
@@ -10220,7 +10276,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10276,7 +10332,7 @@
         <f>C50</f>
         <v>-2005.1803206181248</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-1218.572383664188</v>
@@ -10331,7 +10387,7 @@
         <f>SUM(C8:C12)</f>
         <v>120172.88350423172</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>193398.4276163358</v>
@@ -10386,7 +10442,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-30043.220876057931</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-51994</v>
@@ -10442,7 +10498,7 @@
         <v>-223.13946170149947</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10499,7 +10555,7 @@
         <v>89906.523166472296</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10556,8 +10612,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10581,8 +10637,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10607,7 +10663,7 @@
         <v>89906.523166472296</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10703,7 +10759,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10727,7 +10783,7 @@
         <v>-239590.97053351856</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10784,7 +10840,7 @@
         <v>-5670.965641631592</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10841,7 +10897,7 @@
         <v>-245261.93617515016</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10890,14 +10946,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10909,8 +10965,8 @@
         <v>0.6365937510854347</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10969,8 +11025,8 @@
         <v>1.5067768547553942E-2</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11027,7 +11083,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.65166151963298868</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.52032789068408059</v>
@@ -11075,14 +11131,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -11093,8 +11149,8 @@
         <f>G33</f>
         <v>-7213</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11151,8 +11207,8 @@
         <v>-1711</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11210,7 +11266,7 @@
         <v>-8924</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11259,14 +11315,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11279,7 +11335,7 @@
         <v>1.9164957328543644E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11337,7 +11393,7 @@
         <v>4.546130873303504E-3</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11393,7 +11449,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>2.3711088201847148E-2</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>2.1222051528396742E-2</v>
@@ -11441,26 +11497,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11539,7 +11595,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11550,7 +11606,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-2807</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-2807</v>
@@ -11599,111 +11655,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>801.81967938187529</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>1588.427616335812</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>1665.7343292216447</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>1033.0672843039545</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>464.88027793677952</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>510.62907328849445</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>369.83101577658761</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>276.64207206195277</v>
       </c>
-      <c r="N48" s="323">
+      <c r="N48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="323">
+      <c r="O48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="323">
+      <c r="P48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>2312.94</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>4582</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>4805</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>2980</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>1341</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>1472.9675999999999</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>1066.8196</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>798.00549999999998</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="318">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="319">
+      <c r="O49" s="318">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="319">
+      <c r="P49" s="318">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11717,7 +11773,7 @@
         <f>C47+C48</f>
         <v>-2005.1803206181248</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-1218.572383664188</v>
@@ -11765,14 +11821,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11785,8 +11841,8 @@
       <c r="C53" s="87">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11812,8 +11868,8 @@
         <f>G54</f>
         <v>3.0548390958459848E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11839,7 +11895,7 @@
         <f>-C8/C47</f>
         <v>43.526207276398232</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>68.678660491628079</v>
@@ -11887,14 +11943,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11908,7 +11964,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11963,7 +12019,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>1836</v>
@@ -12018,7 +12074,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -12073,7 +12129,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>1836</v>
@@ -12124,11 +12180,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12184,7 +12240,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-4580</v>
@@ -12232,14 +12288,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12253,7 +12309,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12277,7 +12333,7 @@
       <c r="C67" s="177">
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>3.7862696170423378E-2</v>
@@ -12302,7 +12358,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12328,7 +12384,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12356,7 +12412,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12378,7 +12434,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12402,7 +12458,7 @@
         <v>0.65166151963298868</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12459,7 +12515,7 @@
         <v>0.34833848036701132</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12516,7 +12572,7 @@
         <v>2.3711088201847148E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12573,7 +12629,7 @@
         <v>0.32462739216516417</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12630,7 +12686,7 @@
         <v>0.19822831089052087</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12687,8 +12743,8 @@
         <v>0.19822831089052087</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>453</v>
+      <c r="E78" s="295" t="s">
+        <v>461</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12746,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12803,7 +12859,7 @@
         <v>5.3277686511412486E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12860,7 +12916,7 @@
         <v>0.31929962351402291</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12917,7 +12973,7 @@
         <v>7.9824905878505728E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12970,12 +13026,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>5.9288205487639486E-4</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -13032,7 +13088,7 @@
         <v>0.2388818355806408</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -13084,26 +13140,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -13113,7 +13169,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -13139,7 +13195,7 @@
         <v>0.2388818355806408</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13188,14 +13244,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13207,7 +13263,7 @@
         <f>G90</f>
         <v>1.4</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>1.4</v>
@@ -13263,7 +13319,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>66541.935577600001</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>66541.935577600001</v>
@@ -13318,7 +13374,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.74012355537751062</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.47073200161933748</v>
@@ -13367,13 +13423,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>8.1206496519721574E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>8.1206496519721574E-2</v>
@@ -13421,7 +13477,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13430,7 +13486,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13454,7 +13510,7 @@
         <v>-0.10497353188777325</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13511,7 +13567,7 @@
         <v>-0.37862533328021186</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13589,7 +13645,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13604,7 +13660,7 @@
         <v>1056281</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13661,7 +13717,7 @@
         <v>33661</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13718,7 +13774,7 @@
         <v>5732</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13775,7 +13831,7 @@
         <v>306845</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13832,7 +13888,7 @@
         <v>749436</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13881,7 +13937,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13890,7 +13946,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13916,7 +13972,7 @@
         <v>8.9437353200624931E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13973,7 +14029,7 @@
         <v>1.5229936975906303E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -14030,7 +14086,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -14049,63 +14105,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.6008682291893146</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.6902490128132808</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.4510047502417471</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.1035316540316042</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>3.2993724703992493</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>2.023384343788782</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>2.361580198596569</v>
       </c>
-      <c r="N113" s="328">
+      <c r="N113" s="327">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.716234671522463</v>
       </c>
-      <c r="O113" s="328">
+      <c r="O113" s="327">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>3.6258745986141627</v>
       </c>
-      <c r="P113" s="328">
+      <c r="P113" s="327">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>3.8254510220089513</v>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14113,58 +14169,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.5626305677332901</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6995798647481588</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.4609446298590569</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.9450934170318153</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.9447404307897362</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.059112762372902</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>2.4469482333251551</v>
       </c>
-      <c r="N114" s="328">
+      <c r="N114" s="327">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.63781492393722561</v>
       </c>
-      <c r="O114" s="328">
+      <c r="O114" s="327">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>0.76192556289509195</v>
       </c>
-      <c r="P114" s="328">
+      <c r="P114" s="327">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.58467527247211815</v>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14173,7 +14229,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14229,7 +14285,7 @@
         <f>C81</f>
         <v>0.31929962351402291</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.4599183545926474</v>
@@ -14283,7 +14339,7 @@
         <f>C4/C101</f>
         <v>0.35631048934895165</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.39810050545262105</v>
@@ -14338,7 +14394,7 @@
         <v>1.4094345614568822</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14395,7 +14451,7 @@
         <v>0.16302668116403515</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14491,7 +14547,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14516,7 +14572,7 @@
         <v>2.0500410681106991</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14573,7 +14629,7 @@
         <v>0.11891189490201272</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14622,7 +14678,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15355,7 +15411,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15423,7 +15479,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15433,7 +15489,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15451,10 +15507,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15469,8 +15525,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15485,8 +15541,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15501,8 +15557,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16847,7 +16903,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16878,12 +16934,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16898,6 +16954,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>442</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>66541.935577600001</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>831774.19472000003</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>446</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>18.966046050000003</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>18.620540752123823</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>448</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>447</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>67862.361753742487</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>62835.520142354144</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>69208.989832061518</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>59335.553696897732</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>70582.339750505969</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>56030.536940591148</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>71982.941764423405</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>52909.611088959806</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>73411.336651293517</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>49962.522196658472</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>74868.075919524344</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>47179.587467662597</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>76353.722021391586</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>44551.663441996869</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>77868.848570203481</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>42070.115954477107</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>79414.040561774949</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>39726.791766763716</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>80989.894600296597</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>1.98435191985455E-2</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>37513.991779522315</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>848279.52192178112</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>392917.55062975816</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>885033.44510564208</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>885033.44510564208</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.02</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.03</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.04</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>831774.1947199998</v>
+      </c>
+      <c r="C51" s="124">
+        <v>831774.1947199998</v>
+      </c>
+      <c r="D51" s="124">
+        <v>858611.58435650798</v>
+      </c>
+      <c r="E51" s="124">
+        <v>872329.51311163534</v>
+      </c>
+      <c r="F51" s="124">
+        <v>886252.74210126267</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>831774.1947199998</v>
+      </c>
+      <c r="C52" s="124">
+        <v>831774.1947199998</v>
+      </c>
+      <c r="D52" s="124">
+        <v>885473.6869878954</v>
+      </c>
+      <c r="E52" s="124">
+        <v>914303.08723679534</v>
+      </c>
+      <c r="F52" s="124">
+        <v>944555.32235037233</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>831774.1947199998</v>
+      </c>
+      <c r="C53" s="124">
+        <v>831774.1947199998</v>
+      </c>
+      <c r="D53" s="124">
+        <v>918722.98715735739</v>
+      </c>
+      <c r="E53" s="124">
+        <v>967608.18250875163</v>
+      </c>
+      <c r="F53" s="124">
+        <v>1020560.1293549866</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>831774.19471999968</v>
+      </c>
+      <c r="C54" s="124">
+        <v>831774.19471999968</v>
+      </c>
+      <c r="D54" s="124">
+        <v>952598.69192144671</v>
+      </c>
+      <c r="E54" s="124">
+        <v>1023405.045002889</v>
+      </c>
+      <c r="F54" s="124">
+        <v>1102366.0834342125</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>831774.19471999968</v>
+      </c>
+      <c r="C55" s="124">
+        <v>831774.19471999968</v>
+      </c>
+      <c r="D55" s="124">
+        <v>984104.97711523261</v>
+      </c>
+      <c r="E55" s="124">
+        <v>1076779.0564839209</v>
+      </c>
+      <c r="F55" s="124">
+        <v>1182947.7311820304</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>831774.19471999945</v>
+      </c>
+      <c r="C56" s="124">
+        <v>831774.19471999945</v>
+      </c>
+      <c r="D56" s="124">
+        <v>1011897.9034381259</v>
+      </c>
+      <c r="E56" s="124">
+        <v>1125254.5295689418</v>
+      </c>
+      <c r="F56" s="124">
+        <v>1258413.1584305295</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>0.02</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>0.03</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.04</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>18.966046050000003</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>18.966046050000003</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>18.966046050000003</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>18.966046050000003</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>18.966046050000003</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>18.966046049999999</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999999</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>19.57798997773768</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>19.890785048962449</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>20.208261359069496</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999999</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999999</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>20.190497409130433</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>20.847862997273715</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>21.537671947733728</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999999</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999999</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>20.948645187875325</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>22.063321348885463</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>23.270727239448007</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999996</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999996</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>21.721076192119455</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>23.335596769578892</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>25.136059804559714</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999996</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999996</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>22.439479888270341</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>24.552626542861589</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>26.973475838468374</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999989</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>18.966046049999989</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>23.073211884105696</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>25.657960250810458</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>28.69423223781757</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>0.04</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>15</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>23.270727239448007</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>0.03</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>10</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>20.847862997273715</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>0.02</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>10</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>20.190497409130433</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>10</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>18.966046049999999</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>15</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>18.966046049999999</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16918,19 +18425,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-17.239999999999998</v>
       </c>
@@ -16947,19 +18454,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>1.4</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
@@ -16973,13 +18480,13 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>28.985840894032098</v>
       </c>
@@ -16996,15 +18503,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国海油(0883.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17021,12 +18528,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17043,37 +18550,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>449</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17087,12 +18594,12 @@
         <v>0.19549305441006948</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17105,12 +18612,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22866289579809873</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17123,8 +18630,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22962169479662209</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17140,7 +18647,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -17150,25 +18657,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17178,23 +18685,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>25.944000372833873</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17214,8 +18721,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17225,23 +18732,23 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>27.598388143948494</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17251,8 +18758,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17272,8 +18779,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17283,23 +18790,23 @@
         <v>0</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>25.944000372833859</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17309,8 +18816,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17330,8 +18837,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17341,23 +18848,23 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>28.486571722713233</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17368,8 +18875,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17431,8 +18938,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17442,23 +18949,23 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>25.944000372833852</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17468,12 +18975,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17489,8 +18996,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17500,23 +19007,23 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>31.760166009194872</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17526,8 +19033,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17542,16 +19049,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17560,10 +19067,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17575,8 +19082,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17587,8 +19094,8 @@
         <v>1.98435191985455E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17596,30 +19103,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>27.584825058794923</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17627,38 +19134,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>1.15453077059916E-2</v>
       </c>
@@ -17678,10 +19185,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17702,12 +19209,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17751,7 +19258,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.55492968813451693</v>
       </c>
@@ -17761,14 +19268,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>17.239999999999998</v>
       </c>
@@ -17779,9 +19286,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.24005737138914962</v>
       </c>
@@ -17791,12 +19298,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17840,28 +19347,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.3416979166818539</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17873,7 +19380,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17885,23 +19392,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>25.506465679482371</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>7.5378351616592454E-2</v>
       </c>
@@ -17911,12 +19418,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17945,19 +19452,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>23.150082537164369</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>0.16076746951188714</v>
       </c>
@@ -17966,33 +19473,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865FDA5B-5618-AD45-A9AF-8A0F117067BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DA09D4-DC9A-5C46-956D-EE9F3461CC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="5280" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3877,6 +3877,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3912,9 +3915,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4223,7 +4223,7 @@
       <c r="C1" s="44">
         <v>45792</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>462</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0837740600000001</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="E25" s="329">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.92270154537561078</v>
+        <v>0.922701545375611</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.15">
@@ -4466,14 +4466,14 @@
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>27.585840894032099</v>
+        <v>27.585840894032092</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24005737138914962</v>
+        <v>0.2400573713891494</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
@@ -4505,11 +4505,11 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>12.277638809778463</v>
+        <v>12.277638809778461</v>
       </c>
       <c r="D29" s="340">
         <f>D144</f>
-        <v>11.328596303346162</v>
+        <v>11.328596303346163</v>
       </c>
       <c r="E29" s="336" t="s">
         <v>426</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D30" s="341">
         <f>D152</f>
-        <v>16.75609077654455</v>
+        <v>16.756090776544553</v>
       </c>
       <c r="E30" s="337" t="s">
         <v>439</v>
@@ -4543,11 +4543,11 @@
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>25.506465679482371</v>
+        <v>25.506465679482364</v>
       </c>
       <c r="D31" s="341">
         <f>D160</f>
-        <v>23.534855299528363</v>
+        <v>23.53485529952836</v>
       </c>
       <c r="E31" s="337" t="s">
         <v>438</v>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>23.150082537164369</v>
+        <v>23.150082537164366</v>
       </c>
       <c r="D32" s="341">
         <f>D168</f>
@@ -4590,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4617,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4643,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4678,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4700,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4770,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4814,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11891189490201272</v>
+        <v>0.1189118949020127</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4898,22 +4898,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4957,22 +4957,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>25.625513351383745</v>
+        <v>25.625513351383738</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -5009,13 +5009,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5028,13 +5028,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C109" s="245">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11659076138507207</v>
+        <v>0.11659076138507206</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5165,13 +5165,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>25.944000372833873</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C114" s="245">
         <f>BS!D47</f>
-        <v>-0.45424610691085382</v>
+        <v>-0.45424610691085376</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5210,13 +5210,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>27.585840894032099</v>
+        <v>27.585840894032092</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
@@ -5359,13 +5359,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5378,22 +5378,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>10.053149013860097</v>
+        <v>10.053149013860095</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -5479,11 +5479,11 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>12.277638809778463</v>
+        <v>12.277638809778461</v>
       </c>
       <c r="D144" s="330">
         <f>IF($D$11="","",C144*$E$25)</f>
-        <v>11.328596303346162</v>
+        <v>11.328596303346163</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.15">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>15.289255377213331</v>
+        <v>15.289255377213328</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.15">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="D152" s="330">
         <f>IF($D$11="","",C152*$E$25)</f>
-        <v>16.75609077654455</v>
+        <v>16.756090776544553</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.15">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3416979166818539</v>
+        <v>0.34169791668185379</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.15">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>21.89852989733534</v>
+        <v>21.898529897335333</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.15">
@@ -5617,11 +5617,11 @@
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>25.506465679482371</v>
+        <v>25.506465679482364</v>
       </c>
       <c r="D160" s="330">
         <f>IF($D$11="","",C160*$E$25)</f>
-        <v>23.534855299528363</v>
+        <v>23.53485529952836</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.15">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>7.5378351616592454E-2</v>
+        <v>7.5378351616592565E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.15">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>19.77243816085026</v>
+        <v>19.772438160850257</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>23.150082537164369</v>
+        <v>23.150082537164366</v>
       </c>
       <c r="D168" s="330">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5726,13 +5726,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5769,13 +5769,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5783,22 +5783,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -9298,11 +9298,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.045527358970482</v>
+        <v>17.045527358970478</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45424610691085382</v>
+        <v>-0.45424610691085376</v>
       </c>
       <c r="F47" s="275"/>
     </row>
@@ -9708,11 +9708,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-99584.747051220009</v>
+        <v>-99584.747051219994</v>
       </c>
       <c r="D86" s="245">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.0951997362493389</v>
+        <v>-2.0951997362493384</v>
       </c>
       <c r="E86" s="262" t="str">
         <f>Market_currency</f>
@@ -9725,11 +9725,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>109180.86700165378</v>
+        <v>109180.86700165375</v>
       </c>
       <c r="D87" s="245">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.2970959963143938</v>
+        <v>2.2970959963143933</v>
       </c>
       <c r="E87" s="262" t="str">
         <f>Market_currency</f>
@@ -9742,11 +9742,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>5541.5535235920006</v>
+        <v>5541.5535235919988</v>
       </c>
       <c r="D88" s="245">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.1165907613850721</v>
+        <v>0.11659076138507206</v>
       </c>
       <c r="E88" s="262" t="str">
         <f>Market_currency</f>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>15137.673474025771</v>
+        <v>15137.673474025756</v>
       </c>
       <c r="D89" s="264">
         <f>SUM(D86:D88)</f>
@@ -14582,50 +14582,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0500410681106991</v>
+        <v>2.0500410681106986</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="290"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2232431166363908</v>
+        <v>3.2232431166363904</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.8139557023022834</v>
+        <v>2.8139557023022825</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>3.2085276639884759</v>
+        <v>3.2085276639884754</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7337182180759734</v>
+        <v>1.7337182180759729</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.63756559662202417</v>
+        <v>0.63756559662202394</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3678011880301388</v>
+        <v>1.3678011880301386</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1591957982944394</v>
+        <v>1.1591957982944392</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>6.8259362330267566</v>
+        <v>6.8259362330267557</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4205637547540872</v>
+        <v>6.4205637547540864</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4667832402675698</v>
+        <v>6.4667832402675689</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14639,42 +14639,42 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11891189490201272</v>
+        <v>0.1189118949020127</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18696305780953545</v>
+        <v>0.18696305780953543</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.16322248853261506</v>
+        <v>0.16322248853261501</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18610949327079329</v>
+        <v>0.18610949327079326</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10056370174454603</v>
+        <v>0.100563701744546</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6981763145129014E-2</v>
+        <v>3.6981763145129E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.9338816011028948E-2</v>
+        <v>7.9338816011028934E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.7238735399909488E-2</v>
+        <v>6.7238735399909474E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.3959359763936634</v>
+        <v>0.39593597639366335</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.37510343621041592</v>
+        <v>0.37510343621041586</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15520,10 +15520,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15538,8 +15538,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15554,8 +15554,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15570,8 +15570,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="C11" s="229">
         <f>Exchange_Rate</f>
-        <v>1.0837740600000001</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>25.944000372833873</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>27.584825058794923</v>
+        <v>27.58482505879492</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16597,23 +16597,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>25.944000372833873</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>25.944000372833873</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>25.944000372833873</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>25.944000372833873</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>25.944000372833873</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16624,23 +16624,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>25.944000372833862</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833862</v>
+        <v>25.944000372833859</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>26.770813576239554</v>
+        <v>26.770813576239547</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>27.193439054042674</v>
+        <v>27.19343905404267</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>27.622389474280432</v>
+        <v>27.622389474280428</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16651,23 +16651,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833859</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833859</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>27.598388143948494</v>
+        <v>27.598388143948487</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>28.486571722713233</v>
+        <v>28.486571722713226</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>29.418590363990191</v>
+        <v>29.418590363990184</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16678,23 +16678,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833852</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833852</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>28.622741136413637</v>
+        <v>28.62274113641363</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>30.12880880972472</v>
+        <v>30.128808809724717</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>31.760166009194872</v>
+        <v>31.760166009194865</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16705,23 +16705,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833859</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833859</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>29.6663925627625</v>
+        <v>29.666392562762493</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>31.847812902283948</v>
+        <v>31.847812902283941</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>34.280464885725387</v>
+        <v>34.28046488572538</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16732,23 +16732,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833852</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833852</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>30.637046301494621</v>
+        <v>30.637046301494614</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>33.492173177592221</v>
+        <v>33.492173177592214</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>36.763045017864883</v>
+        <v>36.763045017864876</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.15">
@@ -16758,23 +16758,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833852</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833852</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>31.493297924930808</v>
+        <v>31.4932979249308</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>34.98561802192647</v>
+        <v>34.985618021926463</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>39.088003312796459</v>
+        <v>39.088003312796452</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.760166009194872</v>
+        <v>31.760166009194865</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.486571722713233</v>
+        <v>28.486571722713226</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16854,7 +16854,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>27.598388143948494</v>
+        <v>27.598388143948487</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>25.944000372833859</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>25.944000372833852</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -17050,8 +17050,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>18.966046050000003</v>
+        <v>18.966046049999999</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18049,23 +18049,23 @@
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>18.966046050000003</v>
+        <v>18.966046049999999</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>18.966046050000003</v>
+        <v>18.966046049999999</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>18.966046050000003</v>
+        <v>18.966046049999999</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>18.966046050000003</v>
+        <v>18.966046049999999</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>18.966046050000003</v>
+        <v>18.966046049999999</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -18076,23 +18076,23 @@
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>18.966046049999999</v>
+        <v>18.966046049999996</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999999</v>
+        <v>18.966046049999996</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>19.57798997773768</v>
+        <v>19.577989977737676</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>19.890785048962449</v>
+        <v>19.890785048962446</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>20.208261359069496</v>
+        <v>20.208261359069489</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -18103,23 +18103,23 @@
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999999</v>
+        <v>18.966046049999996</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999999</v>
+        <v>18.966046049999996</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>20.190497409130433</v>
+        <v>20.19049740913043</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>20.847862997273715</v>
+        <v>20.847862997273708</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>21.537671947733728</v>
+        <v>21.537671947733724</v>
       </c>
       <c r="H62" s="121"/>
     </row>
@@ -18130,23 +18130,23 @@
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999999</v>
+        <v>18.966046049999996</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999999</v>
+        <v>18.966046049999996</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>20.948645187875325</v>
+        <v>20.948645187875321</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>22.063321348885463</v>
+        <v>22.063321348885459</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>23.270727239448007</v>
+        <v>23.270727239448004</v>
       </c>
       <c r="H63" s="121"/>
     </row>
@@ -18157,23 +18157,23 @@
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999996</v>
+        <v>18.966046049999989</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999996</v>
+        <v>18.966046049999989</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>21.721076192119455</v>
+        <v>21.721076192119451</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>23.335596769578892</v>
+        <v>23.335596769578888</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>25.136059804559714</v>
+        <v>25.136059804559707</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -18184,23 +18184,23 @@
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999996</v>
+        <v>18.966046049999989</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999996</v>
+        <v>18.966046049999989</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>22.439479888270341</v>
+        <v>22.439479888270338</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>24.552626542861589</v>
+        <v>24.552626542861585</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>26.973475838468374</v>
+        <v>26.973475838468371</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.15">
@@ -18210,23 +18210,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999989</v>
+        <v>18.966046049999985</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999989</v>
+        <v>18.966046049999985</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>23.073211884105696</v>
+        <v>23.073211884105692</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>25.657960250810458</v>
+        <v>25.657960250810454</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>28.69423223781757</v>
+        <v>28.694232237817562</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>23.270727239448007</v>
+        <v>23.270727239448004</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
@@ -18283,7 +18283,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>20.847862997273715</v>
+        <v>20.847862997273708</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18306,7 +18306,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>20.190497409130433</v>
+        <v>20.19049740913043</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18329,7 +18329,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>18.966046049999999</v>
+        <v>18.966046049999996</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>18.966046049999999</v>
+        <v>18.966046049999996</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>28.985840894032098</v>
+        <v>28.985840894032091</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18516,11 +18516,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国海油(0883.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18541,8 +18541,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18563,8 +18563,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18574,8 +18574,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18588,8 +18588,8 @@
       <c r="B11" s="160" t="s">
         <v>449</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18607,8 +18607,8 @@
         <v>0.19549305441006948</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18625,8 +18625,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22866289579809873</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18643,8 +18643,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22962169479662209</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18670,21 +18670,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18698,8 +18698,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18707,14 +18707,14 @@
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>25.944000372833873</v>
+        <v>25.944000372833866</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18734,8 +18734,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18745,8 +18745,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18754,14 +18754,14 @@
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>27.598388143948494</v>
+        <v>27.598388143948487</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18771,8 +18771,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18792,8 +18792,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18803,8 +18803,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18812,14 +18812,14 @@
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>25.944000372833859</v>
+        <v>25.944000372833855</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18829,8 +18829,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18850,8 +18850,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18861,8 +18861,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18870,14 +18870,14 @@
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>28.486571722713233</v>
+        <v>28.486571722713226</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18888,8 +18888,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18897,7 +18897,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>27.445147305478514</v>
+        <v>27.445147305478507</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18951,8 +18951,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18962,8 +18962,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18971,14 +18971,14 @@
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>25.944000372833852</v>
+        <v>25.944000372833848</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18988,8 +18988,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -19009,8 +19009,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -19020,8 +19020,8 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -19029,14 +19029,14 @@
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>31.760166009194872</v>
+        <v>31.760166009194865</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -19046,8 +19046,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
@@ -19055,7 +19055,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>27.585840894032099</v>
+        <v>27.585840894032092</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>27.584825058794923</v>
+        <v>27.58482505879492</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>1.15453077059916E-2</v>
+        <v>1.1545307705991601E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.053149013860097</v>
+        <v>10.053149013860095</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19262,7 +19262,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.277638809778463</v>
+        <v>12.277638809778461</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24005737138914962</v>
+        <v>0.2400573713891494</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.15">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>15.289255377213331</v>
+        <v>15.289255377213328</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.3416979166818539</v>
+        <v>0.34169791668185379</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.15">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>21.89852989733534</v>
+        <v>21.898529897335333</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>25.506465679482371</v>
+        <v>25.506465679482364</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>7.5378351616592454E-2</v>
+        <v>7.5378351616592565E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.15">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>19.77243816085026</v>
+        <v>19.772438160850257</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -19469,7 +19469,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>23.150082537164369</v>
+        <v>23.150082537164366</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DA09D4-DC9A-5C46-956D-EE9F3461CC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D993BF1B-E2B9-459B-B882-4435E967E0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2380" yWindow="5280" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2505,7 +2494,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3880,29 +3869,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3918,7 +3907,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4207,7 +4196,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4216,7 +4205,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4233,7 +4222,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4247,7 +4236,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>417</v>
       </c>
@@ -4256,7 +4245,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4264,7 +4253,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4273,7 +4262,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4283,7 +4272,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4293,17 +4282,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>419</v>
       </c>
@@ -4315,7 +4304,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4327,7 +4316,7 @@
       </c>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>418</v>
       </c>
@@ -4339,7 +4328,7 @@
       </c>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>422</v>
       </c>
@@ -4353,7 +4342,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>421</v>
       </c>
@@ -4367,7 +4356,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4379,27 +4368,27 @@
       </c>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="347" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4414,7 +4403,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4427,7 +4416,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>436</v>
       </c>
@@ -4435,7 +4424,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>437</v>
       </c>
@@ -4443,7 +4432,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4459,28 +4448,28 @@
         <v>0.922701545375611</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>27.585840894032092</v>
+        <v>29.367659943749512</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2400573713891494</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.26346001995218948</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>435</v>
       </c>
@@ -4499,36 +4488,36 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>12.277638809778461</v>
+        <v>13.80652813600231</v>
       </c>
       <c r="D29" s="340">
         <f>D144</f>
-        <v>11.328596303346163</v>
+        <v>12.739304847361185</v>
       </c>
       <c r="E29" s="336" t="s">
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>18.159816530624241</v>
+        <v>19.147377018331063</v>
       </c>
       <c r="D30" s="341">
         <f>D152</f>
-        <v>16.756090776544553</v>
+        <v>17.667314364703532</v>
       </c>
       <c r="E30" s="337" t="s">
         <v>439</v>
@@ -4537,36 +4526,36 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>25.506465679482364</v>
+        <v>27.280544309305707</v>
       </c>
       <c r="D31" s="341">
         <f>D160</f>
-        <v>23.53485529952836</v>
+        <v>25.171800392884208</v>
       </c>
       <c r="E31" s="337" t="s">
         <v>438</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>430</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>23.150082537164366</v>
+        <v>24.427219859521085</v>
       </c>
       <c r="D32" s="341">
         <f>D168</f>
-        <v>21.360616932614505</v>
+        <v>22.539033513609919</v>
       </c>
       <c r="E32" s="337" t="s">
         <v>440</v>
@@ -4575,11 +4564,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4589,25 +4578,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="347" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="349" t="s">
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4616,16 +4605,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="348" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4638,20 +4627,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="348" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4664,7 +4653,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4677,16 +4666,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="348" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4699,16 +4688,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="348" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4723,7 +4712,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4738,7 +4727,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4751,12 +4740,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4769,16 +4758,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="348" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4791,8 +4780,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="348" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4800,7 +4789,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4813,25 +4802,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="347" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="347" t="s">
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4844,7 +4833,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4857,7 +4846,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4867,7 +4856,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4883,7 +4872,7 @@
         <v>0.74012355537751062</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4893,43 +4882,43 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="349" t="s">
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
+    </row>
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>432</v>
       </c>
@@ -4938,43 +4927,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="347" t="s">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
-    </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="347" t="s">
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
+    </row>
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4982,20 +4971,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>25.625513351383738</v>
+        <v>27.333880908142653</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -5005,38 +4994,38 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="347" t="s">
+    <row r="91" spans="1:6">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="347" t="s">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
+    </row>
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5049,7 +5038,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5062,7 +5051,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5071,7 +5060,7 @@
         <v>0.40943456145688223</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5080,7 +5069,7 @@
         <v>0.12260820136742831</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5089,12 +5078,12 @@
         <v>0.75207444874659302</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5107,7 +5096,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5120,7 +5109,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5133,12 +5122,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5151,7 +5140,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5164,29 +5153,29 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="347" t="s">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
+    </row>
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>451</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>25.944000372833866</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5199,7 +5188,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5209,16 +5198,16 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="348" t="s">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
-    </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5235,7 +5224,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5250,14 +5239,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>31.76 HKD</v>
+        <v>33.76 HKD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5272,14 +5261,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>28.49 HKD</v>
+        <v>30.31 HKD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5294,14 +5283,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>27.6 HKD</v>
+        <v>29.38 HKD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5316,14 +5305,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>25.94 HKD</v>
+        <v>27.65 HKD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5338,36 +5327,36 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>25.94 HKD</v>
+        <v>27.65 HKD</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>27.585840894032092</v>
+        <v>29.367659943749512</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="352" t="s">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
-    </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5377,30 +5366,30 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="350" t="s">
+    <row r="133" spans="1:6">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
-    </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="347" t="s">
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
+    </row>
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5409,16 +5398,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5431,7 +5420,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5444,49 +5433,49 @@
         <v>600938.SS</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>2.2244897959183665</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2.3201630471108023</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>10.053149013860095</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>11.486365088891507</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>12.277638809778461</v>
+        <v>13.80652813600231</v>
       </c>
       <c r="D144" s="330">
         <f>IF($D$11="","",C144*$E$25)</f>
-        <v>11.328596303346163</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+        <v>12.739304847361185</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>418</v>
       </c>
@@ -5499,21 +5488,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55492968813451693</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.52987305892103143</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
@@ -5522,7 +5511,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5532,30 +5521,30 @@
         <v>2.870561153410911</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>15.289255377213328</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>16.276815864920152</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>18.159816530624241</v>
+        <v>19.147377018331063</v>
       </c>
       <c r="D152" s="330">
         <f>IF($D$11="","",C152*$E$25)</f>
-        <v>16.756090776544553</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+        <v>17.667314364703532</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>418</v>
       </c>
@@ -5568,63 +5557,63 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34169791668185379</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.34801148423109862</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>3.6079357821470319</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>3.6407360358207437</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>21.898529897335333</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>23.639808273484963</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>25.506465679482364</v>
+        <v>27.280544309305707</v>
       </c>
       <c r="D160" s="330">
         <f>IF($D$11="","",C160*$E$25)</f>
-        <v>23.53485529952836</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+        <v>25.171800392884208</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>418</v>
       </c>
@@ -5637,21 +5626,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>7.5378351616592565E-2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.1068503191655141E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>425</v>
       </c>
@@ -5660,7 +5649,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5670,30 +5659,30 @@
         <v>3.3776443763141084</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>19.772438160850257</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>21.049575483206976</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>23.150082537164366</v>
+        <v>24.427219859521085</v>
       </c>
       <c r="D168" s="330">
         <f>IF($D$11="","",C168*$E$25)</f>
-        <v>21.360616932614505</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+        <v>22.539033513609919</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>418</v>
       </c>
@@ -5706,16 +5695,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.16076746951188714</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.16813787783196477</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5725,21 +5714,21 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="354" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5748,91 +5737,80 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="348" t="s">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
-    </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
+    </row>
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="353" t="s">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
-    </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="353" t="s">
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
-    </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
+    </row>
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5849,6 +5827,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5876,15 +5865,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5933,7 +5922,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5949,7 +5938,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5957,7 +5946,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5993,7 +5982,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6029,7 +6018,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6065,7 +6054,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6101,7 +6090,7 @@
       </c>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6137,7 +6126,7 @@
       </c>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6167,7 +6156,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6183,7 +6172,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6199,7 +6188,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6235,7 +6224,7 @@
       </c>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6271,7 +6260,7 @@
       </c>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6307,7 +6296,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6343,7 +6332,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6379,13 +6368,13 @@
       </c>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6415,7 +6404,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6431,7 +6420,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6447,7 +6436,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6483,7 +6472,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6519,7 +6508,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6555,7 +6544,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6581,7 +6570,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6589,7 +6578,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6626,7 +6615,7 @@
       </c>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6663,7 +6652,7 @@
       </c>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6700,7 +6689,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6737,7 +6726,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6774,7 +6763,7 @@
       </c>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6790,12 +6779,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6844,7 +6833,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6893,7 +6882,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6942,7 +6931,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6991,7 +6980,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7040,7 +7029,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7089,7 +7078,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7138,7 +7127,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7187,7 +7176,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7236,7 +7225,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7285,7 +7274,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7334,7 +7323,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7383,7 +7372,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7432,12 +7421,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7486,7 +7475,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7535,12 +7524,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7589,7 +7578,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7638,7 +7627,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7687,7 +7676,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7736,13 +7725,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7791,7 +7780,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7840,7 +7829,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7889,7 +7878,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7938,7 +7927,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7987,12 +7976,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8042,7 +8031,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8091,7 +8080,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8141,7 +8130,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8190,7 +8179,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8240,7 +8229,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8256,13 +8245,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8311,7 +8300,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8345,7 +8334,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8379,7 +8368,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8428,7 +8417,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8509,7 +8498,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8520,7 +8509,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8536,7 +8525,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8547,7 +8536,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8567,7 +8556,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8589,7 +8578,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8611,7 +8600,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8632,7 +8621,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8653,7 +8642,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8674,7 +8663,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8695,7 +8684,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8707,7 +8696,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8720,7 +8709,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8744,12 +8733,12 @@
         <v>138776.4</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8769,7 +8758,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8789,7 +8778,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8809,7 +8798,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8830,7 +8819,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8851,7 +8840,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8872,7 +8861,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8892,7 +8881,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8912,7 +8901,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8924,7 +8913,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8936,7 +8925,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8960,7 +8949,7 @@
         <v>9962.2999999999993</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8977,7 +8966,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8996,7 +8985,7 @@
         <v>-18033.400000000023</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9011,7 +9000,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9030,7 +9019,7 @@
         <v>-19921.400000000023</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9046,7 +9035,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -9063,7 +9052,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9083,7 +9072,7 @@
         <v>288811.59999999998</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9094,7 +9083,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -9107,7 +9096,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9126,7 +9115,7 @@
         <v>140072.9</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9142,7 +9131,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9158,7 +9147,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9174,7 +9163,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9193,7 +9182,7 @@
         <v>64516.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9213,7 +9202,7 @@
         <v>148738.69999999998</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9233,7 +9222,7 @@
         <v>143625.49999999997</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9252,7 +9241,7 @@
         <v>5113.2</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9263,7 +9252,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9277,7 +9266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9291,7 +9280,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9306,10 +9295,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9322,7 +9311,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9336,7 +9325,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9347,10 +9336,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9362,7 +9351,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9376,7 +9365,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9390,10 +9379,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9405,7 +9394,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9416,7 +9405,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9427,10 +9416,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9442,7 +9431,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9458,7 +9447,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9469,7 +9458,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9483,7 +9472,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9499,7 +9488,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9509,7 +9498,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9519,7 +9508,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9529,7 +9518,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9539,10 +9528,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9554,7 +9543,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9570,7 +9559,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9586,7 +9575,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9599,7 +9588,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9612,10 +9601,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9627,7 +9616,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9641,7 +9630,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9655,7 +9644,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9669,7 +9658,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9683,7 +9672,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9694,7 +9683,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9702,7 +9691,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9719,7 +9708,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9736,7 +9725,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9753,7 +9742,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9784,19 +9773,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9853,7 +9842,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9876,7 +9865,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9890,7 +9879,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9947,7 +9936,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10002,7 +9991,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10057,7 +10046,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10112,7 +10101,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10169,7 +10158,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10224,7 +10213,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10279,7 +10268,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10336,7 +10325,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10391,7 +10380,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10446,7 +10435,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10501,7 +10490,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10558,7 +10547,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10615,7 +10604,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10641,7 +10630,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10666,7 +10655,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10723,7 +10712,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10742,7 +10731,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10765,7 +10754,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10786,7 +10775,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10843,7 +10832,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10900,7 +10889,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10957,18 +10946,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11027,7 +11016,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11087,7 +11076,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11142,18 +11131,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11210,7 +11199,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11269,7 +11258,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11326,18 +11315,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11395,7 +11384,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11453,7 +11442,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11508,18 +11497,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11577,10 +11566,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11603,14 +11592,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11665,7 +11654,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11720,7 +11709,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11777,7 +11766,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11832,11 +11821,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11846,7 +11835,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11872,7 +11861,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11899,7 +11888,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11954,11 +11943,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11968,7 +11957,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -12023,7 +12012,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -12078,7 +12067,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12133,7 +12122,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12188,7 +12177,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12244,7 +12233,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12299,11 +12288,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12313,7 +12302,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12338,7 +12327,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12362,7 +12351,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12387,7 +12376,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12414,10 +12403,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12440,7 +12429,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12461,7 +12450,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12518,7 +12507,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12575,7 +12564,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12632,7 +12621,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12689,7 +12678,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12746,7 +12735,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12805,7 +12794,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12862,7 +12851,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12919,7 +12908,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12976,7 +12965,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13033,7 +13022,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13091,7 +13080,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13148,7 +13137,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13174,7 +13163,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13198,7 +13187,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13255,18 +13244,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13322,7 +13311,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13378,7 +13367,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13433,7 +13422,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13488,11 +13477,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13513,7 +13502,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13570,7 +13559,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13627,10 +13616,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13653,7 +13642,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13663,7 +13652,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13720,7 +13709,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13777,7 +13766,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13834,7 +13823,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13891,7 +13880,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13948,11 +13937,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13975,7 +13964,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -14032,7 +14021,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -14089,7 +14078,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14116,18 +14105,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14179,7 +14168,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14231,11 +14220,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14289,7 +14278,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14344,7 +14333,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14398,7 +14387,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14454,7 +14443,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14511,7 +14500,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14530,7 +14519,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14553,7 +14542,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14574,7 +14563,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14632,7 +14621,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14689,7 +14678,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
@@ -14739,688 +14728,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15442,16 +15431,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15463,7 +15452,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15476,7 +15465,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15497,24 +15486,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1123831.5395809037</v>
+        <v>1198753.6422196308</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15526,7 +15515,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15542,7 +15531,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15558,7 +15547,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15574,13 +15563,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>1137799.0942887787</v>
+        <v>1212721.1969275058</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15588,7 +15577,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15602,13 +15591,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>25.944000372833866</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15616,10 +15605,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15629,13 +15618,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15645,7 +15634,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15655,13 +15644,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>27.58482505879492</v>
+        <v>29.364505497446864</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15669,10 +15658,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15690,7 +15679,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15704,15 +15693,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>84898.689800926528</v>
+        <v>85293.56742790759</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15726,15 +15715,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>80169.794983261658</v>
+        <v>80917.294856442531</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15748,15 +15737,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>75704.301712180983</v>
+        <v>76765.561628298354</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15770,15 +15759,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>71487.538404276973</v>
+        <v>72826.846999308487</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15792,15 +15781,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>67505.650689869421</v>
+        <v>69090.221335729104</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15814,15 +15803,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>63745.555893837176</v>
+        <v>65545.315785336206</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15836,15 +15825,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>60194.900051887496</v>
+        <v>62182.293504648602</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15858,15 +15847,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>56842.017321038562</v>
+        <v>58991.82236243505</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15880,15 +15869,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>53675.89165095616</v>
+        <v>55965.049043759282</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15902,15 +15891,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>50686.120590213846</v>
+        <v>53093.57448270388</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15932,7 +15921,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15954,7 +15943,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15976,7 +15965,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15998,7 +15987,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -16020,7 +16009,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -16042,7 +16031,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -16064,7 +16053,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -16086,7 +16075,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -16108,7 +16097,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -16130,7 +16119,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16152,7 +16141,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16174,7 +16163,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16196,7 +16185,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16218,7 +16207,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16240,7 +16229,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16262,7 +16251,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16284,7 +16273,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16306,7 +16295,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16328,7 +16317,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16350,13 +16339,13 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1146132.3123125082</v>
+        <v>1222541.1331333423</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16364,30 +16353,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>530881.02354659536</v>
+        <v>593169.53489508992</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>1195791.484645044</v>
+        <v>1273841.0823216592</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16397,10 +16386,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>1195791.484645044</v>
+        <v>1273841.0823216592</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16424,141 +16413,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1123831.5395809035</v>
+        <v>1198753.6422196308</v>
       </c>
       <c r="C56" s="124">
-        <v>1123831.5395809035</v>
+        <v>1198753.6422196308</v>
       </c>
       <c r="D56" s="124">
-        <v>1160092.2280044998</v>
+        <v>1236766.7235655249</v>
       </c>
       <c r="E56" s="124">
-        <v>1178626.8748961668</v>
+        <v>1256185.5299687099</v>
       </c>
       <c r="F56" s="124">
-        <v>1197438.9082228532</v>
+        <v>1275887.2001585364</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>1123831.5395809032</v>
+        <v>1198753.642219631</v>
       </c>
       <c r="C57" s="124">
-        <v>1123831.5395809032</v>
+        <v>1198753.642219631</v>
       </c>
       <c r="D57" s="124">
-        <v>1196386.3067920422</v>
+        <v>1274461.5714570428</v>
       </c>
       <c r="E57" s="124">
-        <v>1235338.4520648608</v>
+        <v>1315088.6439278601</v>
       </c>
       <c r="F57" s="124">
-        <v>1276213.0261731616</v>
+        <v>1357709.2969660095</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>1123831.539580903</v>
+        <v>1198753.642219631</v>
       </c>
       <c r="C58" s="124">
-        <v>1123831.539580903</v>
+        <v>1198753.642219631</v>
       </c>
       <c r="D58" s="124">
-        <v>1241310.2926966697</v>
+        <v>1322187.6631956201</v>
       </c>
       <c r="E58" s="124">
-        <v>1307360.3393357873</v>
+        <v>1391606.636241809</v>
       </c>
       <c r="F58" s="124">
-        <v>1378905.0786722163</v>
+        <v>1466817.627889662</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>1123831.5395809032</v>
+        <v>1198753.642219631</v>
       </c>
       <c r="C59" s="124">
-        <v>1123831.5395809032</v>
+        <v>1198753.642219631</v>
       </c>
       <c r="D59" s="124">
-        <v>1287080.6299842198</v>
+        <v>1371942.8924623169</v>
       </c>
       <c r="E59" s="124">
-        <v>1382748.9174843063</v>
+        <v>1473562.967952199</v>
       </c>
       <c r="F59" s="124">
-        <v>1489435.2104115037</v>
+        <v>1586983.4089888346</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>1123831.539580903</v>
+        <v>1198753.642219631</v>
       </c>
       <c r="C60" s="124">
-        <v>1123831.539580903</v>
+        <v>1198753.642219631</v>
       </c>
       <c r="D60" s="124">
-        <v>1329649.5834580972</v>
+        <v>1419298.3872991232</v>
       </c>
       <c r="E60" s="124">
-        <v>1454863.9192204799</v>
+        <v>1553791.0049023672</v>
       </c>
       <c r="F60" s="124">
-        <v>1598311.1503303675</v>
+        <v>1708114.802828433</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>1123831.539580903</v>
+        <v>1198753.6422196312</v>
       </c>
       <c r="C61" s="124">
-        <v>1123831.539580903</v>
+        <v>1198753.6422196312</v>
       </c>
       <c r="D61" s="124">
-        <v>1367201.3221116753</v>
+        <v>1462049.7984249359</v>
       </c>
       <c r="E61" s="124">
-        <v>1520360.3795517492</v>
+        <v>1628360.6634412652</v>
       </c>
       <c r="F61" s="124">
-        <v>1700274.4329474259</v>
+        <v>1824209.7782913516</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16568,7 +16557,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16591,193 +16580,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>25.944000372833866</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>25.944000372833859</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833859</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>26.770813576239547</v>
+        <v>28.519139050751839</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>27.19343905404267</v>
+        <v>28.961925060244258</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>27.622389474280428</v>
+        <v>29.411160906287723</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833855</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833855</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>27.598388143948487</v>
+        <v>29.378653839136131</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>28.486571722713226</v>
+        <v>30.3050289686478</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>29.418590363990184</v>
+        <v>31.276861556547125</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>28.62274113641363</v>
+        <v>30.466900215912805</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>30.128808809724717</v>
+        <v>32.049785869128989</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>31.760166009194865</v>
+        <v>33.764740649061217</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833855</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833855</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>29.666392562762493</v>
+        <v>31.601414817941482</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>31.847812902283941</v>
+        <v>33.918547332486945</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>34.28046488572538</v>
+        <v>36.504750801369831</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>30.637046301494614</v>
+        <v>32.681210874968407</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>33.492173177592214</v>
+        <v>35.747900362380122</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>36.763045017864876</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>39.26677877512283</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>27.652367929592796</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>25.944000372833848</v>
+        <v>27.652367929592796</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>31.4932979249308</v>
+        <v>33.656024997913875</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>34.985618021926463</v>
+        <v>37.448231518070287</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>39.088003312796452</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>41.913966755683525</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16794,7 +16783,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16809,14 +16798,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.760166009194865</v>
+        <v>33.764740649061217</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16831,7 +16820,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.486571722713226</v>
+        <v>30.3050289686478</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16839,7 +16828,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16854,7 +16843,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>27.598388143948487</v>
+        <v>29.378653839136131</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16862,7 +16851,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16877,7 +16866,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>25.944000372833855</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16885,7 +16874,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16900,21 +16889,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>25.944000372833848</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16922,23 +16911,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16972,16 +16961,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>445</v>
       </c>
@@ -16993,7 +16982,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>444</v>
       </c>
@@ -17006,7 +16995,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>442</v>
       </c>
@@ -17027,24 +17016,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>443</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>831774.19472000003</v>
+        <v>887225.80770133343</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17054,13 +17043,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>446</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>18.966046049999999</v>
+        <v>20.230449119999999</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17068,10 +17057,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -17081,13 +17070,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -17097,7 +17086,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -17107,13 +17096,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>18.620540752123823</v>
+        <v>19.835907923479517</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17121,10 +17110,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17142,7 +17131,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17156,15 +17145,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>62835.520142354144</v>
+        <v>63127.778375574402</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17178,15 +17167,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>59335.553696897732</v>
+        <v>59888.795960680603</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17200,15 +17189,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>56030.536940591148</v>
+        <v>56816.000402887577</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17222,15 +17211,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>52909.611088959806</v>
+        <v>53900.86492806219</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17244,15 +17233,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>49962.522196658472</v>
+        <v>51135.30025681897</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17266,15 +17255,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>47179.587467662597</v>
+        <v>48511.632157384694</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17288,15 +17277,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>44551.663441996869</v>
+        <v>46022.580150188405</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17310,15 +17299,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>42070.115954477107</v>
+        <v>43661.237305083967</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17332,15 +17321,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>39726.791766763716</v>
+        <v>41421.051075143871</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17354,15 +17343,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>37513.991779522315</v>
+        <v>39295.805113839466</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17384,7 +17373,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17406,7 +17395,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17428,7 +17417,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17450,7 +17439,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17472,7 +17461,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17494,7 +17483,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17516,7 +17505,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17538,7 +17527,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17560,7 +17549,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17582,7 +17571,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17604,7 +17593,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17626,7 +17615,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17648,7 +17637,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17670,7 +17659,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17692,7 +17681,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17714,7 +17703,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17736,7 +17725,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17758,7 +17747,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17780,7 +17769,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17802,13 +17791,13 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>848279.52192178112</v>
+        <v>904831.4900498999</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17816,30 +17805,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>392917.55062975816</v>
+        <v>439018.74510817835</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>885033.44510564208</v>
+        <v>942799.79083384247</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17849,10 +17838,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>885033.44510564208</v>
+        <v>942799.79083384247</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17876,141 +17865,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>831774.1947199998</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="C51" s="124">
-        <v>831774.1947199998</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="D51" s="124">
-        <v>858611.58435650798</v>
+        <v>915360.184617911</v>
       </c>
       <c r="E51" s="124">
-        <v>872329.51311163534</v>
+        <v>929732.50065422419</v>
       </c>
       <c r="F51" s="124">
-        <v>886252.74210126267</v>
+        <v>944314.17084199353</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>831774.1947199998</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="C52" s="124">
-        <v>831774.1947199998</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="D52" s="124">
-        <v>885473.6869878954</v>
+        <v>943259.02945879591</v>
       </c>
       <c r="E52" s="124">
-        <v>914303.08723679534</v>
+        <v>973328.08278047689</v>
       </c>
       <c r="F52" s="124">
-        <v>944555.32235037233</v>
+        <v>1004872.6320395834</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>831774.1947199998</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="C53" s="124">
-        <v>831774.1947199998</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="D53" s="124">
-        <v>918722.98715735739</v>
+        <v>978582.23416062468</v>
       </c>
       <c r="E53" s="124">
-        <v>967608.18250875163</v>
+        <v>1029960.8513022257</v>
       </c>
       <c r="F53" s="124">
-        <v>1020560.1293549866</v>
+        <v>1085626.2778441031</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>831774.19471999968</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="C54" s="124">
-        <v>831774.19471999968</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="D54" s="124">
-        <v>952598.69192144671</v>
+        <v>1015407.2513441156</v>
       </c>
       <c r="E54" s="124">
-        <v>1023405.045002889</v>
+        <v>1090618.6629134184</v>
       </c>
       <c r="F54" s="124">
-        <v>1102366.0834342125</v>
+        <v>1174563.8029859385</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>831774.19471999968</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="C55" s="124">
-        <v>831774.19471999968</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="D55" s="124">
-        <v>984104.97711523261</v>
+        <v>1050456.1685493938</v>
       </c>
       <c r="E55" s="124">
-        <v>1076779.0564839209</v>
+        <v>1149997.322861935</v>
       </c>
       <c r="F55" s="124">
-        <v>1182947.7311820304</v>
+        <v>1264216.0008623353</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>831774.19471999945</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="C56" s="124">
-        <v>831774.19471999945</v>
+        <v>887225.80770133354</v>
       </c>
       <c r="D56" s="124">
-        <v>1011897.9034381259</v>
+        <v>1082097.4949492363</v>
       </c>
       <c r="E56" s="124">
-        <v>1125254.5295689418</v>
+        <v>1205188.0836630308</v>
       </c>
       <c r="F56" s="124">
-        <v>1258413.1584305295</v>
+        <v>1350140.6268634161</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -18020,7 +18009,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -18043,193 +18032,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>18.966046049999999</v>
+        <v>20.230449119999999</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>18.966046049999999</v>
+        <v>20.230449119999999</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>18.966046049999999</v>
+        <v>20.230449119999999</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>18.966046049999999</v>
+        <v>20.230449119999999</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>18.966046049999999</v>
+        <v>20.230449119999999</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>18.966046049999996</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999996</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>19.577989977737676</v>
+        <v>20.871966843890789</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>19.890785048962446</v>
+        <v>21.199683199507746</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>20.208261359069489</v>
+        <v>21.532173231084457</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999996</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999996</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>20.19049740913043</v>
+        <v>21.50811398496932</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>20.847862997273708</v>
+        <v>22.1937460394368</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>21.537671947733724</v>
+        <v>22.913022229624577</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999996</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999996</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>20.948645187875321</v>
+        <v>22.313550762475963</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>22.063321348885459</v>
+        <v>23.485081719890381</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>23.270727239448004</v>
+        <v>24.754360148925478</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999989</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999989</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>21.721076192119451</v>
+        <v>23.153231743357132</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>23.335596769578888</v>
+        <v>24.868196098303354</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>25.136059804559707</v>
+        <v>26.782306204622614</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999989</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999989</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>22.439479888270338</v>
+        <v>23.952414240166512</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>24.552626542861585</v>
+        <v>26.222143366828512</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>26.973475838468371</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>28.826548168608817</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999985</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.966046049999985</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>23.073211884105692</v>
+        <v>24.673897134673126</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>25.657960250810454</v>
+        <v>27.480598507097064</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>28.694232237817562</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>30.785794348534022</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18246,7 +18235,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18261,14 +18250,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>23.270727239448004</v>
+        <v>24.754360148925478</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18283,7 +18272,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>20.847862997273708</v>
+        <v>22.1937460394368</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18291,7 +18280,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18306,7 +18295,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>20.19049740913043</v>
+        <v>21.50811398496932</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18314,7 +18303,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18329,7 +18318,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>18.966046049999996</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18337,7 +18326,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18352,21 +18341,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>18.966046049999996</v>
+        <v>20.230449120000003</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18374,23 +18363,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18420,7 +18409,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18430,7 +18419,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18443,7 +18432,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18455,7 +18444,7 @@
         <v>-17.239999999999998</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18475,7 +18464,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18484,7 +18473,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18501,10 +18490,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>28.985840894032091</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>30.767659943749511</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18529,7 +18518,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18551,7 +18540,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18573,7 +18562,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18584,7 +18573,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>449</v>
       </c>
@@ -18598,7 +18587,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18617,7 +18606,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18635,7 +18624,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18646,7 +18635,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18655,7 +18644,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18663,7 +18652,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18675,18 +18664,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18701,13 +18690,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>25.944000372833866</v>
+        <v>27.652367929592781</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18716,7 +18705,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18725,7 +18714,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18737,7 +18726,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18748,13 +18737,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>27.598388143948487</v>
+        <v>29.378653839136131</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18763,7 +18752,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18774,7 +18763,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18783,7 +18772,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18795,7 +18784,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18806,13 +18795,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>25.944000372833855</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18821,7 +18810,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18832,7 +18821,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18841,7 +18830,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18853,7 +18842,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18864,13 +18853,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>28.486571722713226</v>
+        <v>30.3050289686478</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18879,7 +18868,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18891,20 +18880,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>27.445147305478507</v>
+        <v>29.218671683129795</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18913,12 +18902,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18928,12 +18917,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18942,7 +18931,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18954,7 +18943,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18965,13 +18954,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>25.944000372833848</v>
+        <v>27.652367929592785</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18980,7 +18969,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18991,7 +18980,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -19000,7 +18989,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -19012,7 +19001,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -19023,13 +19012,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>31.760166009194865</v>
+        <v>33.764740649061217</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19038,7 +19027,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -19049,13 +19038,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>27.585840894032092</v>
+        <v>29.367659943749512</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19069,7 +19058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>350</v>
       </c>
@@ -19078,7 +19067,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -19086,7 +19075,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -19099,7 +19088,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -19111,13 +19100,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>27.58482505879492</v>
+        <v>29.364505497446864</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19127,7 +19116,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>351</v>
       </c>
@@ -19135,7 +19124,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -19145,7 +19134,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -19157,7 +19146,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19167,7 +19156,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19180,10 +19169,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>1.1545307705991601E-2</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>1.0844821210139093E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19192,12 +19181,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19207,7 +19196,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19220,49 +19209,49 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.2244897959183665</v>
+        <v>2.3201630471108023</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.053149013860095</v>
+        <v>11.486365088891507</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.277638809778461</v>
+        <v>13.80652813600231</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19273,18 +19262,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.55492968813451693</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.52987305892103143</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19297,24 +19286,24 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2400573713891494</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.26346001995218948</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>415</v>
       </c>
@@ -19323,7 +19312,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
@@ -19335,23 +19324,23 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>15.289255377213328</v>
+        <v>16.276815864920152</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>18.159816530624241</v>
+        <v>19.147377018331063</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19362,58 +19351,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.34169791668185379</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.34801148423109862</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.6079357821470319</v>
+        <v>3.6407360358207437</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>21.898529897335333</v>
+        <v>23.639808273484963</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>25.506465679482364</v>
+        <v>27.280544309305707</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19423,18 +19412,18 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>7.5378351616592565E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>7.1068503191655141E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>423</v>
       </c>
@@ -19443,7 +19432,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
@@ -19453,23 +19442,23 @@
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>19.772438160850257</v>
+        <v>21.049575483206976</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>23.150082537164366</v>
+        <v>24.427219859521085</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19479,19 +19468,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.16076746951188714</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.16813787783196477</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>325</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>326</v>
       </c>
@@ -19499,7 +19488,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>326</v>
       </c>
@@ -19507,7 +19496,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>326</v>
       </c>

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D993BF1B-E2B9-459B-B882-4435E967E0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D7479A-9575-4455-8714-E6E02A14F901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3869,29 +3869,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4309,7 +4309,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>17.239999999999998</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="D12" s="50">
         <v>25.72</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>819416.40668415988</v>
+        <v>836527.19011840003</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4361,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0837740599999999</v>
+        <v>1.0843026500000001</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4373,13 +4373,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E25" s="329">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.922701545375611</v>
+        <v>0.92225173479009748</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>29.367659943749512</v>
+        <v>29.381983456317876</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.26346001995218948</v>
+        <v>0.25442291516277704</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4494,11 +4494,11 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>13.80652813600231</v>
+        <v>13.81213039014958</v>
       </c>
       <c r="D29" s="340">
         <f>D144</f>
-        <v>12.739304847361185</v>
+        <v>12.738261213462476</v>
       </c>
       <c r="E29" s="336" t="s">
         <v>426</v>
@@ -4513,11 +4513,11 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>19.147377018331063</v>
+        <v>19.155315722914974</v>
       </c>
       <c r="D30" s="341">
         <f>D152</f>
-        <v>17.667314364703532</v>
+        <v>17.666023155910366</v>
       </c>
       <c r="E30" s="337" t="s">
         <v>439</v>
@@ -4532,11 +4532,11 @@
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>27.280544309305707</v>
+        <v>27.292074172140115</v>
       </c>
       <c r="D31" s="341">
         <f>D160</f>
-        <v>25.171800392884208</v>
+        <v>25.170162751276234</v>
       </c>
       <c r="E31" s="337" t="s">
         <v>438</v>
@@ -4551,11 +4551,11 @@
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>24.427219859521085</v>
+        <v>24.437486386018939</v>
       </c>
       <c r="D32" s="341">
         <f>D168</f>
-        <v>22.539033513609919</v>
+        <v>22.537514213415356</v>
       </c>
       <c r="E32" s="337" t="s">
         <v>440</v>
@@ -4579,22 +4579,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4606,13 +4606,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4632,13 +4632,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4667,13 +4667,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4689,13 +4689,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4759,13 +4759,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4781,7 +4781,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4803,22 +4803,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.1189118949020127</v>
+        <v>0.11653641683529069</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>8.1206496519721574E-2</v>
+        <v>7.954545454545453E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4887,22 +4887,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4946,22 +4946,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>27.333880908142653</v>
+        <v>27.347212484014882</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4998,13 +4998,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5017,13 +5017,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="C97" s="245">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0951997362493384</v>
+        <v>2.0962216297135394</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C105" s="245">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.2970959963143938</v>
+        <v>2.2982163608050259</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C109" s="245">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11659076138507206</v>
+        <v>0.11664762629154581</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5154,13 +5154,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C114" s="245">
         <f>BS!D47</f>
-        <v>-0.45424610691085376</v>
+        <v>-0.45446765673245781</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5199,13 +5199,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>33.76 HKD</v>
+        <v>33.78 HKD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>30.31 HKD</v>
+        <v>30.32 HKD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>29.38 HKD</v>
+        <v>29.39 HKD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>27.65 HKD</v>
+        <v>27.67 HKD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>27.65 HKD</v>
+        <v>27.67 HKD</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>29.367659943749512</v>
+        <v>29.381983456317876</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
@@ -5348,13 +5348,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5367,22 +5367,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>11.486365088891507</v>
+        <v>11.491967343038779</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5468,11 +5468,11 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>13.80652813600231</v>
+        <v>13.81213039014958</v>
       </c>
       <c r="D144" s="330">
         <f>IF($D$11="","",C144*$E$25)</f>
-        <v>12.739304847361185</v>
+        <v>12.738261213462476</v>
       </c>
     </row>
     <row r="145" spans="2:4">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.52987305892103143</v>
+        <v>0.52991157282883772</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>16.276815864920152</v>
+        <v>16.284754569504063</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5537,11 +5537,11 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>19.147377018331063</v>
+        <v>19.155315722914974</v>
       </c>
       <c r="D152" s="330">
         <f>IF($D$11="","",C152*$E$25)</f>
-        <v>17.667314364703532</v>
+        <v>17.666023155910366</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34801148423109862</v>
+        <v>0.34805913455798054</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>23.639808273484963</v>
+        <v>23.651338136319371</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5606,11 +5606,11 @@
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>27.280544309305707</v>
+        <v>27.292074172140115</v>
       </c>
       <c r="D160" s="330">
         <f>IF($D$11="","",C160*$E$25)</f>
-        <v>25.171800392884208</v>
+        <v>25.170162751276234</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>7.1068503191655141E-2</v>
+        <v>7.112893815643262E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>21.049575483206976</v>
+        <v>21.05984200970483</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5675,11 +5675,11 @@
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>24.427219859521085</v>
+        <v>24.437486386018939</v>
       </c>
       <c r="D168" s="330">
         <f>IF($D$11="","",C168*$E$25)</f>
-        <v>22.539033513609919</v>
+        <v>22.537514213415356</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.16813787783196477</v>
+        <v>0.16819395158877859</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5715,13 +5715,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5758,13 +5758,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5772,22 +5772,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5811,6 +5811,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5827,17 +5838,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9287,11 +9287,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.045527358970478</v>
+        <v>17.053840987833937</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45424610691085376</v>
+        <v>-0.45446765673245781</v>
       </c>
       <c r="F47" s="275"/>
     </row>
@@ -9697,11 +9697,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-99584.747051219994</v>
+        <v>-99633.317600550014</v>
       </c>
       <c r="D86" s="245">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.0951997362493384</v>
+        <v>-2.0962216297135394</v>
       </c>
       <c r="E86" s="262" t="str">
         <f>Market_currency</f>
@@ -9714,11 +9714,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>109180.86700165375</v>
+        <v>109234.11787433882</v>
       </c>
       <c r="D87" s="245">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.2970959963143933</v>
+        <v>2.2982163608050259</v>
       </c>
       <c r="E87" s="262" t="str">
         <f>Market_currency</f>
@@ -9731,11 +9731,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>5541.5535235919988</v>
+        <v>5544.2563099800009</v>
       </c>
       <c r="D88" s="245">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11659076138507206</v>
+        <v>0.11664762629154581</v>
       </c>
       <c r="E88" s="262" t="str">
         <f>Market_currency</f>
@@ -9748,11 +9748,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>15137.673474025756</v>
+        <v>15145.056583768803</v>
       </c>
       <c r="D89" s="264">
         <f>SUM(D86:D88)</f>
-        <v>0.31848702145012697</v>
+        <v>0.31864235738303226</v>
       </c>
       <c r="E89" s="262" t="str">
         <f>Market_currency</f>
@@ -13429,20 +13429,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.1206496519721574E-2</v>
+        <v>7.954545454545453E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.1206496519721574E-2</v>
+        <v>7.954545454545453E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.2505800464037123E-2</v>
+        <v>7.1022727272727265E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>8.4106728538283063E-2</v>
+        <v>8.2386363636363633E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14571,50 +14571,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0500410681106986</v>
+        <v>2.0510409363011157</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="290"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2232431166363904</v>
+        <v>3.2248151916120764</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.8139557023022825</v>
+        <v>2.815328155195906</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>3.2085276639884754</v>
+        <v>3.2100925617845237</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.7337182180759729</v>
+        <v>1.734563805866562</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.63756559662202394</v>
+        <v>0.6378765570068099</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3678011880301386</v>
+        <v>1.3684683068113181</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1591957982944392</v>
+        <v>1.1597611737999396</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>6.8259362330267557</v>
+        <v>6.8292654524338126</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4205637547540864</v>
+        <v>6.4236952615140162</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>6.4667832402675689</v>
+        <v>6.4699372896946006</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14628,50 +14628,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1189118949020127</v>
+        <v>0.11653641683529069</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18696305780953543</v>
+        <v>0.18322813588704978</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.16322248853261501</v>
+        <v>0.15996182699976738</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18610949327079326</v>
+        <v>0.18239162282866611</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.100563701744546</v>
+        <v>9.8554761696963741E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6981763145129E-2</v>
+        <v>3.6242986193568742E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.9338816011028934E-2</v>
+        <v>7.7753881068824887E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.7238735399909474E-2</v>
+        <v>6.5895521238632931E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.39593597639366335</v>
+        <v>0.38802644616101206</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.37242249157506307</v>
+        <v>0.36498268531329636</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.37510343621041586</v>
+        <v>0.3676100732781023</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14685,43 +14685,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16839057513914837</v>
+        <v>0.16494622246584759</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15143704591190824</v>
+        <v>0.14833946997280101</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17289988197003323</v>
+        <v>0.16936329347519163</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5801308622197855E-2</v>
+        <v>8.4046281854925617E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0455415825740285E-2</v>
+        <v>2.9832464138395593E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4498702371637623E-2</v>
+        <v>7.2974865277672288E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4283996354375497E-2</v>
+        <v>6.2969096428945076E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5785443672589876E-2</v>
+        <v>8.4030741415650534E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2209928331111381E-2</v>
+        <v>7.0732907069793183E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2898623515976906E-2</v>
+        <v>5.1816606216786465E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="C11" s="229">
         <f>Exchange_Rate</f>
-        <v>1.0837740599999999</v>
+        <v>1.0843026500000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>29.364505497446864</v>
+        <v>29.378827471494578</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16586,23 +16586,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16613,23 +16613,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>28.519139050751839</v>
+        <v>28.533048713537866</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>28.961925060244258</v>
+        <v>28.976050683409294</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>29.411160906287723</v>
+        <v>29.425505635615774</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16640,23 +16640,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>29.378653839136131</v>
+        <v>29.392982713765992</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>30.3050289686478</v>
+        <v>30.319809664969821</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>31.276861556547125</v>
+        <v>31.292116245564305</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16667,23 +16667,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>30.466900215912805</v>
+        <v>30.481759861829353</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>32.049785869128989</v>
+        <v>32.065417537147106</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>33.764740649061217</v>
+        <v>33.781208753363046</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16694,23 +16694,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>31.601414817941482</v>
+        <v>31.616827801583682</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>33.918547332486945</v>
+        <v>33.935090453047039</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>36.504750801369831</v>
+        <v>36.522555293042302</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16721,23 +16721,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>32.681210874968407</v>
+        <v>32.697150508416001</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>35.747900362380122</v>
+        <v>35.765335714775034</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.26677877512283</v>
+        <v>39.285930392935818</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16747,23 +16747,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592796</v>
+        <v>27.665854841397927</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>27.652367929592796</v>
+        <v>27.665854841397927</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>33.656024997913875</v>
+        <v>33.67244007824312</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>37.448231518070287</v>
+        <v>37.466496174356813</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>41.913966755683525</v>
+        <v>41.934409488634152</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>33.764740649061217</v>
+        <v>33.781208753363046</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>30.3050289686478</v>
+        <v>30.319809664969821</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>29.378653839136131</v>
+        <v>29.392982713765992</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>20.230449119999999</v>
+        <v>20.240316133333337</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18038,23 +18038,23 @@
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>20.230449119999999</v>
+        <v>20.240316133333337</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>20.230449119999999</v>
+        <v>20.240316133333337</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>20.230449119999999</v>
+        <v>20.240316133333337</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>20.230449119999999</v>
+        <v>20.240316133333337</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>20.230449119999999</v>
+        <v>20.240316133333337</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -18065,23 +18065,23 @@
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>20.871966843890789</v>
+        <v>20.882146745183146</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>21.199683199507746</v>
+        <v>21.210022938163636</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>21.532173231084457</v>
+        <v>21.542675135372722</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -18092,23 +18092,23 @@
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>21.50811398496932</v>
+        <v>21.518604154821993</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>22.1937460394368</v>
+        <v>22.20457061316667</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>22.913022229624577</v>
+        <v>22.924197616513208</v>
       </c>
       <c r="H62" s="121"/>
     </row>
@@ -18119,23 +18119,23 @@
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>22.313550762475963</v>
+        <v>22.324433768660427</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>23.485081719890381</v>
+        <v>23.496536117817495</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>24.754360148925478</v>
+        <v>24.766433613048736</v>
       </c>
       <c r="H63" s="121"/>
     </row>
@@ -18146,23 +18146,23 @@
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>23.153231743357132</v>
+        <v>23.164524287826435</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>24.868196098303354</v>
+        <v>24.880325083726394</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>26.782306204622614</v>
+        <v>26.795368760517992</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -18173,23 +18173,23 @@
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>23.952414240166512</v>
+        <v>23.964096570562216</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>26.222143366828512</v>
+        <v>26.23493271404935</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>28.826548168608817</v>
+        <v>28.840607764292859</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18199,23 +18199,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>24.673897134673126</v>
+        <v>24.685931354505275</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>27.480598507097064</v>
+        <v>27.494001641662649</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>30.785794348534022</v>
+        <v>30.800809528944136</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18250,7 +18250,7 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>24.754360148925478</v>
+        <v>24.766433613048736</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>22.1937460394368</v>
+        <v>22.20457061316667</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>21.50811398496932</v>
+        <v>21.518604154821993</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>20.230449120000003</v>
+        <v>20.240316133333341</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-17.239999999999998</v>
+        <v>-17.600000000000001</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>30.767659943749511</v>
+        <v>30.781983456317874</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>17.239999999999998</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18696,7 +18696,7 @@
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.652367929592781</v>
+        <v>27.665854841397916</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>29.378653839136131</v>
+        <v>29.392982713765992</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18859,7 +18859,7 @@
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>30.3050289686478</v>
+        <v>30.319809664969821</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18886,7 +18886,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>29.218671683129795</v>
+        <v>29.232922529533145</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>27.652367929592785</v>
+        <v>27.66585484139792</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19018,7 +19018,7 @@
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>33.764740649061217</v>
+        <v>33.781208753363046</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>29.367659943749512</v>
+        <v>29.381983456317876</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19106,7 +19106,7 @@
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>29.364505497446864</v>
+        <v>29.378827471494578</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>1.0844821210139093E-2</v>
+        <v>1.08448212101391E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>11.486365088891507</v>
+        <v>11.491967343038779</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>13.80652813600231</v>
+        <v>13.81213039014958</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19262,7 +19262,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.52987305892103143</v>
+        <v>0.52991157282883772</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>17.239999999999998</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19292,7 +19292,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.26346001995218948</v>
+        <v>0.25442291516277704</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>16.276815864920152</v>
+        <v>16.284754569504063</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>19.147377018331063</v>
+        <v>19.155315722914974</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.34801148423109862</v>
+        <v>0.34805913455798054</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19390,7 +19390,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>23.639808273484963</v>
+        <v>23.651338136319371</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>27.280544309305707</v>
+        <v>27.292074172140115</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>7.1068503191655141E-2</v>
+        <v>7.112893815643262E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>21.049575483206976</v>
+        <v>21.05984200970483</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>24.427219859521085</v>
+        <v>24.437486386018939</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.16813787783196477</v>
+        <v>0.16819395158877859</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3D8127-75E9-4ED5-B9D4-E431881432ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823C8552-D15F-4906-B6DB-10D216CDC523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3868,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4308,7 +4308,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>17.600000000000001</v>
+        <v>17.86</v>
       </c>
       <c r="D12" s="50">
         <v>25.72</v>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>836527.19011840003</v>
+        <v>848884.97815423994</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4360,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0843026499999999</v>
+        <v>1.0877953499999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4372,13 +4372,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="E25" s="302">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.9222517347900977</v>
+        <v>0.91929056324794922</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -4454,14 +4454,14 @@
       </c>
       <c r="C26" s="307">
         <f>C127</f>
-        <v>29.381983456317865</v>
+        <v>29.476627192195373</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2544229151627766</v>
+        <v>0.24912793382512621</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4493,11 +4493,11 @@
       </c>
       <c r="C29" s="313">
         <f>C144</f>
-        <v>13.812130390149576</v>
+        <v>13.849147725059744</v>
       </c>
       <c r="D29" s="313">
         <f>D144</f>
-        <v>12.738261213462476</v>
+        <v>12.731390812674226</v>
       </c>
       <c r="E29" s="309" t="s">
         <v>426</v>
@@ -4512,11 +4512,11 @@
       </c>
       <c r="C30" s="314">
         <f>C152</f>
-        <v>19.155315722914967</v>
+        <v>19.207771337853202</v>
       </c>
       <c r="D30" s="314">
         <f>D152</f>
-        <v>17.666023155910363</v>
+        <v>17.657522931912887</v>
       </c>
       <c r="E30" s="310" t="s">
         <v>439</v>
@@ -4531,11 +4531,11 @@
       </c>
       <c r="C31" s="314">
         <f>C160</f>
-        <v>27.292074172140108</v>
+        <v>27.368258647672583</v>
       </c>
       <c r="D31" s="314">
         <f>D160</f>
-        <v>25.170162751276234</v>
+        <v>25.159381907334485</v>
       </c>
       <c r="E31" s="310" t="s">
         <v>438</v>
@@ -4550,11 +4550,11 @@
       </c>
       <c r="C32" s="314">
         <f>C168</f>
-        <v>24.437486386018929</v>
+        <v>24.505323267342881</v>
       </c>
       <c r="D32" s="314">
         <f>D168</f>
-        <v>22.537514213415353</v>
+        <v>22.527512429008713</v>
       </c>
       <c r="E32" s="310" t="s">
         <v>440</v>
@@ -4578,22 +4578,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4605,13 +4605,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4631,13 +4631,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4666,13 +4666,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4758,13 +4758,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4780,7 +4780,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4802,22 +4802,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11653641683529066</v>
+        <v>0.11520983449112923</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.954545454545453E-2</v>
+        <v>7.8387458006718924E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4886,22 +4886,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4945,22 +4945,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C87" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>27.347212484014879</v>
+        <v>27.435301920154245</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4997,13 +4997,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5016,13 +5016,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="C97" s="223">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.096221629713539</v>
+        <v>2.1029738711528645</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C105" s="223">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.2982163608050254</v>
+        <v>2.305619257296502</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C109" s="223">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11664762629154578</v>
+        <v>0.11702336563364597</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5153,13 +5153,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="C113" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C114" s="223">
         <f>BS!D47</f>
-        <v>-0.4544676567324577</v>
+        <v>-0.45593156460418477</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5198,13 +5198,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="E121" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>33.78 HKD</v>
+        <v>33.89 HKD</v>
       </c>
       <c r="F121" s="232">
         <f>DCF!F74</f>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="E122" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>30.32 HKD</v>
+        <v>30.42 HKD</v>
       </c>
       <c r="F122" s="221">
         <f>DCF!F75</f>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="E123" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>29.39 HKD</v>
+        <v>29.49 HKD</v>
       </c>
       <c r="F123" s="221">
         <f>DCF!F76</f>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E124" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>27.67 HKD</v>
+        <v>27.75 HKD</v>
       </c>
       <c r="F124" s="221">
         <f>DCF!F77</f>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="E125" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>27.67 HKD</v>
+        <v>27.75 HKD</v>
       </c>
       <c r="F125" s="221">
         <f>DCF!F78</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="C127" s="217">
         <f>Scenarios!C60</f>
-        <v>29.381983456317865</v>
+        <v>29.476627192195373</v>
       </c>
       <c r="D127" s="212" t="str">
         <f>Market_currency</f>
@@ -5347,13 +5347,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5366,22 +5366,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="C143" s="216">
         <f>Scenarios!C82</f>
-        <v>11.491967343038775</v>
+        <v>11.528984677948941</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5467,11 +5467,11 @@
       </c>
       <c r="C144" s="215">
         <f>Scenarios!C83</f>
-        <v>13.812130390149576</v>
+        <v>13.849147725059744</v>
       </c>
       <c r="D144" s="303">
         <f>IF($D$11="","",C144*$E$25)</f>
-        <v>12.738261213462476</v>
+        <v>12.731390812674226</v>
       </c>
     </row>
     <row r="145" spans="2:4">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.52991157282883772</v>
+        <v>0.53016511574544634</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C151" s="216">
         <f>Scenarios!C92</f>
-        <v>16.284754569504056</v>
+        <v>16.337210184442291</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5536,11 +5536,11 @@
       </c>
       <c r="C152" s="215">
         <f>Scenarios!C93</f>
-        <v>19.155315722914967</v>
+        <v>19.207771337853202</v>
       </c>
       <c r="D152" s="303">
         <f>IF($D$11="","",C152*$E$25)</f>
-        <v>17.666023155910363</v>
+        <v>17.657522931912887</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34805913455798054</v>
+        <v>0.3483728239118582</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C159" s="216">
         <f>Scenarios!C98</f>
-        <v>23.651338136319364</v>
+        <v>23.727522611851839</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5605,11 +5605,11 @@
       </c>
       <c r="C160" s="215">
         <f>Scenarios!C99</f>
-        <v>27.292074172140108</v>
+        <v>27.368258647672583</v>
       </c>
       <c r="D160" s="303">
         <f>IF($D$11="","",C160*$E$25)</f>
-        <v>25.170162751276234</v>
+        <v>25.159381907334485</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>7.1128938156432508E-2</v>
+        <v>7.1526790727299727E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C167" s="216">
         <f>Scenarios!C104</f>
-        <v>21.05984200970482</v>
+        <v>21.127678891028772</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5674,11 +5674,11 @@
       </c>
       <c r="C168" s="215">
         <f>Scenarios!C105</f>
-        <v>24.437486386018929</v>
+        <v>24.505323267342881</v>
       </c>
       <c r="D168" s="303">
         <f>IF($D$11="","",C168*$E$25)</f>
-        <v>22.537514213415353</v>
+        <v>22.527512429008713</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.16819395158877881</v>
+        <v>0.16856309366387923</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5714,13 +5714,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5757,13 +5757,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5771,22 +5771,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5810,6 +5810,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5826,17 +5837,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -9289,11 +9289,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.053840987833933</v>
+        <v>17.108773944438077</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.4544676567324577</v>
+        <v>-0.45593156460418477</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9699,11 +9699,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-99633.317600549999</v>
+        <v>-99954.251325449994</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.096221629713539</v>
+        <v>-2.1029738711528645</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9716,11 +9716,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>109234.1178743388</v>
+        <v>109585.97720392699</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.2982163608050254</v>
+        <v>2.305619257296502</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9733,11 +9733,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>5544.2563099799991</v>
+        <v>5562.1151836199997</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11664762629154576</v>
+        <v>0.11702336563364597</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9750,11 +9750,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>15145.056583768801</v>
+        <v>15193.841062096995</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>0.31864235738303226</v>
+        <v>0.31966875177728343</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13431,20 +13431,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.954545454545453E-2</v>
+        <v>7.8387458006718924E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.954545454545453E-2</v>
+        <v>7.8387458006718924E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1022727272727265E-2</v>
+        <v>6.9988801791713323E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>8.2386363636363633E-2</v>
+        <v>8.1187010078387453E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14573,50 +14573,50 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0510409363011153</v>
+        <v>2.0576476440115679</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="267"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2248151916120755</v>
+        <v>3.2352028006617664</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>2.8153281551959055</v>
+        <v>2.8243967456375616</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>3.2100925617845233</v>
+        <v>3.2204327470552543</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>1.7345638058665618</v>
+        <v>1.7401510937005906</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.63787655700680979</v>
+        <v>0.63993125220713754</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>1.3684683068113179</v>
+        <v>1.3728763466286142</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>1.1597611737999394</v>
+        <v>1.1634969369208088</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>6.8292654524338117</v>
+        <v>6.8512635315178345</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4236952615140153</v>
+        <v>6.4443869387315251</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4699372896945988</v>
+        <v>6.4907779193580204</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14630,50 +14630,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11653641683529066</v>
+        <v>0.11520983449112923</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18322813588704973</v>
+        <v>0.18114237405720976</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.15996182699976735</v>
+        <v>0.15814091520926998</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18239162282866608</v>
+        <v>0.18031538337375444</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.8554761696963727E-2</v>
+        <v>9.7432871987715039E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6242986193568735E-2</v>
+        <v>3.5830417256838609E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.7753881068824873E-2</v>
+        <v>7.6868776406977285E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.5895521238632918E-2</v>
+        <v>6.5145405202732862E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.38802644616101201</v>
+        <v>0.38360938026415647</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.36498268531329631</v>
+        <v>0.36082793609918956</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.36761007327810219</v>
+        <v>0.36342541541758233</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14687,43 +14687,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16494622246584759</v>
+        <v>0.16254498966399317</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14833946997280101</v>
+        <v>0.14617999280634367</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16936329347519163</v>
+        <v>0.16689775840780363</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4046281854925617E-2</v>
+        <v>8.2822763754014053E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9832464138395593E-2</v>
+        <v>2.9398172947131155E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2974865277672288E-2</v>
+        <v>7.1912521214279532E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2969096428945076E-2</v>
+        <v>6.2052413054279582E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4030741415650534E-2</v>
+        <v>8.2807449547337583E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0732907069793183E-2</v>
+        <v>6.9703200695876821E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1816606216786465E-2</v>
+        <v>5.1062277122925076E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0843026499999999</v>
+        <v>1.0877953499999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>29.378827471494571</v>
+        <v>29.473461041475876</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16588,23 +16588,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16615,23 +16615,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>28.533048713537859</v>
+        <v>28.624957904428221</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>28.976050683409287</v>
+        <v>29.069386849489806</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>29.425505635615767</v>
+        <v>29.520289562901674</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16642,23 +16642,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>29.392982713765985</v>
+        <v>29.487661879886598</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>30.319809664969814</v>
+        <v>30.417474278458347</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>31.292116245564298</v>
+        <v>31.392912803066839</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16669,23 +16669,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>30.481759861829346</v>
+        <v>30.579946140973284</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>32.065417537147098</v>
+        <v>32.168705013048772</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>33.781208753363039</v>
+        <v>33.890023047797229</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16696,23 +16696,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>31.616827801583678</v>
+        <v>31.718670303271367</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>33.935090453047032</v>
+        <v>34.044400423307977</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>36.522555293042295</v>
+        <v>36.640199872138368</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16723,23 +16723,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>32.697150508415994</v>
+        <v>32.80247289011519</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>35.765335714775027</v>
+        <v>35.880541177060849</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>39.285930392935811</v>
+        <v>39.412476213960417</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16749,23 +16749,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397923</v>
+        <v>27.754970671931538</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>27.665854841397923</v>
+        <v>27.754970671931538</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>33.67244007824312</v>
+        <v>33.780904012608012</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>37.466496174356806</v>
+        <v>37.587181327333397</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>41.934409488634145</v>
+        <v>42.069486454480305</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>33.781208753363039</v>
+        <v>33.890023047797229</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>30.319809664969814</v>
+        <v>30.417474278458347</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16845,7 +16845,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>29.392982713765985</v>
+        <v>29.487661879886598</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>20.240316133333334</v>
+        <v>20.3055132</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18040,23 +18040,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>20.240316133333334</v>
+        <v>20.3055132</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>20.240316133333334</v>
+        <v>20.3055132</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>20.240316133333334</v>
+        <v>20.3055132</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>20.240316133333334</v>
+        <v>20.3055132</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>20.240316133333334</v>
+        <v>20.3055132</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18067,23 +18067,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>20.882146745183142</v>
+        <v>20.949411243648491</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>21.210022938163632</v>
+        <v>21.278343574580155</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>21.542675135372718</v>
+        <v>21.612067293959914</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18094,23 +18094,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>21.51860415482199</v>
+        <v>21.587918777203061</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>22.204570613166666</v>
+        <v>22.276094835468076</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>22.924197616513204</v>
+        <v>22.998039864353508</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18121,23 +18121,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>22.324433768660423</v>
+        <v>22.396344088001431</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>23.496536117817492</v>
+        <v>23.572221953039513</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>24.766433613048729</v>
+        <v>24.846209976852965</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18148,23 +18148,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>23.164524287826431</v>
+        <v>23.239140663595769</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>24.88032508372639</v>
+        <v>24.960468308885833</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>26.795368760517984</v>
+        <v>26.88168062600117</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18175,23 +18175,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>23.964096570562212</v>
+        <v>24.041288487497951</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>26.234932714049343</v>
+        <v>26.319439331726947</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>28.840607764292852</v>
+        <v>28.933507648599459</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18201,23 +18201,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>24.685931354505271</v>
+        <v>24.765448408569355</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>27.494001641662646</v>
+        <v>27.582563907496667</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>30.800809528944129</v>
+        <v>30.900023514487504</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>24.766433613048729</v>
+        <v>24.846209976852965</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>22.204570613166666</v>
+        <v>22.276094835468076</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>21.51860415482199</v>
+        <v>21.587918777203061</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>20.240316133333337</v>
+        <v>20.305513200000004</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18443,7 +18443,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-17.600000000000001</v>
+        <v>-17.86</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>30.781983456317864</v>
+        <v>30.876627192195372</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>17.600000000000001</v>
+        <v>17.86</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.665854841397909</v>
+        <v>27.754970671931527</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>29.392982713765985</v>
+        <v>29.487661879886598</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18803,7 +18803,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>30.319809664969814</v>
+        <v>30.417474278458347</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>29.232922529533134</v>
+        <v>29.327086118009934</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>27.665854841397913</v>
+        <v>27.754970671931531</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>33.781208753363039</v>
+        <v>33.890023047797229</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>29.381983456317865</v>
+        <v>29.476627192195373</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19108,7 +19108,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>29.378827471494571</v>
+        <v>29.473461041475876</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="F72" s="293">
         <f>BS!D89/C60</f>
-        <v>1.0844821210139105E-2</v>
+        <v>1.0844821210139103E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>11.491967343038775</v>
+        <v>11.528984677948941</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>13.812130390149576</v>
+        <v>13.849147725059744</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19264,7 +19264,7 @@
       </c>
       <c r="F83" s="293">
         <f>(1-C83/C60)</f>
-        <v>0.52991157282883772</v>
+        <v>0.53016511574544634</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>17.600000000000001</v>
+        <v>17.86</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2544229151627766</v>
+        <v>0.24912793382512621</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>16.284754569504056</v>
+        <v>16.337210184442291</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>19.155315722914967</v>
+        <v>19.207771337853202</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19353,7 +19353,7 @@
       </c>
       <c r="F93" s="293">
         <f>(1-C93/C60)</f>
-        <v>0.34805913455798054</v>
+        <v>0.3483728239118582</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19392,7 +19392,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>23.651338136319364</v>
+        <v>23.727522611851839</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>27.292074172140108</v>
+        <v>27.368258647672583</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="F99" s="293">
         <f>(1-C99/C60)</f>
-        <v>7.1128938156432508E-2</v>
+        <v>7.1526790727299727E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>21.05984200970482</v>
+        <v>21.127678891028772</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19460,7 +19460,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>24.437486386018929</v>
+        <v>24.505323267342881</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="F105" s="293">
         <f>(1-C105/C66)</f>
-        <v>0.16819395158877881</v>
+        <v>0.16856309366387923</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210B899A-6606-4EBD-80B3-D935FE214075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96866526-F0EC-43FB-92D7-F15B0EFC9E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4322,7 +4322,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>17.86</v>
+        <v>17.7</v>
       </c>
       <c r="D12" s="50">
         <v>25.72</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>848884.97815423994</v>
+        <v>841280.18551679992</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0877953499999999</v>
+        <v>1.0859573200000001</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4386,13 +4386,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="E25" s="299">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.91929056324794922</v>
+        <v>0.92084650251264011</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -4468,14 +4468,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>29.476627192195373</v>
+        <v>29.426821017644194</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24912793382512621</v>
+        <v>0.25247997608512951</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4507,11 +4507,11 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>13.849147725059744</v>
+        <v>13.829667388333164</v>
       </c>
       <c r="D29" s="310">
         <f>D149</f>
-        <v>12.731390812674226</v>
+        <v>12.735000845459712</v>
       </c>
       <c r="E29" s="306" t="s">
         <v>425</v>
@@ -4526,11 +4526,11 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>19.207771337853202</v>
+        <v>19.180166621179882</v>
       </c>
       <c r="D30" s="311">
         <f>D157</f>
-        <v>17.657522931912887</v>
+        <v>17.661989350723175</v>
       </c>
       <c r="E30" s="307" t="s">
         <v>438</v>
@@ -4545,11 +4545,11 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>27.368258647672583</v>
+        <v>27.32816664104077</v>
       </c>
       <c r="D31" s="311">
         <f>D165</f>
-        <v>25.159381907334485</v>
+        <v>25.165046671484998</v>
       </c>
       <c r="E31" s="307" t="s">
         <v>437</v>
@@ -4564,11 +4564,11 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>24.505323267342881</v>
+        <v>24.469624174097014</v>
       </c>
       <c r="D32" s="311">
         <f>D173</f>
-        <v>22.527512429008713</v>
+        <v>22.532767838515984</v>
       </c>
       <c r="E32" s="307" t="s">
         <v>439</v>
@@ -4592,22 +4592,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4619,13 +4619,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4645,13 +4645,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4680,13 +4680,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4702,13 +4702,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4772,13 +4772,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4794,7 +4794,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4816,22 +4816,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11520983449112923</v>
+        <v>0.11605485143858825</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.8387458006718924E-2</v>
+        <v>7.9096045197740106E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4966,22 +4966,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5025,22 +5025,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>27.435301920154245</v>
+        <v>27.388944939506832</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5077,13 +5077,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5096,13 +5096,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1029738711528645</v>
+        <v>2.0994205106201185</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.305619257296502</v>
+        <v>2.3017234901712902</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11702336563364597</v>
+        <v>0.11682563316794312</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,13 +5224,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-0.45593156460418477</v>
+        <v>-0.4551611845012643</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5269,13 +5269,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>33.89 HKD</v>
+        <v>33.83 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>30.42 HKD</v>
+        <v>30.37 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>29.49 HKD</v>
+        <v>29.44 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>27.75 HKD</v>
+        <v>27.71 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>27.75 HKD</v>
+        <v>27.71 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>29.476627192195373</v>
+        <v>29.426821017644194</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5418,13 +5418,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5437,22 +5437,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>11.528984677948941</v>
+        <v>11.509504341222362</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5538,11 +5538,11 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>13.849147725059744</v>
+        <v>13.829667388333164</v>
       </c>
       <c r="D149" s="300">
         <f>IF($D$11="","",C149*$E$25)</f>
-        <v>12.731390812674226</v>
+        <v>12.735000845459712</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53016511574544634</v>
+        <v>0.53003189233247605</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>16.337210184442291</v>
+        <v>16.309605467768971</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5607,11 +5607,11 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>19.207771337853202</v>
+        <v>19.180166621179882</v>
       </c>
       <c r="D157" s="300">
         <f>IF($D$11="","",C157*$E$25)</f>
-        <v>17.657522931912887</v>
+        <v>17.661989350723175</v>
       </c>
     </row>
     <row r="158" spans="2:4">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3483728239118582</v>
+        <v>0.3482079967224615</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>23.727522611851839</v>
+        <v>23.687430605220026</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5676,11 +5676,11 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>27.368258647672583</v>
+        <v>27.32816664104077</v>
       </c>
       <c r="D165" s="300">
         <f>IF($D$11="","",C165*$E$25)</f>
-        <v>25.159381907334485</v>
+        <v>25.165046671484998</v>
       </c>
     </row>
     <row r="166" spans="2:4">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.1526790727299727E-2</v>
+        <v>7.1317740212069825E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>21.127678891028772</v>
+        <v>21.091979797782905</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5745,11 +5745,11 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>24.505323267342881</v>
+        <v>24.469624174097014</v>
       </c>
       <c r="D173" s="300">
         <f>IF($D$11="","",C173*$E$25)</f>
-        <v>22.527512429008713</v>
+        <v>22.532767838515984</v>
       </c>
     </row>
     <row r="174" spans="2:4">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.16856309366387923</v>
+        <v>0.16836912899796119</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5785,13 +5785,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5828,13 +5828,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5842,22 +5842,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5881,6 +5881,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5897,17 +5908,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -9360,11 +9360,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.108773944438077</v>
+        <v>17.079865529106925</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45593156460418477</v>
+        <v>-0.4551611845012643</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9770,11 +9770,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-99954.251325449994</v>
+        <v>-99785.360262840011</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.1029738711528645</v>
+        <v>-2.0994205106201185</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9787,11 +9787,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>109585.97720392699</v>
+        <v>109400.8115717333</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.305619257296502</v>
+        <v>2.3017234901712902</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9804,11 +9804,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>5562.1151836199997</v>
+        <v>5552.7169686240004</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11702336563364597</v>
+        <v>0.11682563316794312</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9821,11 +9821,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>15193.841062096995</v>
+        <v>15168.168277517289</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>0.31966875177728343</v>
+        <v>0.31912861271911486</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13502,20 +13502,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.8387458006718924E-2</v>
+        <v>7.9096045197740106E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.8387458006718924E-2</v>
+        <v>7.9096045197740106E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.9988801791713323E-2</v>
+        <v>7.0621468926553674E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>8.1187010078387453E-2</v>
+        <v>8.1920903954802254E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14644,50 +14644,50 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0576476440115679</v>
+        <v>2.0541708704630119</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2352028006617664</v>
+        <v>3.2297363314369258</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>2.8243967456375616</v>
+        <v>2.8196244086806299</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>3.2204327470552543</v>
+        <v>3.2149912345482656</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>1.7401510937005906</v>
+        <v>1.7372107888769357</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.63993125220713754</v>
+        <v>0.63884997084341955</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>1.3728763466286142</v>
+        <v>1.370556619934256</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>1.1634969369208088</v>
+        <v>1.1615309951883237</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>6.8512635315178345</v>
+        <v>6.8396870636566369</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4443869387315251</v>
+        <v>6.4334979635902032</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4907779193580204</v>
+        <v>6.47981055813597</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11520983449112923</v>
+        <v>0.11605485143858825</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18114237405720976</v>
+        <v>0.18247097917722746</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.15814091520926998</v>
+        <v>0.1593008140497531</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18031538337375444</v>
+        <v>0.18163792285583422</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.7432871987715039E-2</v>
+        <v>9.8147502196437045E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.5830417256838609E-2</v>
+        <v>3.6093218691718623E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.6868776406977285E-2</v>
+        <v>7.7432577397415603E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.5145405202732862E-2</v>
+        <v>6.5623220067136931E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.38360938026415647</v>
+        <v>0.38642299794670265</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.36082793609918956</v>
+        <v>0.36347446121978549</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.36342541541758233</v>
+        <v>0.36609099198508305</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16254498966399317</v>
+        <v>0.16401432290389367</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14617999280634367</v>
+        <v>0.14750139387125977</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16689775840780363</v>
+        <v>0.16840643870979508</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2822763754014053E-2</v>
+        <v>8.3571444104332829E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9398172947131155E-2</v>
+        <v>2.9663919143263415E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1912521214279532E-2</v>
+        <v>7.2562577903222181E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2052413054279582E-2</v>
+        <v>6.2613338822001888E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2807449547337583E-2</v>
+        <v>8.3555991464149687E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9703200695876821E-2</v>
+        <v>7.0333286125896052E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1062277122925076E-2</v>
+        <v>5.152385702912101E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0877953499999999</v>
+        <v>1.0859573200000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>29.473461041475876</v>
+        <v>29.423660216717742</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16659,23 +16659,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16686,23 +16686,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>28.624957904428221</v>
+        <v>28.576590781534129</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>29.069386849489806</v>
+        <v>29.020268782280784</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>29.520289562901674</v>
+        <v>29.470409612757287</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16713,23 +16713,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>29.487661879886598</v>
+        <v>29.437837060204217</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>30.417474278458347</v>
+        <v>30.366078369983441</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>31.392912803066839</v>
+        <v>31.33986871208096</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16740,23 +16740,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>30.579946140973284</v>
+        <v>30.528275706451304</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>32.168705013048772</v>
+        <v>32.114350078662326</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>33.890023047797229</v>
+        <v>33.832759630498614</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16767,23 +16767,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>31.718670303271367</v>
+        <v>31.665075785168749</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>34.044400423307977</v>
+        <v>33.986876157084509</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>36.640199872138368</v>
+        <v>36.578289526069156</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16794,23 +16794,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>32.80247289011519</v>
+        <v>32.747047088519132</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>35.880541177060849</v>
+        <v>35.819914413856111</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>39.412476213960417</v>
+        <v>39.345881597927594</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16820,23 +16820,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931538</v>
+        <v>27.708073552225954</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>27.754970671931538</v>
+        <v>27.708073552225954</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>33.780904012608012</v>
+        <v>33.723824971957313</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>37.587181327333397</v>
+        <v>37.523670882197671</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>42.069486454480305</v>
+        <v>41.998402331728798</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16871,7 +16871,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>33.890023047797229</v>
+        <v>33.832759630498614</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>30.417474278458347</v>
+        <v>30.366078369983441</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>29.487661879886598</v>
+        <v>29.437837060204217</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16962,7 +16962,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>20.3055132</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18111,23 +18111,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>20.3055132</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>20.3055132</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>20.3055132</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>20.3055132</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>20.3055132</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18138,23 +18138,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>20.949411243648491</v>
+        <v>20.914013366328867</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>21.278343574580155</v>
+        <v>21.242389905684274</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>21.612067293959914</v>
+        <v>21.575549737557129</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18165,23 +18165,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>21.587918777203061</v>
+        <v>21.551442024153825</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>22.276094835468076</v>
+        <v>22.238455282595901</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>22.998039864353508</v>
+        <v>22.9591804527814</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18192,23 +18192,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>22.396344088001431</v>
+        <v>22.358501351935253</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>23.572221953039513</v>
+        <v>23.532392355389238</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>24.846209976852965</v>
+        <v>24.804227742488983</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18219,23 +18219,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>23.239140663595769</v>
+        <v>23.199873867949048</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>24.960468308885833</v>
+        <v>24.918293014088171</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>26.88168062600117</v>
+        <v>26.836259090193902</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18246,23 +18246,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>24.041288487497951</v>
+        <v>24.000666315801162</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>26.319439331726947</v>
+        <v>26.274967805832954</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>28.933507648599459</v>
+        <v>28.884619174252375</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18272,23 +18272,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>24.765448408569355</v>
+        <v>24.723602635705557</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>27.582563907496667</v>
+        <v>27.535958100679338</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>30.900023514487504</v>
+        <v>30.847812250465896</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>24.846209976852965</v>
+        <v>24.804227742488983</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>22.276094835468076</v>
+        <v>22.238455282595901</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18368,7 +18368,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>21.587918777203061</v>
+        <v>21.551442024153825</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>20.305513200000004</v>
+        <v>20.271203306666674</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-17.86</v>
+        <v>-17.7</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>30.876627192195372</v>
+        <v>30.826821017644193</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>17.86</v>
+        <v>17.7</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18769,7 +18769,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.754970671931527</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>29.487661879886598</v>
+        <v>29.437837060204217</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18874,7 +18874,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18932,7 +18932,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>30.417474278458347</v>
+        <v>30.366078369983441</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>29.327086118009934</v>
+        <v>29.277532620564411</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>27.754970671931531</v>
+        <v>27.708073552225947</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19091,7 +19091,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>33.890023047797229</v>
+        <v>33.832759630498614</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>29.476627192195373</v>
+        <v>29.426821017644194</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19179,7 +19179,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>29.473461041475876</v>
+        <v>29.423660216717742</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>1.0844821210139103E-2</v>
+        <v>1.0844821210139102E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>11.528984677948941</v>
+        <v>11.509504341222362</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19324,7 +19324,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>13.849147725059744</v>
+        <v>13.829667388333164</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53016511574544634</v>
+        <v>0.53003189233247605</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>17.86</v>
+        <v>17.7</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24912793382512621</v>
+        <v>0.25247997608512951</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>16.337210184442291</v>
+        <v>16.309605467768971</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>19.207771337853202</v>
+        <v>19.180166621179882</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.3483728239118582</v>
+        <v>0.3482079967224615</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>23.727522611851839</v>
+        <v>23.687430605220026</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>27.368258647672583</v>
+        <v>27.32816664104077</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.1526790727299727E-2</v>
+        <v>7.1317740212069825E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19521,7 +19521,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>21.127678891028772</v>
+        <v>21.091979797782905</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19531,7 +19531,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>24.505323267342881</v>
+        <v>24.469624174097014</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.16856309366387923</v>
+        <v>0.16836912899796119</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96866526-F0EC-43FB-92D7-F15B0EFC9E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C57ABD0-3E2D-49F1-B7B7-DD4BC4B520E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2501,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3149,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3821,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3865,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3880,6 +3854,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4374,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0859573200000001</v>
+        <v>1.0859573199999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4386,13 +4402,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4458,7 +4474,7 @@
       </c>
       <c r="E25" s="299">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.92084650251264011</v>
+        <v>0.92084650251264022</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -4468,14 +4484,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>29.426821017644194</v>
+        <v>29.426821017644187</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.25247997608512951</v>
+        <v>0.25247997608512929</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4526,7 +4542,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>19.180166621179882</v>
+        <v>19.180166621179879</v>
       </c>
       <c r="D30" s="311">
         <f>D157</f>
@@ -4545,11 +4561,11 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>27.32816664104077</v>
+        <v>27.328166641040763</v>
       </c>
       <c r="D31" s="311">
         <f>D165</f>
-        <v>25.165046671484998</v>
+        <v>25.165046671484994</v>
       </c>
       <c r="E31" s="307" t="s">
         <v>437</v>
@@ -4564,7 +4580,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>24.469624174097014</v>
+        <v>24.46962417409701</v>
       </c>
       <c r="D32" s="311">
         <f>D173</f>
@@ -4592,22 +4608,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4619,19 +4635,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>122178.06382484984</v>
       </c>
@@ -4645,19 +4661,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>74606</v>
       </c>
@@ -4670,7 +4686,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-74606</v>
       </c>
@@ -4680,19 +4696,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4702,19 +4718,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>801.81967938187529</v>
       </c>
@@ -4729,7 +4745,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-2807</v>
       </c>
@@ -4744,7 +4760,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-2005.1803206181248</v>
       </c>
@@ -4762,7 +4778,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-223.13946170149947</v>
       </c>
@@ -4772,19 +4788,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-30043.220876057931</v>
       </c>
@@ -4794,19 +4810,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4816,28 +4832,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>141358.4276163358</v>
       </c>
@@ -4850,7 +4866,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>89906.523166472296</v>
       </c>
@@ -4865,7 +4881,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11605485143858825</v>
+        <v>0.11605485143858822</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4889,10 +4905,10 @@
       <c r="B72" s="210" t="s">
         <v>452</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>454</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>455</v>
       </c>
     </row>
@@ -4914,11 +4930,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.31929962351402291</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.4599183545926474</v>
       </c>
@@ -4928,11 +4944,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.35631048934895165</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.39810050545262105</v>
       </c>
@@ -4942,11 +4958,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.4094345614568822</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.4094345614568822</v>
       </c>
@@ -4966,22 +4982,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5025,22 +5041,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5056,7 +5072,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>27.388944939506832</v>
+        <v>27.388944939506825</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5077,13 +5093,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5096,19 +5112,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>91887</v>
       </c>
@@ -5123,7 +5139,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0994205106201185</v>
+        <v>2.099420510620118</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5134,7 +5150,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>0.12260820136742831</v>
       </c>
@@ -5143,7 +5159,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>0.75207444874659302</v>
       </c>
@@ -5157,7 +5173,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>154196</v>
       </c>
@@ -5170,7 +5186,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>100741.35470787497</v>
       </c>
@@ -5185,7 +5201,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.3017234901712902</v>
+        <v>2.3017234901712897</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5201,7 +5217,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>5113.2</v>
       </c>
@@ -5216,7 +5232,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11682563316794312</v>
+        <v>0.1168256331679431</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,13 +5240,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5238,7 +5254,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5251,7 +5267,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-0.4551611845012643</v>
+        <v>-0.45516118450126425</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5269,13 +5285,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5410,7 +5426,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>29.426821017644194</v>
+        <v>29.426821017644187</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5418,13 +5434,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5437,22 +5453,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5529,7 +5545,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>11.509504341222362</v>
+        <v>11.50950434122236</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5564,7 +5580,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53003189233247605</v>
+        <v>0.53003189233247594</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5598,7 +5614,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>16.309605467768971</v>
+        <v>16.309605467768968</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5607,7 +5623,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>19.180166621179882</v>
+        <v>19.180166621179879</v>
       </c>
       <c r="D157" s="300">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5667,7 +5683,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>23.687430605220026</v>
+        <v>23.687430605220019</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5676,11 +5692,11 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>27.32816664104077</v>
+        <v>27.328166641040763</v>
       </c>
       <c r="D165" s="300">
         <f>IF($D$11="","",C165*$E$25)</f>
-        <v>25.165046671484998</v>
+        <v>25.165046671484994</v>
       </c>
     </row>
     <row r="166" spans="2:4">
@@ -5736,7 +5752,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>21.091979797782905</v>
+        <v>21.091979797782901</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5745,7 +5761,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>24.469624174097014</v>
+        <v>24.46962417409701</v>
       </c>
       <c r="D173" s="300">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5785,13 +5801,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5799,13 +5815,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5828,13 +5844,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5842,22 +5858,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6023,423 +6039,423 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>420506</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>416609</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>422230</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>246111</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>155372.67139999999</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>233198.55619999999</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>227710.21479999999</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>2360193</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>1930911</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>2018883</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>215269</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>233125</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>217001</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>132757</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>104581.49189999999</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>138539.2739</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>139181.76360000001</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>1890398</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>1492165</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>1592771</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>10745</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>10513</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>9711</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>7912</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>7881.8548000000001</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>7386.8598000000002</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>6980.6142</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>134983</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>123705</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>118753</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>3532</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>3501</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>3355</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>2694</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>3048.0317</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>2798.4634999999998</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>2444.741</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>56055</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>49550</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>46872</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>1711</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>1605</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>1527</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>1506</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>1321.0753999999999</v>
       </c>
-      <c r="H8" s="334">
+      <c r="H8" s="321">
         <v>984.92179999999996</v>
       </c>
-      <c r="I8" s="334">
+      <c r="I8" s="321">
         <v>715.09730000000002</v>
       </c>
-      <c r="J8" s="334">
-        <v>0</v>
-      </c>
-      <c r="K8" s="334">
-        <v>0</v>
-      </c>
-      <c r="L8" s="334">
-        <v>0</v>
-      </c>
-      <c r="M8" s="334"/>
+      <c r="J8" s="321">
+        <v>0</v>
+      </c>
+      <c r="K8" s="321">
+        <v>0</v>
+      </c>
+      <c r="L8" s="321">
+        <v>0</v>
+      </c>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334">
+      <c r="C9" s="321">
         <v>1836</v>
       </c>
-      <c r="D9" s="334">
+      <c r="D9" s="321">
         <v>1931</v>
       </c>
-      <c r="E9" s="334">
+      <c r="E9" s="321">
         <v>1911</v>
       </c>
-      <c r="F9" s="334">
+      <c r="F9" s="321">
         <v>346</v>
       </c>
-      <c r="G9" s="334">
+      <c r="G9" s="321">
         <v>-632.40350000000001</v>
       </c>
-      <c r="H9" s="334">
+      <c r="H9" s="321">
         <v>1002.7065</v>
       </c>
-      <c r="I9" s="334">
+      <c r="I9" s="321">
         <v>-5186.9755999999998</v>
       </c>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>2807</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>2423</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>3129</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>3199</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>3553.9661000000001</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>3069.9225999999999</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>2601.9825999999998</v>
       </c>
-      <c r="J12" s="334">
-        <v>0</v>
-      </c>
-      <c r="K12" s="334">
-        <v>0</v>
-      </c>
-      <c r="L12" s="334">
-        <v>0</v>
-      </c>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321">
+        <v>0</v>
+      </c>
+      <c r="K12" s="321">
+        <v>0</v>
+      </c>
+      <c r="L12" s="321">
+        <v>0</v>
+      </c>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>4582</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>4805</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>2980</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>1341</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>1472.9675999999999</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>1066.8196</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>798.00549999999998</v>
       </c>
-      <c r="J13" s="334">
-        <v>0</v>
-      </c>
-      <c r="K13" s="334">
-        <v>0</v>
-      </c>
-      <c r="L13" s="334">
-        <v>0</v>
-      </c>
-      <c r="M13" s="334"/>
+      <c r="J13" s="321">
+        <v>0</v>
+      </c>
+      <c r="K13" s="321">
+        <v>0</v>
+      </c>
+      <c r="L13" s="321">
+        <v>0</v>
+      </c>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>51994</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>48884</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>53093</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>25514</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>9951.4562000000005</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>24603.813999999998</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>22482.776699999999</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>16279</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>20707</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>12613</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>137982</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>124090</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>141677</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>70307</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>24955.667399999998</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>61045.459000000003</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>52675.361299999997</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>70294</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>59170</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>43346</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>46</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>247</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>-23</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>-13</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>-1.1203000000000001</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>6.4699999999999994E-2</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>-1E-4</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>19175</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>12754</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>11139</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6451,171 +6467,171 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>74606</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>68947</v>
       </c>
-      <c r="E19" s="334">
+      <c r="E19" s="321">
         <v>62852</v>
       </c>
-      <c r="F19" s="334">
+      <c r="F19" s="321">
         <v>55963</v>
       </c>
-      <c r="G19" s="334">
+      <c r="G19" s="321">
         <v>51078.741900000001</v>
       </c>
-      <c r="H19" s="334">
+      <c r="H19" s="321">
         <v>56363.515599999999</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="321">
         <v>50838.249000000003</v>
       </c>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>220891</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>209743</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>205574</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>147893</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>82338.042000000001</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>123518.42600000001</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>124397.09020000001</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>190935</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>214543</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>165818</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-175426</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-78095</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-98473</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-96235</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-50849.064100000003</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-67455.145999999993</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-95452.180500000002</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-145323</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-66217</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-116952</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-97935</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-84228</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-64962</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-33332</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-38698.972800000003</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-37690.758699999998</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-27108.465100000001</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-56509</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-93047</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>9310</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6655,186 +6671,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>33661</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>41642</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>41488</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>33105</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>25613.371299999999</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>31381.7863</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>27143.492099999999</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>84701</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>63486</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>67075</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>5732</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>6451</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>6239</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>5703</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>5644.0001000000002</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>6313.6594999999998</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>5853.2028</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>186693</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>156511</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>145498</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>306845</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>337722</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>330648</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>304593</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>287345.75290000002</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>309503.74410000001</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>266468.9056</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>741434</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>666084</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>657506</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>749436</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>667876</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>598383</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>481976</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>433930.65610000002</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>448226.6789</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>419911.09840000002</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>854070</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>832525</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>785623</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>1888</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>1290</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>1201</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>1064</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>221.14420000000001</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>39.264600000000002</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>10.0449</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>126826</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>120293</v>
       </c>
-      <c r="L32" s="334">
+      <c r="L32" s="321">
         <v>110253</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6861,47 +6877,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>420506</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>416609</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>422230</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>246111</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>155372.67139999999</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>233198.55619999999</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>227710.21479999999</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>2360193</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>1930911</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>2018883</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6910,47 +6926,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-215269</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-233125</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-217001</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-132757</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-104581.49189999999</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-138539.2739</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-139181.76360000001</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-1890398</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-1492165</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-1592771</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6959,47 +6975,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>205237</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>183484</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>205229</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>113354</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>50791.179499999998</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>94659.282299999992</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>88528.451199999981</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>469795</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>438746</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>426112</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -7008,47 +7024,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-10745</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-10513</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-9711</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-7912</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-7881.8548000000001</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-7386.8598000000002</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-6980.6142</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-134983</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-123705</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-118753</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7057,47 +7073,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-3532</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-3501</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-3355</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-2694</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-3048.0317</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-2798.4634999999998</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-2444.741</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-56055</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-49550</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-46872</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7106,47 +7122,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-7213</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-7012</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-6356</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-5218</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-4833.8230999999996</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-4588.3963000000003</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-4535.8732</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-78928</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-74155</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-71881</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7155,47 +7171,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-1711</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-1605</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-1527</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-1506</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-1321.0753999999999</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>-984.92179999999996</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>-715.09730000000002</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7204,47 +7220,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>192781</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>171366</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>193991</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>103936</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>41588.249299999996</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>86287.50069999999</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>80832.739699999991</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>334812</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>315041</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>307359</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7351,47 +7367,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-51994</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-48884</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-53093</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-25514</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-9951.4562000000005</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-24603.813999999998</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-22482.776699999999</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-16279</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-20707</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-12613</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7400,47 +7416,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>137982</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>124090</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>141677</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>70307</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>24955.667399999998</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>61045.459000000003</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>52675.361299999997</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>70294</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>59170</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>43346</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7449,47 +7465,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-46</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>-247</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>-6.4699999999999994E-2</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>-19175</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>-12754</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-11139</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7503,47 +7519,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-2807</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-2423</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-3129</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-3199</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-3553.9661000000001</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-3069.9225999999999</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-2601.9825999999998</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7552,47 +7568,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>4582</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>4805</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>2980</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>1341</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>1472.9675999999999</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>1066.8196</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>798.00549999999998</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7808,47 +7824,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-74606</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-68947</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>-62852</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>-55963</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>-51078.741900000001</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>-56363.515599999999</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>-50838.249000000003</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7857,47 +7873,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-74606</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-68947</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-62852</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-55963</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-51078.741900000001</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>-56363.515599999999</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>-50838.249000000003</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7906,47 +7922,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7955,47 +7971,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-52470</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>47420</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>42139</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>18326</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>-7209.9949000000051</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>18372.521300000015</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>1836.4446000000025</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>-10897</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>55279</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>58176</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8377,115 +8393,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>33661</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>41642</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>41488</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>33105</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>25613.371299999999</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>31381.7863</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>5732</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>6451</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>6239</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>5703</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>5644.0001000000002</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>6313.6594999999998</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>306845</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>337722</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>330648</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>304593</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>287345.75290000002</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>309503.74410000001</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>266468.9056</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>741434</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>666084</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>657506</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8494,47 +8510,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>749436</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>667876</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>598383</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>481976</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>433930.65610000002</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>448226.6789</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>419911.09840000002</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>854070</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>832525</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>785623</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9360,11 +9376,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.079865529106925</v>
+        <v>17.079865529106922</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.4551611845012643</v>
+        <v>-0.45516118450126425</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9620,11 +9636,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-24522.24463146667</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-26727.322646062512</v>
       </c>
@@ -9652,8 +9668,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>53454.645292125024</v>
       </c>
@@ -9770,11 +9786,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-99785.360262840011</v>
+        <v>-99785.360262839997</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.0994205106201185</v>
+        <v>-2.099420510620118</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9787,11 +9803,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>109400.8115717333</v>
+        <v>109400.81157173327</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.3017234901712902</v>
+        <v>2.3017234901712897</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9804,11 +9820,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>5552.7169686240004</v>
+        <v>5552.7169686239995</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11682563316794312</v>
+        <v>0.1168256331679431</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9821,11 +9837,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>15168.168277517289</v>
+        <v>15168.168277517272</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>0.31912861271911486</v>
+        <v>0.3191286127191148</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -9957,54 +9973,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:J4)</f>
         <v>376364</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>420506</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>416609</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>422230</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>246111</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>155372.67139999999</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>233198.55619999999</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>227710.21479999999</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>2360193</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>1930911</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>2018883</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -10014,52 +10030,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-245261.93617515016</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-218801</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-236626</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-220356</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-135451</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-107629.5236</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-141337.73740000001</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-141626.50460000001</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-1946453</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-1541715</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-1639643</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10069,52 +10085,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>131102.06382484984</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>201705</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>179983</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>201874</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>110660</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>47743.147799999992</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>91860.818799999979</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>86083.710199999972</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>413740</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>389196</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>379240</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10124,52 +10140,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-8924</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-8924</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-8617</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-7883</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-6724</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-6154.8984999999993</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-5573.3181000000004</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-5250.9705000000004</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-78928</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-74155</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-71881</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10179,54 +10195,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>122178.06382484984</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>192781</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>171366</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>193991</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>103936</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>41588.249299999996</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>86287.500699999975</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>80832.739699999976</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>334812</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>315041</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>307359</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10236,52 +10252,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>74606</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>74606</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>68947</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>62852</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>55963</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>51078.741900000001</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>56363.515599999999</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>50838.249000000003</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10291,52 +10307,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-74606</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-74606</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-68947</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-62852</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-55963</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-51078.741900000001</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>-56363.515599999999</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>-50838.249000000003</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10346,54 +10362,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>1836</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>1931</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>1911</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>346</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>-632.40350000000001</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>1002.7065</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>-5186.9755999999998</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10403,52 +10419,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-2005.1803206181248</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>-1218.572383664188</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>-757.26567077835534</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-2095.9327156960453</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-2734.1197220632203</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>-3043.3370267115056</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-2700.0915842234122</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-2325.3405279380472</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10458,52 +10474,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>120172.88350423172</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>193398.4276163358</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>172539.73432922165</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>193806.06728430395</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>101547.88027793678</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>37912.508773288486</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>84590.115615776551</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>73320.423572061918</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>334812</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>315041</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>307359</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10513,52 +10529,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-30043.220876057931</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-51994</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-48884</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-53093</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-25514</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-9951.4562000000005</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-24603.813999999998</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-22482.776699999999</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-16279</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-20707</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-12613</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10568,54 +10584,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-223.13946170149947</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-46</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>-247</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>-6.4699999999999994E-2</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>0</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>-19175</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>-12754</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-11139</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10625,54 +10641,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>89906.523166472296</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>141358.4276163358</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>123408.73432922165</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>140713.06728430395</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>76033.880277936783</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>27961.052573288485</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>59986.23691577655</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>50837.646872061916</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>299358</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>281580</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>283607</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10682,7 +10698,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10691,24 +10707,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10716,71 +10732,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>89906.523166472296</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>141358.4276163358</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>123408.73432922165</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>140713.06728430395</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>76033.880277936783</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>27961.052573288485</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>59986.23691577655</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>50837.646872061916</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>299358</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>281580</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>283607</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10853,54 +10869,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-239590.97053351856</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-215269</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-233125</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-217001</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-132757</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-104581.49189999999</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-138539.2739</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-139181.76360000001</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-1890398</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-1492165</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-1592771</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10910,54 +10926,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-5670.965641631592</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-3532</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-3501</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-3355</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-2694</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-3048.0317</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-2798.4634999999998</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-2444.741</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-56055</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-49550</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-46872</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10967,54 +10983,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-245261.93617515016</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-218801</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-236626</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-220356</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-135451</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-107629.5236</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-141337.73740000001</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-141626.50460000001</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-1946453</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-1541715</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-1639643</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11220,54 +11236,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>G33</f>
         <v>-7213</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-7213</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-7012</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-6356</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-5218</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-4833.8230999999996</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-4588.3963000000003</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-4535.8732</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-78928</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-74155</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-71881</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11277,7 +11293,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>G34</f>
         <v>-1711</v>
       </c>
@@ -11286,47 +11302,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-1711</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-1605</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-1527</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-1506</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-1321.0753999999999</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>-984.92179999999996</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>-715.09730000000002</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11336,54 +11352,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-8924</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-8924</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-8617</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-7883</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-6724</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-6154.8984999999993</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-5573.3181000000004</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-5250.9705000000004</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-78928</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-74155</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-71881</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11677,52 +11693,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-2807</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-2807</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-2423</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-3129</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-3199</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-3553.9661000000001</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-3069.9225999999999</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-2601.9825999999998</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11732,52 +11748,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>801.81967938187529</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>1588.427616335812</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>1665.7343292216447</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>1033.0672843039545</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>464.88027793677952</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>510.62907328849445</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>369.83101577658761</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>276.64207206195277</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11787,54 +11803,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>2312.94</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>4582</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>4805</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>2980</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>1341</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>1472.9675999999999</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>1066.8196</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>798.00549999999998</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11844,52 +11860,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-2005.1803206181248</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-1218.572383664188</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>-757.26567077835534</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-2095.9327156960453</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-2734.1197220632203</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>-3043.3370267115056</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-2700.0915842234122</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-2325.3405279380472</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -12035,52 +12051,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12090,52 +12106,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>1836</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>1931</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>1911</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>346</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>-632.40350000000001</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>1002.7065</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>-5186.9755999999998</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12145,52 +12161,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12200,52 +12216,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>1836</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>1931</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>1911</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>346</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>-632.40350000000001</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>1002.7065</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>-5186.9755999999998</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12255,53 +12271,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>-6416</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>-2705</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>-983</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>-6603</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>-3967.7236999999955</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>362.16880000001424</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>1316.3510000000042</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-248239</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>-235164</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>-251400</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12311,52 +12327,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-4580</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>-774</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>928</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>-6257</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>-4600.1271999999954</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>1364.8753000000142</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>-3870.6245999999956</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-248239</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>-235164</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>-251400</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13730,54 +13746,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>1056281</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>1056281</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>1005598</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>929031</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>786569</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>721276.40899999999</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>757730.42299999995</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>686380.00399999996</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>1595504</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>1498609</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>1443129</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13787,54 +13803,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>33661</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>41642</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>41488</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>33105</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>25613.371299999999</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>31381.7863</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13844,54 +13860,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>5732</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>6451</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>6239</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>5703</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>5644.0001000000002</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>6313.6594999999998</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13901,54 +13917,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>306845</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>306845</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>337722</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>330648</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>304593</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>287345.75290000002</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>309503.74410000001</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>266468.9056</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>741434</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>666084</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>657506</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13958,54 +13974,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>749436</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>749436</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>667876</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>598383</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>481976</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>433930.65610000002</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>448226.6789</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>419911.09840000002</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>854070</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>832525</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>785623</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -14644,50 +14660,50 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0541708704630119</v>
+        <v>2.0541708704630115</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2297363314369258</v>
+        <v>3.229736331436925</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>2.8196244086806299</v>
+        <v>2.8196244086806295</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>3.2149912345482656</v>
+        <v>3.2149912345482647</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>1.7372107888769357</v>
+        <v>1.7372107888769355</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.63884997084341955</v>
+        <v>0.63884997084341943</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>1.370556619934256</v>
+        <v>1.3705566199342558</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>1.1615309951883237</v>
+        <v>1.1615309951883233</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>6.8396870636566369</v>
+        <v>6.839687063656636</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4334979635902032</v>
+        <v>6.4334979635902014</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>6.47981055813597</v>
+        <v>6.4798105581359691</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14701,50 +14717,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11605485143858825</v>
+        <v>0.11605485143858822</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18247097917722746</v>
+        <v>0.1824709791772274</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1593008140497531</v>
+        <v>0.15930081404975308</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18163792285583422</v>
+        <v>0.18163792285583416</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.8147502196437045E-2</v>
+        <v>9.8147502196437031E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6093218691718623E-2</v>
+        <v>3.6093218691718616E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.7432577397415603E-2</v>
+        <v>7.7432577397415589E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.5623220067136931E-2</v>
+        <v>6.5623220067136903E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.38642299794670265</v>
+        <v>0.3864229979467026</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.36347446121978549</v>
+        <v>0.36347446121978538</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.36609099198508305</v>
+        <v>0.36609099198508299</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15503,7 +15519,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15542,7 +15558,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>89906.523166472296</v>
       </c>
@@ -15574,7 +15590,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>1198753.6422196308</v>
       </c>
@@ -15582,17 +15598,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>91887</v>
       </c>
@@ -15600,15 +15616,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>100741.35470787497</v>
       </c>
@@ -15616,15 +15632,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>5113.2</v>
       </c>
@@ -15632,15 +15648,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>1212721.1969275058</v>
       </c>
@@ -15656,7 +15672,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0859573200000001</v>
+        <v>1.0859573199999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15670,7 +15686,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15707,7 +15723,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15717,13 +15733,13 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>29.423660216717742</v>
+        <v>29.423660216717739</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15731,10 +15747,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15752,7 +15768,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15774,7 +15790,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15796,7 +15812,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15816,9 +15832,19 @@
         <f t="shared" si="1"/>
         <v>76765.561628298354</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15838,9 +15864,19 @@
         <f t="shared" si="1"/>
         <v>72826.846999308487</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15860,9 +15896,19 @@
         <f t="shared" si="1"/>
         <v>69090.221335729104</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15884,7 +15930,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15906,7 +15952,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15928,7 +15974,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15950,7 +15996,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15972,7 +16018,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15994,7 +16040,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16016,11 +16062,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16036,13 +16082,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16058,13 +16114,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16080,9 +16146,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16104,7 +16180,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16126,7 +16202,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16148,7 +16224,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16170,7 +16246,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16192,7 +16268,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16214,7 +16290,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16236,7 +16312,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16258,7 +16334,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16280,7 +16356,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16302,7 +16378,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16324,11 +16400,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16344,13 +16420,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16366,13 +16452,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16388,13 +16484,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16410,9 +16516,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16434,7 +16550,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16445,11 +16561,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16459,7 +16575,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>1273841.0823216592</v>
@@ -16486,7 +16602,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16508,7 +16624,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16529,14 +16645,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>1198753.642219631</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>1198753.642219631</v>
       </c>
       <c r="D58" s="123">
@@ -16548,16 +16664,26 @@
       <c r="F58" s="123">
         <v>1466817.627889662</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>1198753.642219631</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>1198753.642219631</v>
       </c>
       <c r="D59" s="123">
@@ -16569,16 +16695,26 @@
       <c r="F59" s="123">
         <v>1586983.4089888346</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>1198753.642219631</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>1198753.642219631</v>
       </c>
       <c r="D60" s="123">
@@ -16590,16 +16726,26 @@
       <c r="F60" s="123">
         <v>1708114.802828433</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>1198753.6422196312</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>1198753.6422196312</v>
       </c>
       <c r="D61" s="123">
@@ -16611,26 +16757,56 @@
       <c r="F61" s="123">
         <v>1824209.7782913516</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16659,23 +16835,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16686,23 +16862,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>28.576590781534129</v>
+        <v>28.576590781534122</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>29.020268782280784</v>
+        <v>29.020268782280777</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>29.470409612757287</v>
+        <v>29.470409612757283</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16713,23 +16889,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>29.437837060204217</v>
+        <v>29.437837060204213</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>30.366078369983441</v>
+        <v>30.366078369983434</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>31.33986871208096</v>
+        <v>31.339868712080953</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16740,15 +16916,15 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>30.528275706451304</v>
+        <v>30.5282757064513</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
@@ -16756,7 +16932,7 @@
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>33.832759630498614</v>
+        <v>33.832759630498607</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16767,23 +16943,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>31.665075785168749</v>
+        <v>31.665075785168746</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>33.986876157084509</v>
+        <v>33.986876157084502</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>36.578289526069156</v>
+        <v>36.578289526069149</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16794,23 +16970,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>32.747047088519132</v>
+        <v>32.747047088519125</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>35.819914413856111</v>
+        <v>35.819914413856104</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>39.345881597927594</v>
+        <v>39.345881597927587</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16820,23 +16996,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225954</v>
+        <v>27.708073552225951</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225954</v>
+        <v>27.708073552225951</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>33.723824971957313</v>
+        <v>33.723824971957306</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>37.523670882197671</v>
+        <v>37.523670882197663</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>41.998402331728798</v>
+        <v>41.998402331728791</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16871,7 +17047,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>33.832759630498614</v>
+        <v>33.832759630498607</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16893,7 +17069,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>30.366078369983441</v>
+        <v>30.366078369983434</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16916,7 +17092,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>29.437837060204217</v>
+        <v>29.437837060204213</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16939,7 +17115,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16962,7 +17138,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17002,6 +17178,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17104,7 +17350,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>887225.80770133343</v>
       </c>
@@ -17112,8 +17358,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17122,7 +17368,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>20.271203306666671</v>
+        <v>20.271203306666667</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18111,23 +18357,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>20.271203306666671</v>
+        <v>20.271203306666667</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>20.271203306666671</v>
+        <v>20.271203306666667</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>20.271203306666671</v>
+        <v>20.271203306666667</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>20.271203306666671</v>
+        <v>20.271203306666667</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>20.271203306666671</v>
+        <v>20.271203306666667</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18138,23 +18384,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>20.914013366328867</v>
+        <v>20.914013366328863</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>21.242389905684274</v>
+        <v>21.242389905684266</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>21.575549737557129</v>
+        <v>21.575549737557125</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18165,23 +18411,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>21.551442024153825</v>
+        <v>21.551442024153822</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>22.238455282595901</v>
+        <v>22.238455282595897</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>22.9591804527814</v>
+        <v>22.959180452781396</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18192,23 +18438,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>22.358501351935253</v>
+        <v>22.358501351935249</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>23.532392355389238</v>
+        <v>23.532392355389231</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>24.804227742488983</v>
+        <v>24.804227742488976</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18219,23 +18465,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>23.199873867949048</v>
+        <v>23.199873867949044</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>24.918293014088171</v>
+        <v>24.918293014088164</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>26.836259090193902</v>
+        <v>26.836259090193899</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18246,23 +18492,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>24.000666315801162</v>
+        <v>24.000666315801155</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>26.274967805832954</v>
+        <v>26.274967805832947</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>28.884619174252375</v>
+        <v>28.884619174252371</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18272,23 +18518,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>24.723602635705557</v>
+        <v>24.72360263570555</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>27.535958100679338</v>
+        <v>27.535958100679331</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>30.847812250465896</v>
+        <v>30.847812250465889</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18323,7 +18569,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>24.804227742488983</v>
+        <v>24.804227742488976</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18345,7 +18591,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>22.238455282595901</v>
+        <v>22.238455282595897</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18368,7 +18614,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>21.551442024153825</v>
+        <v>21.551442024153822</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18391,7 +18637,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18414,7 +18660,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>20.271203306666674</v>
+        <v>20.271203306666671</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18563,14 +18809,14 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>30.826821017644193</v>
+        <v>30.826821017644185</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>192781</v>
       </c>
@@ -18578,11 +18824,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国海油(0883.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18595,7 +18841,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>141358.4276163358</v>
       </c>
@@ -18603,8 +18849,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18617,7 +18863,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>89906.523166472296</v>
       </c>
@@ -18625,8 +18871,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18636,8 +18882,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18650,8 +18896,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18669,8 +18915,8 @@
         <v>0.19549305441006948</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18687,8 +18933,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22866289579809873</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18705,8 +18951,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22962169479662209</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18732,21 +18978,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18760,8 +19006,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18769,14 +19015,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.708073552225944</v>
+        <v>27.70807355222594</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18796,8 +19042,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18807,8 +19053,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18816,14 +19062,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>29.437837060204217</v>
+        <v>29.437837060204213</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18833,8 +19079,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18854,8 +19100,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18865,8 +19111,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18874,14 +19120,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18891,8 +19137,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18912,8 +19158,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18923,8 +19169,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18932,14 +19178,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>30.366078369983441</v>
+        <v>30.366078369983434</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18950,8 +19196,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18959,7 +19205,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>29.277532620564411</v>
+        <v>29.277532620564401</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19013,8 +19259,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19024,8 +19270,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19033,14 +19279,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>27.708073552225947</v>
+        <v>27.708073552225944</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19050,8 +19296,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19071,8 +19317,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19082,8 +19328,8 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19091,14 +19337,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>33.832759630498614</v>
+        <v>33.832759630498607</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19108,8 +19354,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19117,7 +19363,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>29.426821017644194</v>
+        <v>29.426821017644187</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19179,7 +19425,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>29.423660216717742</v>
+        <v>29.423660216717739</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19314,7 +19560,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>11.509504341222362</v>
+        <v>11.50950434122236</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19335,7 +19581,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53003189233247605</v>
+        <v>0.53003189233247594</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19365,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.25247997608512951</v>
+        <v>0.25247997608512929</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19403,7 +19649,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>16.309605467768971</v>
+        <v>16.309605467768968</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19413,7 +19659,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>19.180166621179882</v>
+        <v>19.180166621179879</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19463,7 +19709,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>23.687430605220026</v>
+        <v>23.687430605220019</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19475,7 +19721,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>27.32816664104077</v>
+        <v>27.328166641040763</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19521,7 +19767,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>21.091979797782905</v>
+        <v>21.091979797782901</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19531,7 +19777,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>24.469624174097014</v>
+        <v>24.46962417409701</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C57ABD0-3E2D-49F1-B7B7-DD4BC4B520E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB034B20-D312-4309-B0A1-517D8F5EC020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="D12" s="50">
         <v>25.72</v>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>841280.18551679992</v>
+        <v>846033.18091520004</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4390,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0859573199999999</v>
+        <v>1.0910393900000002</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
@@ -4402,13 +4402,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="E25" s="299">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.92084650251264022</v>
+        <v>0.91655719231181909</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -4484,14 +4484,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>29.426821017644187</v>
+        <v>29.564532842533538</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.25247997608512929</v>
+        <v>0.25173434575411702</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4523,11 +4523,11 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>13.829667388333164</v>
+        <v>13.883529640237686</v>
       </c>
       <c r="D29" s="310">
         <f>D149</f>
-        <v>12.735000845459712</v>
+        <v>12.725048946434173</v>
       </c>
       <c r="E29" s="306" t="s">
         <v>425</v>
@@ -4542,11 +4542,11 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>19.180166621179879</v>
+        <v>19.256492416985179</v>
       </c>
       <c r="D30" s="311">
         <f>D157</f>
-        <v>17.661989350723175</v>
+        <v>17.649676623485771</v>
       </c>
       <c r="E30" s="307" t="s">
         <v>438</v>
@@ -4561,11 +4561,11 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>27.328166641040763</v>
+        <v>27.439019230031903</v>
       </c>
       <c r="D31" s="311">
         <f>D165</f>
-        <v>25.165046671484994</v>
+        <v>25.149430425268054</v>
       </c>
       <c r="E31" s="307" t="s">
         <v>437</v>
@@ -4580,11 +4580,11 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>24.46962417409701</v>
+        <v>24.568330555827487</v>
       </c>
       <c r="D32" s="311">
         <f>D173</f>
-        <v>22.532767838515984</v>
+        <v>22.518280074037914</v>
       </c>
       <c r="E32" s="307" t="s">
         <v>439</v>
@@ -4608,22 +4608,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4635,13 +4635,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4661,13 +4661,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4696,13 +4696,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4718,13 +4718,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4788,13 +4788,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4810,7 +4810,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4832,22 +4832,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11605485143858822</v>
+        <v>0.11594292092238964</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.9096045197740106E-2</v>
+        <v>7.8651685393258425E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4982,22 +4982,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5041,22 +5041,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>27.388944939506825</v>
+        <v>27.517119898913819</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5093,13 +5093,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5112,13 +5112,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.099420510620118</v>
+        <v>2.1092453921305694</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.3017234901712897</v>
+        <v>2.3124951104571547</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.1168256331679431</v>
+        <v>0.11737235451197699</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5240,13 +5240,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-0.45516118450126425</v>
+        <v>-0.45729125071870863</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5285,13 +5285,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>33.83 HKD</v>
+        <v>33.99 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>30.37 HKD</v>
+        <v>30.51 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>29.44 HKD</v>
+        <v>29.58 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>27.71 HKD</v>
+        <v>27.84 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>27.71 HKD</v>
+        <v>27.84 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>29.426821017644187</v>
+        <v>29.564532842533538</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5434,13 +5434,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5453,22 +5453,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>11.50950434122236</v>
+        <v>11.563366593126883</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5554,11 +5554,11 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>13.829667388333164</v>
+        <v>13.883529640237686</v>
       </c>
       <c r="D149" s="300">
         <f>IF($D$11="","",C149*$E$25)</f>
-        <v>12.735000845459712</v>
+        <v>12.725048946434173</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53003189233247594</v>
+        <v>0.5303991538041859</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>16.309605467768968</v>
+        <v>16.385931263574268</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>19.180166621179879</v>
+        <v>19.256492416985179</v>
       </c>
       <c r="D157" s="300">
         <f>IF($D$11="","",C157*$E$25)</f>
-        <v>17.661989350723175</v>
+        <v>17.649676623485771</v>
       </c>
     </row>
     <row r="158" spans="2:4">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3482079967224615</v>
+        <v>0.34866238138958561</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>23.687430605220019</v>
+        <v>23.798283194211159</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>27.328166641040763</v>
+        <v>27.439019230031903</v>
       </c>
       <c r="D165" s="300">
         <f>IF($D$11="","",C165*$E$25)</f>
-        <v>25.165046671484994</v>
+        <v>25.149430425268054</v>
       </c>
     </row>
     <row r="166" spans="2:4">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.1317740212069825E-2</v>
+        <v>7.1894036811693707E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>21.091979797782901</v>
+        <v>21.190686179513378</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>24.46962417409701</v>
+        <v>24.568330555827487</v>
       </c>
       <c r="D173" s="300">
         <f>IF($D$11="","",C173*$E$25)</f>
-        <v>22.532767838515984</v>
+        <v>22.518280074037914</v>
       </c>
     </row>
     <row r="174" spans="2:4">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.16836912899796119</v>
+        <v>0.16890383792844488</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5801,13 +5801,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5844,13 +5844,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5858,22 +5858,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5897,17 +5897,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5924,6 +5913,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -9376,11 +9376,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.079865529106922</v>
+        <v>17.159795992865401</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45516118450126425</v>
+        <v>-0.45729125071870863</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9786,11 +9786,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-99785.360262839997</v>
+        <v>-100252.33642893001</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.099420510620118</v>
+        <v>-2.1092453921305694</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9803,11 +9803,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>109400.81157173327</v>
+        <v>109912.78618825355</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.3017234901712897</v>
+        <v>2.3124951104571547</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9820,11 +9820,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>5552.7169686239995</v>
+        <v>5578.7026089480005</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.1168256331679431</v>
+        <v>0.11737235451197699</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9837,11 +9837,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>15168.168277517272</v>
+        <v>15239.152368271543</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>0.3191286127191148</v>
+        <v>0.32062207283856231</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.9096045197740106E-2</v>
+        <v>7.8651685393258425E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.9096045197740106E-2</v>
+        <v>7.8651685393258425E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.0621468926553674E-2</v>
+        <v>7.0224719101123587E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>8.1920903954802254E-2</v>
+        <v>8.1460674157303362E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14660,50 +14660,50 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0541708704630115</v>
+        <v>2.0637839924185357</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.229736331436925</v>
+        <v>3.2448508721427296</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>2.8196244086806295</v>
+        <v>2.8328197049917443</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>3.2149912345482647</v>
+        <v>3.2300367710555022</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>1.7372107888769355</v>
+        <v>1.7453405990188555</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.63884997084341943</v>
+        <v>0.64183966501604528</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>1.3705566199342558</v>
+        <v>1.3769705595552619</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>1.1615309951883233</v>
+        <v>1.1669667353560098</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>6.839687063656636</v>
+        <v>6.8716954748487069</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4334979635902014</v>
+        <v>6.4636054884382537</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4798105581359691</v>
+        <v>6.5101348169596838</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11605485143858822</v>
+        <v>0.11594292092238964</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1824709791772274</v>
+        <v>0.18229499281700728</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.15930081404975308</v>
+        <v>0.15914717443773843</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18163792285583416</v>
+        <v>0.18146273994693832</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.8147502196437031E-2</v>
+        <v>9.8052842641508736E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6093218691718616E-2</v>
+        <v>3.6058408146968833E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.7432577397415589E-2</v>
+        <v>7.7357896604228191E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.5623220067136903E-2</v>
+        <v>6.555992895258482E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.3864229979467026</v>
+        <v>0.38605030757577002</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.36347446121978538</v>
+        <v>0.36312390384484572</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.36609099198508299</v>
+        <v>0.36573791106515074</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16401432290389367</v>
+        <v>0.1630928941235347</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14750139387125977</v>
+        <v>0.14667273435512906</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16840643870979508</v>
+        <v>0.16746033512153777</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3571444104332829E-2</v>
+        <v>8.3101941609364655E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9663919143263415E-2</v>
+        <v>2.9497267912121483E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2562577903222181E-2</v>
+        <v>7.215492297118159E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2613338822001888E-2</v>
+        <v>6.2261578491541195E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3555991464149687E-2</v>
+        <v>8.3086575781766814E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0333286125896052E-2</v>
+        <v>6.9938155304964042E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.152385702912101E-2</v>
+        <v>5.1234397158170887E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15672,7 +15672,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0859573199999999</v>
+        <v>1.0910393900000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>29.423660216717739</v>
+        <v>29.561357249670731</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16835,23 +16835,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>28.576590781534122</v>
+        <v>28.710323693535784</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>29.020268782280777</v>
+        <v>29.156078021423227</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>29.470409612757283</v>
+        <v>29.608325423832355</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16889,23 +16889,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>29.437837060204213</v>
+        <v>29.575600438039871</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>30.366078369983434</v>
+        <v>30.508185737427443</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>31.339868712080953</v>
+        <v>31.486533229785586</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16916,23 +16916,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>30.5282757064513</v>
+        <v>30.671142126026144</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>32.114350078662326</v>
+        <v>32.264639019211366</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>33.832759630498607</v>
+        <v>33.991090395040423</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16943,23 +16943,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>31.665075785168746</v>
+        <v>31.813262209010468</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>33.986876157084502</v>
+        <v>34.145928157131472</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>36.578289526069149</v>
+        <v>36.749468838946527</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16970,23 +16970,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>32.747047088519125</v>
+        <v>32.900296928574676</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>35.819914413856104</v>
+        <v>35.987544678041104</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>39.345881597927587</v>
+        <v>39.530012705853991</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16996,23 +16996,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225951</v>
+        <v>27.83774197175239</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>27.708073552225951</v>
+        <v>27.83774197175239</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>33.723824971957306</v>
+        <v>33.881645943388527</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>37.523670882197663</v>
+        <v>37.699274396781739</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>41.998402331728791</v>
+        <v>42.194946723121646</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>33.832759630498607</v>
+        <v>33.991090395040423</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17069,7 +17069,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>30.366078369983434</v>
+        <v>30.508185737427443</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>29.437837060204213</v>
+        <v>29.575600438039871</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17115,7 +17115,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17368,7 +17368,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>20.271203306666667</v>
+        <v>20.366068613333336</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18357,23 +18357,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>20.271203306666667</v>
+        <v>20.366068613333336</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>20.271203306666667</v>
+        <v>20.366068613333336</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>20.271203306666667</v>
+        <v>20.366068613333336</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>20.271203306666667</v>
+        <v>20.366068613333336</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>20.271203306666667</v>
+        <v>20.366068613333336</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>20.914013366328863</v>
+        <v>21.0118868996171</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>21.242389905684266</v>
+        <v>21.341800177598074</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>21.575549737557125</v>
+        <v>21.676519132979362</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18411,23 +18411,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>21.551442024153822</v>
+        <v>21.652298600144945</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>22.238455282595897</v>
+        <v>22.342526947620474</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>22.959180452781396</v>
+        <v>23.066624972059255</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18438,23 +18438,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>22.358501351935249</v>
+        <v>22.46313480932162</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>23.532392355389231</v>
+        <v>23.642519395388888</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>24.804227742488976</v>
+        <v>24.920306725853884</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18465,23 +18465,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>23.199873867949044</v>
+        <v>23.308444785808039</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>24.918293014088164</v>
+        <v>25.034905800839411</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>26.836259090193899</v>
+        <v>26.961847586834363</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18492,23 +18492,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>24.000666315801155</v>
+        <v>24.112984787270687</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>26.274967805832947</v>
+        <v>26.397929567937002</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>28.884619174252371</v>
+        <v>29.019793599493042</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18518,23 +18518,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>24.72360263570555</v>
+        <v>24.839304309180939</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>27.535958100679331</v>
+        <v>27.664821053216663</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>30.847812250465889</v>
+        <v>30.992174039199661</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18569,7 +18569,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>24.804227742488976</v>
+        <v>24.920306725853884</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>22.238455282595897</v>
+        <v>22.342526947620474</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>21.551442024153822</v>
+        <v>21.652298600144945</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18637,7 +18637,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>20.271203306666671</v>
+        <v>20.36606861333334</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-17.7</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>30.826821017644185</v>
+        <v>30.964532842533536</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19015,7 +19015,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.70807355222594</v>
+        <v>27.837741971752379</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>29.437837060204213</v>
+        <v>29.575600438039871</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>30.366078369983434</v>
+        <v>30.508185737427443</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19205,7 +19205,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>29.277532620564401</v>
+        <v>29.414545804659888</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>27.708073552225944</v>
+        <v>27.837741971752383</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19337,7 +19337,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>33.832759630498607</v>
+        <v>33.991090395040423</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>29.426821017644187</v>
+        <v>29.564532842533538</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>29.423660216717739</v>
+        <v>29.561357249670731</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>1.0844821210139102E-2</v>
+        <v>1.0844821210139119E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>11.50950434122236</v>
+        <v>11.563366593126883</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19570,7 +19570,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>13.829667388333164</v>
+        <v>13.883529640237686</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53003189233247594</v>
+        <v>0.5303991538041859</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.25247997608512929</v>
+        <v>0.25173434575411702</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>16.309605467768968</v>
+        <v>16.385931263574268</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>19.180166621179879</v>
+        <v>19.256492416985179</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.3482079967224615</v>
+        <v>0.34866238138958561</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>23.687430605220019</v>
+        <v>23.798283194211159</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19721,7 +19721,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>27.328166641040763</v>
+        <v>27.439019230031903</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19731,7 +19731,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.1317740212069825E-2</v>
+        <v>7.1894036811693707E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19767,7 +19767,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>21.091979797782901</v>
+        <v>21.190686179513378</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>24.46962417409701</v>
+        <v>24.568330555827487</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.16836912899796119</v>
+        <v>0.16890383792844488</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FD3F0C-1099-4030-B9A2-3DA8EAB5FBC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72A336E-B998-474B-BA57-8159EC868457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,19 +4340,19 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>17.88</v>
+        <v>17.98</v>
       </c>
       <c r="D12" s="50">
         <v>25.72</v>
       </c>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4353,13 +4364,13 @@
       </c>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>849835.57723391987</v>
+        <v>854588.57263232011</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4367,7 +4378,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4381,39 +4392,39 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0907712000000001</v>
+        <v>1.0889065499999999</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
       </c>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4428,7 +4439,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4441,7 +4452,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4449,7 +4460,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4457,7 +4468,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4470,31 +4481,31 @@
       </c>
       <c r="E25" s="299">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.91678254798073133</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
+        <v>0.91835245182426362</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>29.557265541154948</v>
+        <v>29.506738028885355</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>399</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24965636355985632</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.24655165618865404</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4513,17 +4524,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>13.880687232057891</v>
+        <v>13.860924763612207</v>
       </c>
       <c r="D29" s="310">
         <f>D149</f>
-        <v>12.725571808329638</v>
+        <v>12.729214241214923</v>
       </c>
       <c r="E29" s="306" t="s">
         <v>424</v>
@@ -4532,17 +4543,17 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>19.252464567078146</v>
+        <v>19.224460054124101</v>
       </c>
       <c r="D30" s="311">
         <f>D157</f>
-        <v>17.65032352071465</v>
+        <v>17.654830025702484</v>
       </c>
       <c r="E30" s="307" t="s">
         <v>437</v>
@@ -4551,17 +4562,17 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>27.433169338975397</v>
+        <v>27.39249668392296</v>
       </c>
       <c r="D31" s="311">
         <f>D165</f>
-        <v>25.150250885772738</v>
+        <v>25.155966491268661</v>
       </c>
       <c r="E31" s="307" t="s">
         <v>436</v>
@@ -4570,17 +4581,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>24.56312164203521</v>
+        <v>24.526905522482799</v>
       </c>
       <c r="D32" s="311">
         <f>D173</f>
-        <v>22.519041245345687</v>
+        <v>22.524343822234151</v>
       </c>
       <c r="E32" s="307" t="s">
         <v>438</v>
@@ -4589,11 +4600,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4603,25 +4614,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4630,16 +4641,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4652,20 +4663,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4678,7 +4689,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4691,16 +4702,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4713,16 +4724,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4737,7 +4748,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4752,7 +4763,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4765,12 +4776,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4783,16 +4794,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4805,8 +4816,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4814,7 +4825,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4827,25 +4838,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4858,7 +4869,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4871,23 +4882,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11539578806681026</v>
+        <v>0.11455781776035873</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.829977628635347E-2</v>
+        <v>7.7864293659621789E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4897,7 +4908,7 @@
         <v>0.74012355537751062</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
@@ -4908,7 +4919,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>452</v>
       </c>
@@ -4921,7 +4932,7 @@
         <v>0.25805863024505871</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4935,7 +4946,7 @@
         <v>0.4599183545926474</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4949,7 +4960,7 @@
         <v>0.39810050545262105</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4963,7 +4974,7 @@
         <v>1.4094345614568822</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4973,34 +4984,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5009,7 +5020,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5018,7 +5029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5027,34 +5038,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5062,20 +5073,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>27.510355875127573</v>
+        <v>27.463327511083342</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5085,38 +5096,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5129,20 +5140,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1087269154129551</v>
+        <v>2.1051220919240095</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5151,7 +5162,7 @@
         <v>0.12260820136742831</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5160,12 +5171,12 @@
         <v>0.75207444874659302</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5178,7 +5189,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5191,25 +5202,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.3119266726268086</v>
+        <v>2.3079744835058325</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5222,55 +5233,55 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11734350304057724</v>
+        <v>0.11714290683585106</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-0.45717884328259373</v>
+        <v>-0.45639730584364507</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5280,16 +5291,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5306,7 +5317,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5321,14 +5332,14 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>33.98 HKD</v>
+        <v>33.92 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5343,14 +5354,14 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>30.5 HKD</v>
+        <v>30.45 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5365,14 +5376,14 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>29.57 HKD</v>
+        <v>29.52 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5387,14 +5398,14 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>27.83 HKD</v>
+        <v>27.78 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5409,36 +5420,36 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>27.83 HKD</v>
+        <v>27.78 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>29.557265541154948</v>
+        <v>29.506738028885355</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5448,30 +5459,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5480,7 +5491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5489,7 +5500,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5502,7 +5513,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5515,7 +5526,7 @@
         <v>600938.SS</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5524,7 +5535,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5534,30 +5545,30 @@
         <v>2.3201630471108023</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>11.56052418494709</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
+        <v>11.540761716501404</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>13.880687232057891</v>
+        <v>13.860924763612207</v>
       </c>
       <c r="D149" s="300">
         <f>IF($D$11="","",C149*$E$25)</f>
-        <v>12.725571808329638</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4">
+        <v>12.729214241214923</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5570,21 +5581,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53037985828794953</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
+        <v>0.53024543919279798</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5593,7 +5604,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5603,30 +5614,30 @@
         <v>2.870561153410911</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>16.381903413667235</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
+        <v>16.35389890071319</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>19.252464567078146</v>
+        <v>19.224460054124101</v>
       </c>
       <c r="D157" s="300">
         <f>IF($D$11="","",C157*$E$25)</f>
-        <v>17.65032352071465</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4">
+        <v>17.654830025702484</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5639,21 +5650,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34863850851590461</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
+        <v>0.34847220199994688</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5662,7 +5673,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5672,30 +5683,30 @@
         <v>3.6407360358207437</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>23.792433303154652</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4">
+        <v>23.751760648102216</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>27.433169338975397</v>
+        <v>27.39249668392296</v>
       </c>
       <c r="D165" s="300">
         <f>IF($D$11="","",C165*$E$25)</f>
-        <v>25.150250885772738</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4">
+        <v>25.155966491268661</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5708,21 +5719,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.1863758818352164E-2</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
+        <v>7.1652832071531503E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5731,7 +5742,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5741,30 +5752,30 @@
         <v>3.3776443763141084</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>21.185477265721101</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
+        <v>21.149261146168691</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>24.56312164203521</v>
+        <v>24.526905522482799</v>
       </c>
       <c r="D173" s="300">
         <f>IF($D$11="","",C173*$E$25)</f>
-        <v>22.519041245345687</v>
-      </c>
-    </row>
-    <row r="174" spans="2:4">
+        <v>22.524343822234151</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5777,16 +5788,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.16887574490577673</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" ht="13.9">
+        <v>0.16868003940399767</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5796,21 +5807,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5819,80 +5830,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5909,17 +5931,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5950,15 +5961,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6007,7 +6018,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6023,7 +6034,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6031,7 +6042,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6067,7 +6078,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6103,7 +6114,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6139,7 +6150,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6175,7 +6186,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6211,7 +6222,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6241,7 +6252,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6257,7 +6268,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6273,7 +6284,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6309,7 +6320,7 @@
       </c>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6345,7 +6356,7 @@
       </c>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6381,7 +6392,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6417,7 +6428,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6453,13 +6464,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6489,7 +6500,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6505,7 +6516,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6521,7 +6532,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6557,7 +6568,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6593,7 +6604,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6629,7 +6640,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6655,7 +6666,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6663,7 +6674,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6700,7 +6711,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6737,7 +6748,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6774,7 +6785,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6811,7 +6822,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6848,7 +6859,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6864,12 +6875,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6918,7 +6929,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6967,7 +6978,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -7016,7 +7027,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7065,7 +7076,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7114,7 +7125,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7163,7 +7174,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7212,7 +7223,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7261,7 +7272,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7310,7 +7321,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7359,7 +7370,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7408,7 +7419,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7457,7 +7468,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7506,12 +7517,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7560,7 +7571,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7609,12 +7620,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7663,7 +7674,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7712,7 +7723,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7761,7 +7772,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7810,13 +7821,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7865,7 +7876,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7914,7 +7925,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7963,7 +7974,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -8012,7 +8023,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8061,12 +8072,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8116,7 +8127,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8165,7 +8176,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8215,7 +8226,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8264,7 +8275,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8314,7 +8325,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8330,13 +8341,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8385,7 +8396,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8419,7 +8430,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8453,7 +8464,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8502,7 +8513,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8583,18 +8594,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8610,7 +8621,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8621,7 +8632,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8641,7 +8652,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8663,7 +8674,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8685,7 +8696,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8706,7 +8717,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8727,7 +8738,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8748,7 +8759,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8769,7 +8780,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8781,7 +8792,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8794,7 +8805,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8818,12 +8829,12 @@
         <v>138776.4</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8843,7 +8854,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>455</v>
       </c>
@@ -8863,7 +8874,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8883,7 +8894,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8904,7 +8915,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8925,7 +8936,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8946,7 +8957,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8966,7 +8977,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8986,7 +8997,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8998,7 +9009,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -9010,7 +9021,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9034,7 +9045,7 @@
         <v>9962.2999999999993</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9051,7 +9062,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9070,7 +9081,7 @@
         <v>-18033.400000000023</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9085,7 +9096,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9104,7 +9115,7 @@
         <v>-19921.400000000023</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9120,7 +9131,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9137,7 +9148,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9157,7 +9168,7 @@
         <v>288811.59999999998</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9168,7 +9179,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9181,7 +9192,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9200,7 +9211,7 @@
         <v>140072.9</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9216,7 +9227,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9232,7 +9243,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9248,7 +9259,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9267,7 +9278,7 @@
         <v>64516.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9287,7 +9298,7 @@
         <v>148738.69999999998</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9307,7 +9318,7 @@
         <v>143625.49999999997</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9326,7 +9337,7 @@
         <v>5113.2</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9337,7 +9348,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9351,7 +9362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9365,25 +9376,25 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.155577918129044</v>
+        <v>17.12625082518321</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45717884328259373</v>
+        <v>-0.45639730584364507</v>
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9396,7 +9407,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9410,7 +9421,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9421,10 +9432,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9436,7 +9447,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9450,7 +9461,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9464,10 +9475,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9479,7 +9490,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9490,7 +9501,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9501,10 +9512,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9516,7 +9527,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9532,7 +9543,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9543,7 +9554,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9557,7 +9568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9573,7 +9584,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9583,7 +9594,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9593,7 +9604,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9603,7 +9614,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9613,10 +9624,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9628,7 +9639,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9644,7 +9655,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9660,7 +9671,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9673,7 +9684,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9686,10 +9697,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9701,7 +9712,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9715,7 +9726,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9729,7 +9740,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9743,7 +9754,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9757,7 +9768,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9768,7 +9779,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9776,68 +9787,68 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-100227.6932544</v>
+        <v>-100056.35615984999</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.1087269154129547</v>
+        <v>-2.1051220919240095</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>109885.76836433444</v>
+        <v>109697.92099727839</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.3119266726268086</v>
+        <v>2.3079744835058325</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>5577.3312998399997</v>
+        <v>5567.7969714599994</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11734350304057724</v>
+        <v>0.11714290683585105</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>15235.406409774434</v>
+        <v>15209.361808888392</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>0.32054326025443119</v>
+        <v>0.31999529841767405</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -9858,19 +9869,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9927,7 +9938,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9950,7 +9961,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9964,7 +9975,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -10021,7 +10032,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10076,7 +10087,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10131,7 +10142,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10186,7 +10197,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10243,7 +10254,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10298,7 +10309,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10353,7 +10364,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10410,7 +10421,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10465,7 +10476,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10520,7 +10531,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10575,7 +10586,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10632,7 +10643,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10689,7 +10700,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10715,7 +10726,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10740,7 +10751,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10797,7 +10808,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10816,7 +10827,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10839,7 +10850,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10860,7 +10871,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10917,7 +10928,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10974,7 +10985,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11031,18 +11042,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11101,7 +11112,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11161,7 +11172,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11216,18 +11227,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11284,7 +11295,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11343,7 +11354,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11400,18 +11411,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11469,7 +11480,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11527,7 +11538,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11582,18 +11593,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11651,10 +11662,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11677,14 +11688,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11739,7 +11750,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11794,7 +11805,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11851,7 +11862,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11906,11 +11917,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11920,7 +11931,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11946,7 +11957,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11973,7 +11984,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -12028,11 +12039,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12042,7 +12053,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12097,7 +12108,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12152,7 +12163,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12207,7 +12218,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12262,7 +12273,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12318,7 +12329,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12373,11 +12384,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12387,7 +12398,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12412,7 +12423,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12436,7 +12447,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12461,7 +12472,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12488,10 +12499,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12514,7 +12525,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12535,7 +12546,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12592,7 +12603,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12649,7 +12660,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12706,7 +12717,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12763,7 +12774,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12820,7 +12831,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12879,7 +12890,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12936,7 +12947,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12993,7 +13004,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13050,7 +13061,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13107,7 +13118,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13165,7 +13176,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13222,7 +13233,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13248,7 +13259,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13272,7 +13283,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13329,18 +13340,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13396,7 +13407,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13452,7 +13463,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13507,27 +13518,27 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.829977628635347E-2</v>
+        <v>7.7864293659621789E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.829977628635347E-2</v>
+        <v>7.7864293659621789E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.9910514541387025E-2</v>
+        <v>6.9521690767519462E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>8.1096196868008952E-2</v>
+        <v>8.0645161290322578E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13562,11 +13573,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13587,7 +13598,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13644,7 +13655,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13701,10 +13712,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13727,7 +13738,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13737,7 +13748,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13794,7 +13805,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13851,7 +13862,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13908,7 +13919,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13965,7 +13976,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -14022,11 +14033,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14049,7 +14060,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14106,7 +14117,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14163,7 +14174,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14190,18 +14201,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14253,7 +14264,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14305,11 +14316,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14363,7 +14374,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14418,7 +14429,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14472,7 +14483,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14528,7 +14539,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14585,7 +14596,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14604,7 +14615,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14627,7 +14638,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14648,7 +14659,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14656,845 +14667,845 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0632766906345674</v>
+        <v>2.0597495633312501</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2440532505688648</v>
+        <v>3.2385076110308262</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>2.8321233654061659</v>
+        <v>2.8272819111824892</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>3.2292427909576529</v>
+        <v>3.2237224695830511</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>1.7449115742746149</v>
+        <v>1.7419286853177269</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.64168189346229709</v>
+        <v>0.64058495201147347</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>1.3766320843931807</v>
+        <v>1.374278761334996</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>1.1666798815433759</v>
+        <v>1.164685467278386</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>6.8700063332592354</v>
+        <v>6.8582622046011696</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4620166600496249</v>
+        <v>6.4509699809979937</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>6.5085345511282542</v>
+        <v>6.4974083507383256</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11539578806681026</v>
+        <v>0.11455781776035873</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1814347455575428</v>
+        <v>0.18011721974587463</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.15839616137618379</v>
+        <v>0.15724593499346434</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.18060642007593139</v>
+        <v>0.17929490932052564</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.7590132789407993E-2</v>
+        <v>9.6881461919784584E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.5888249075072549E-2</v>
+        <v>3.5627639155254361E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.6992845883287517E-2</v>
+        <v>7.643374645912103E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.5250552659025504E-2</v>
+        <v>6.4776722318041491E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.38422854212859259</v>
+        <v>0.38143838735267904</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.36141032774326765</v>
+        <v>0.35878587213559476</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.36401199950381735</v>
+        <v>0.3613686513202628</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16236317200217662</v>
+        <v>0.16146015102329908</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14601648051013971</v>
+        <v>0.1452043755017407</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16671107187714612</v>
+        <v>0.16578386903022094</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2730120841537538E-2</v>
+        <v>8.2269997811273129E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9365289084774187E-2</v>
+        <v>2.9201967121010145E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.18320821525186E-2</v>
+        <v>7.1432571128311029E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1983003196277038E-2</v>
+        <v>6.1638270141792725E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2714823764846165E-2</v>
+        <v>8.2254785812872599E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9625232909863541E-2</v>
+        <v>6.9237995796905441E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1005160481847979E-2</v>
+        <v>5.0721483282282633E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15516,16 +15527,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15537,7 +15548,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15550,7 +15561,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15571,7 +15582,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15582,7 +15593,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15600,7 +15611,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15616,7 +15627,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15632,7 +15643,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15648,7 +15659,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15662,13 +15673,13 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0907712000000001</v>
+        <v>1.0889065499999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15676,13 +15687,13 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15690,10 +15701,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15703,13 +15714,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15719,7 +15730,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15729,13 +15740,13 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>29.5540907288893</v>
+        <v>29.503568643893267</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15743,10 +15754,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15764,7 +15775,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15786,7 +15797,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15808,7 +15819,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15840,7 +15851,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15872,7 +15883,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15904,7 +15915,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15926,7 +15937,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15948,7 +15959,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15970,7 +15981,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15992,7 +16003,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -16014,7 +16025,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16036,7 +16047,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16058,7 +16069,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16090,7 +16101,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16122,7 +16133,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16154,7 +16165,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16176,7 +16187,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16198,7 +16209,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16220,7 +16231,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16242,7 +16253,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16264,7 +16275,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16286,7 +16297,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16308,7 +16319,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16330,7 +16341,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16352,7 +16363,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16374,7 +16385,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16396,7 +16407,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16428,7 +16439,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16460,7 +16471,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16492,7 +16503,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16524,7 +16535,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16546,7 +16557,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16557,11 +16568,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16571,7 +16582,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>1273841.0823216592</v>
@@ -16598,7 +16609,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16620,7 +16631,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16641,7 +16652,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16672,7 +16683,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16703,7 +16714,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16734,7 +16745,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16765,7 +16776,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16782,7 +16793,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16802,7 +16813,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16825,193 +16836,193 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>28.703266366566705</v>
+        <v>28.654198747591781</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>29.148911122926034</v>
+        <v>29.099081683786672</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>29.601047357734831</v>
+        <v>29.550445001387686</v>
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>29.568330416119323</v>
+        <v>29.517783988683011</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>30.500686475340373</v>
+        <v>30.448546205193669</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>31.478793478659917</v>
+        <v>31.424981155543954</v>
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>30.663602807389093</v>
+        <v>30.611184035262728</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>32.256708000755133</v>
+        <v>32.201565849428057</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>33.982734995027734</v>
+        <v>33.924642237528744</v>
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>31.805442144153012</v>
+        <v>31.751071422140825</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>34.137534696220342</v>
+        <v>34.079177311948271</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>36.740435397864331</v>
+        <v>36.677628410601891</v>
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>32.892209658111163</v>
+        <v>32.835981130314501</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>35.978698526659521</v>
+        <v>35.917193712260556</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>39.520295775187002</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="13.15">
+        <v>39.452736676159446</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382012</v>
+        <v>27.783322809501026</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>27.830899135382012</v>
+        <v>27.783322809501026</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>33.873317446077756</v>
+        <v>33.815411735534759</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>37.690007482595917</v>
+        <v>37.625577222196277</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>42.184574721097341</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="13.15">
+        <v>42.112461094285685</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -17028,7 +17039,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17043,14 +17054,14 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>33.982734995027734</v>
+        <v>33.924642237528744</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17065,7 +17076,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>30.500686475340373</v>
+        <v>30.448546205193669</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17073,7 +17084,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17088,7 +17099,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>29.568330416119323</v>
+        <v>29.517783988683011</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17096,7 +17107,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17111,7 +17122,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17119,7 +17130,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17134,21 +17145,21 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17156,26 +17167,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17189,7 +17200,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17203,7 +17214,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17217,7 +17228,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17231,7 +17242,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17276,16 +17287,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17297,7 +17308,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17310,7 +17321,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17331,7 +17342,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17342,7 +17353,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17358,13 +17369,13 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>20.361062400000002</v>
+        <v>20.3262556</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17372,10 +17383,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17385,13 +17396,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17401,7 +17412,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17411,7 +17422,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17425,10 +17436,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17446,7 +17457,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17468,7 +17479,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17490,7 +17501,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17512,7 +17523,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17534,7 +17545,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17556,7 +17567,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17578,7 +17589,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17600,7 +17611,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17622,7 +17633,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17644,7 +17655,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17666,7 +17677,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17688,7 +17699,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17710,7 +17721,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17732,7 +17743,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17754,7 +17765,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17776,7 +17787,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17798,7 +17809,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17820,7 +17831,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17842,7 +17853,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17864,7 +17875,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17886,7 +17897,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17908,7 +17919,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17930,7 +17941,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17952,7 +17963,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17974,7 +17985,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17996,7 +18007,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -18018,7 +18029,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18040,7 +18051,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18062,7 +18073,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18084,7 +18095,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18106,7 +18117,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18128,7 +18139,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18139,11 +18150,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18153,7 +18164,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>942799.79083384247</v>
@@ -18180,7 +18191,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18202,7 +18213,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18223,7 +18234,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18244,7 +18255,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18265,7 +18276,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18286,7 +18297,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18307,14 +18318,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18324,7 +18335,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18347,193 +18358,193 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>20.361062400000002</v>
+        <v>20.3262556</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>20.361062400000002</v>
+        <v>20.3262556</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>20.361062400000002</v>
+        <v>20.3262556</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>20.361062400000002</v>
+        <v>20.3262556</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>20.361062400000002</v>
+        <v>20.3262556</v>
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>21.006721936739261</v>
+        <v>20.97081139559246</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>21.336554118251275</v>
+        <v>21.300079736055817</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>21.671190795872967</v>
+        <v>21.634144359445667</v>
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>21.646976216723413</v>
+        <v>21.609971174600446</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>22.33703489815186</v>
+        <v>22.298850215495367</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>23.060954930988366</v>
+        <v>23.021532722543487</v>
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>22.457613113056816</v>
+        <v>22.419222304524958</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>23.636707792861273</v>
+        <v>23.596301347232746</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>24.914181028539865</v>
+        <v>24.871590769780862</v>
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>23.30271530265243</v>
+        <v>23.262879810031162</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>25.028751933757921</v>
+        <v>24.985965818490772</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>26.955220055353291</v>
+        <v>26.909140684100898</v>
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>24.107057538951906</v>
+        <v>24.065847040508228</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>26.391440653975035</v>
+        <v>26.346325051532069</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>29.012660201270407</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="13.15">
+        <v>28.963063680162861</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>24.833198523190312</v>
+        <v>24.790746702289404</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>27.658020722792052</v>
+        <v>27.610739928854002</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>30.984555807235026</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="13.15">
+        <v>30.931588372830848</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18550,7 +18561,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18565,14 +18576,14 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>24.914181028539865</v>
+        <v>24.871590769780862</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18587,7 +18598,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>22.33703489815186</v>
+        <v>22.298850215495367</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18595,7 +18606,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18610,7 +18621,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>21.646976216723413</v>
+        <v>21.609971174600446</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18618,7 +18629,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18633,7 +18644,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18641,7 +18652,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18656,21 +18667,21 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>20.361062400000005</v>
+        <v>20.326255600000003</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18678,23 +18689,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18724,17 +18735,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18747,7 +18758,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18756,10 +18767,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-17.88</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-17.98</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18779,7 +18790,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18788,7 +18799,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18805,10 +18816,10 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>30.957265541154946</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+        <v>30.906738028885353</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18833,7 +18844,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18855,7 +18866,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18877,7 +18888,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18888,7 +18899,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18902,7 +18913,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18921,7 +18932,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18939,7 +18950,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18950,7 +18961,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18959,7 +18970,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18967,7 +18978,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18979,24 +18990,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>17.88</v>
+        <v>17.98</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19005,13 +19016,13 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.830899135382001</v>
+        <v>27.783322809501016</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19020,7 +19031,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -19029,7 +19040,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19041,7 +19052,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19052,13 +19063,13 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>29.568330416119323</v>
+        <v>29.517783988683011</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -19067,7 +19078,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19078,7 +19089,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19087,7 +19098,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19099,7 +19110,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19110,13 +19121,13 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19125,7 +19136,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19136,7 +19147,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19145,7 +19156,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19157,7 +19168,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19168,13 +19179,13 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>30.500686475340373</v>
+        <v>30.448546205193669</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19183,7 +19194,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19195,20 +19206,20 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>29.407315371816068</v>
+        <v>29.357044196148742</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19217,12 +19228,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19232,12 +19243,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19246,7 +19257,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19258,7 +19269,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19269,13 +19280,13 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>27.830899135382005</v>
+        <v>27.783322809501019</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19284,7 +19295,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19295,7 +19306,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19304,7 +19315,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19316,7 +19327,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19327,13 +19338,13 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>33.982734995027734</v>
+        <v>33.924642237528744</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19342,7 +19353,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19353,13 +19364,13 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>29.557265541154948</v>
+        <v>29.506738028885355</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19373,7 +19384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19382,7 +19393,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19390,7 +19401,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19403,7 +19414,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19415,13 +19426,13 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>29.5540907288893</v>
+        <v>29.503568643893267</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19431,7 +19442,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19439,7 +19450,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19449,7 +19460,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19461,7 +19472,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19471,7 +19482,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19484,10 +19495,10 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>1.0844821210139115E-2</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="13.9">
+        <v>1.0844821210139105E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19496,12 +19507,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19511,7 +19522,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19524,12 +19535,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19538,7 +19549,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19550,23 +19561,23 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>11.56052418494709</v>
+        <v>11.540761716501404</v>
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>13.880687232057891</v>
+        <v>13.860924763612207</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19577,48 +19588,48 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53037985828794953</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8">
+        <v>0.53024543919279798</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>17.88</v>
+        <v>17.98</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24965636355985632</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>0.24655165618865404</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19627,7 +19638,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19639,23 +19650,23 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>16.381903413667235</v>
+        <v>16.35389890071319</v>
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>19.252464567078146</v>
+        <v>19.224460054124101</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19666,17 +19677,17 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.34863850851590461</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" ht="13.15">
+        <v>0.34847220199994688</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19687,7 +19698,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19699,25 +19710,25 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>23.792433303154652</v>
+        <v>23.751760648102216</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>27.433169338975397</v>
+        <v>27.39249668392296</v>
       </c>
       <c r="D99" t="s">
         <v>396</v>
@@ -19727,18 +19738,18 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.1863758818352164E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8">
+        <v>7.1652832071531503E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19747,7 +19758,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19757,23 +19768,23 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>21.185477265721101</v>
+        <v>21.149261146168691</v>
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>24.56312164203521</v>
+        <v>24.526905522482799</v>
       </c>
       <c r="D105" t="s">
         <v>396</v>
@@ -19783,19 +19794,19 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.16887574490577673</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8">
+        <v>0.16868003940399767</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19803,7 +19814,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19811,7 +19822,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/0883.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0883.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72A336E-B998-474B-BA57-8159EC868457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53B4D58-557B-494F-961A-4F04B2786F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2513,7 +2502,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3905,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3943,7 +3932,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4232,7 +4221,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4241,7 +4230,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4272,7 +4261,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4281,7 +4270,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +4287,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4308,7 +4297,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4318,17 +4307,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4340,19 +4329,19 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>17.98</v>
+        <v>18.02</v>
       </c>
       <c r="D12" s="50">
         <v>25.72</v>
       </c>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4364,13 +4353,13 @@
       </c>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>854588.57263232011</v>
+        <v>856489.77079167997</v>
       </c>
       <c r="D14" s="35">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4378,7 +4367,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4392,39 +4381,39 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0889065499999999</v>
+        <v>1.0894403000000001</v>
       </c>
       <c r="D16" s="50">
         <v>1</v>
       </c>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4439,7 +4428,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4452,7 +4441,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4460,7 +4449,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4468,7 +4457,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4481,31 +4470,31 @@
       </c>
       <c r="E25" s="299">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v>0.91835245182426362</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.91790252297441166</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>29.506738028885355</v>
+        <v>29.52120136499342</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>399</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24655165618865404</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.24575458373695858</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4524,17 +4513,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>13.860924763612207</v>
+        <v>13.866581705951457</v>
       </c>
       <c r="D29" s="310">
         <f>D149</f>
-        <v>12.729214241214923</v>
+        <v>12.728170332923664</v>
       </c>
       <c r="E29" s="306" t="s">
         <v>424</v>
@@ -4543,17 +4532,17 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>19.224460054124101</v>
+        <v>19.232476254906675</v>
       </c>
       <c r="D30" s="311">
         <f>D157</f>
-        <v>17.654830025702484</v>
+        <v>17.653538477424302</v>
       </c>
       <c r="E30" s="307" t="s">
         <v>437</v>
@@ -4562,17 +4551,17 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>27.39249668392296</v>
+        <v>27.404139099193518</v>
       </c>
       <c r="D31" s="311">
         <f>D165</f>
-        <v>25.155966491268661</v>
+        <v>25.154328419091453</v>
       </c>
       <c r="E31" s="307" t="s">
         <v>436</v>
@@ -4581,17 +4570,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>24.526905522482799</v>
+        <v>24.53727226895592</v>
       </c>
       <c r="D32" s="311">
         <f>D173</f>
-        <v>22.524343822234151</v>
+        <v>22.522824122584705</v>
       </c>
       <c r="E32" s="307" t="s">
         <v>438</v>
@@ -4600,11 +4589,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4614,25 +4603,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4641,16 +4630,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4663,20 +4652,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4689,7 +4678,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4702,16 +4691,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4724,16 +4713,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4748,7 +4737,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4763,7 +4752,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4776,12 +4765,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4794,16 +4783,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4816,8 +4805,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4825,7 +4814,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4838,25 +4827,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4869,7 +4858,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4882,23 +4871,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11455781776035873</v>
+        <v>0.1143595556078882</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.7864293659621789E-2</v>
+        <v>7.7691453940066588E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4908,7 +4897,7 @@
         <v>0.74012355537751062</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
@@ -4919,7 +4908,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>452</v>
       </c>
@@ -4932,7 +4921,7 @@
         <v>0.25805863024505871</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4946,7 +4935,7 @@
         <v>0.4599183545926474</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4960,7 +4949,7 @@
         <v>0.39810050545262105</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4974,7 +4963,7 @@
         <v>1.4094345614568822</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4984,34 +4973,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5020,7 +5009,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5029,7 +5018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5038,34 +5027,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5073,20 +5062,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>27.463327511083342</v>
+        <v>27.476789227388608</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5096,38 +5085,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5140,20 +5129,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1051220919240095</v>
+        <v>2.1061539609274282</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5162,7 +5151,7 @@
         <v>0.12260820136742831</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5171,12 +5160,12 @@
         <v>0.75207444874659302</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5189,7 +5178,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5202,25 +5191,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.3079744835058325</v>
+        <v>2.3091057847920369</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5233,55 +5222,55 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.11714290683585106</v>
+        <v>0.11720032684725944</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>27.783322809501016</v>
+        <v>27.796941378100474</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-0.45639730584364507</v>
+        <v>-0.45662101839454683</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5291,16 +5280,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5317,7 +5306,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5332,14 +5321,14 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>33.92 HKD</v>
+        <v>33.94 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5354,14 +5343,14 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>30.45 HKD</v>
+        <v>30.46 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5376,14 +5365,14 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>29.52 HKD</v>
+        <v>29.53 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5398,14 +5387,14 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>27.78 HKD</v>
+        <v>27.8 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5420,36 +5409,36 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>27.78 HKD</v>
+        <v>27.8 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>29.506738028885355</v>
+        <v>29.52120136499342</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5459,30 +5448,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5491,7 +5480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5500,7 +5489,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5513,7 +5502,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5526,7 +5515,7 @@
         <v>600938.SS</v>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5535,7 +5524,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5545,30 +5534,30 @@
         <v>2.3201630471108023</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>11.540761716501404</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+        <v>11.546418658840656</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>13.860924763612207</v>
+        <v>13.866581705951457</v>
       </c>
       <c r="D149" s="300">
         <f>IF($D$11="","",C149*$E$25)</f>
-        <v>12.729214241214923</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+        <v>12.728170332923664</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5581,21 +5570,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53024543919279798</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.53028396322669269</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5604,7 +5593,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5614,30 +5603,30 @@
         <v>2.870561153410911</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>16.35389890071319</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+        <v>16.361915101495764</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>19.224460054124101</v>
+        <v>19.232476254906675</v>
       </c>
       <c r="D157" s="300">
         <f>IF($D$11="","",C157*$E$25)</f>
-        <v>17.654830025702484</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>17.653538477424302</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5650,21 +5639,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34847220199994688</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.34851986485506758</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5673,7 +5662,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5683,30 +5672,30 @@
         <v>3.6407360358207437</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>23.751760648102216</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+        <v>23.763403063372774</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>27.39249668392296</v>
+        <v>27.404139099193518</v>
       </c>
       <c r="D165" s="300">
         <f>IF($D$11="","",C165*$E$25)</f>
-        <v>25.155966491268661</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+        <v>25.154328419091453</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5719,21 +5708,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.1652832071531503E-2</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+        <v>7.1713282925888633E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5742,7 +5731,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5752,30 +5741,30 @@
         <v>3.3776443763141084</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>21.149261146168691</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+        <v>21.159627892641812</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>24.526905522482799</v>
+        <v>24.53727226895592</v>
       </c>
       <c r="D173" s="300">
         <f>IF($D$11="","",C173*$E$25)</f>
-        <v>22.524343822234151</v>
-      </c>
-    </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+        <v>22.522824122584705</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5788,16 +5777,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.16868003940399767</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.16873612790374115</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5807,21 +5796,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5830,91 +5819,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5931,6 +5909,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5961,15 +5950,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6018,7 +6007,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6034,7 +6023,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6042,7 +6031,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6078,7 +6067,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6114,7 +6103,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6150,7 +6139,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6186,7 +6175,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6222,7 +6211,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6252,7 +6241,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6268,7 +6257,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6284,7 +6273,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6320,7 +6309,7 @@
       </c>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6356,7 +6345,7 @@
       </c>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6392,7 +6381,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6428,7 +6417,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6464,13 +6453,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6500,7 +6489,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6516,7 +6505,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6532,7 +6521,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6568,7 +6557,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6604,7 +6593,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6640,7 +6629,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6666,7 +6655,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6674,7 +6663,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6711,7 +6700,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6748,7 +6737,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6785,7 +6774,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6822,7 +6811,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6859,7 +6848,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6875,12 +6864,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6929,7 +6918,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6978,7 +6967,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -7027,7 +7016,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7076,7 +7065,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7125,7 +7114,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7174,7 +7163,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7223,7 +7212,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7272,7 +7261,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7321,7 +7310,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7370,7 +7359,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7419,7 +7408,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7468,7 +7457,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7517,12 +7506,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7571,7 +7560,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7620,12 +7609,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7674,7 +7663,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7723,7 +7712,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7772,7 +7761,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7821,13 +7810,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7876,7 +7865,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7925,7 +7914,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7974,7 +7963,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -8023,7 +8012,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8072,12 +8061,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8127,7 +8116,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8176,7 +8165,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8226,7 +8215,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8275,7 +8264,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8325,7 +8314,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8341,13 +8330,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8396,7 +8385,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8430,7 +8419,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8464,7 +8453,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8513,7 +8502,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8594,7 +8583,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8605,7 +8594,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8621,7 +8610,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8632,7 +8621,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8652,7 +8641,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8674,7 +8663,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8696,7 +8685,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8717,7 +8706,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8738,7 +8727,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8759,7 +8748,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8780,7 +8769,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8792,7 +8781,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8805,7 +8794,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8829,12 +8818,12 @@
         <v>138776.4</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8854,7 +8843,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>455</v>
       </c>
@@ -8874,7 +8863,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8894,7 +8883,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8915,7 +8904,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8936,7 +8925,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8957,7 +8946,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8977,7 +8966,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8997,7 +8986,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -9009,7 +8998,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -9021,7 +9010,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9045,7 +9034,7 @@
         <v>9962.2999999999993</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9062,7 +9051,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9081,7 +9070,7 @@
         <v>-18033.400000000023</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9096,7 +9085,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9115,7 +9104,7 @@
         <v>-19921.400000000023</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9131,7 +9120,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9148,7 +9137,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9168,7 +9157,7 @@
         <v>288811.59999999998</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9179,7 +9168,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9192,7 +9181,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9211,7 +9200,7 @@
         <v>140072.9</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9227,7 +9216,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9243,7 +9232,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9259,7 +9248,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9278,7 +9267,7 @@
         <v>64516.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9298,7 +9287,7 @@
         <v>148738.69999999998</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9318,7 +9307,7 @@
         <v>143625.49999999997</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9337,7 +9326,7 @@
         <v>5113.2</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9348,7 +9337,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9362,7 +9351,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9376,25 +9365,25 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>17.12625082518321</v>
+        <v>17.134645610188354</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.45639730584364507</v>
+        <v>-0.45662101839454683</v>
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9407,7 +9396,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9421,7 +9410,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9432,10 +9421,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9447,7 +9436,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9461,7 +9450,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9475,10 +9464,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9490,7 +9479,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9501,7 +9490,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9512,10 +9501,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9527,7 +9516,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9543,7 +9532,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9554,7 +9543,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9568,7 +9557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9584,7 +9573,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9594,7 +9583,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9604,7 +9593,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9614,7 +9603,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9624,10 +9613,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9639,7 +9628,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9655,7 +9644,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9671,7 +9660,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9684,7 +9673,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9697,10 +9686,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9712,7 +9701,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9726,7 +9715,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9740,7 +9729,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9754,7 +9743,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9768,7 +9757,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9779,7 +9768,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9787,68 +9776,68 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-100056.35615984999</v>
+        <v>-100105.40084610002</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-2.1051220919240095</v>
+        <v>-2.1061539609274287</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>109697.92099727839</v>
+        <v>109751.69169535373</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.3079744835058325</v>
+        <v>2.3091057847920369</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>5567.7969714599994</v>
+        <v>5570.5261419600001</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.11714290683585105</v>
+        <v>0.11720032684725942</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>15209.361808888392</v>
+        <v>15216.816991213709</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>0.31999529841767405</v>
+        <v>0.32015215071186764</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -9869,19 +9858,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9938,7 +9927,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9961,7 +9950,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9975,7 +9964,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -10032,7 +10021,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10087,7 +10076,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10142,7 +10131,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10197,7 +10186,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10254,7 +10243,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10309,7 +10298,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10364,7 +10353,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10421,7 +10410,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10476,7 +10465,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10531,7 +10520,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10586,7 +10575,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10643,7 +10632,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10700,7 +10689,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10726,7 +10715,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10751,7 +10740,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10808,7 +10797,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10827,7 +10816,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10850,7 +10839,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10871,7 +10860,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10928,7 +10917,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10985,7 +10974,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11042,18 +11031,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11112,7 +11101,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11172,7 +11161,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11227,18 +11216,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11295,7 +11284,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11354,7 +11343,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11411,18 +11400,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11480,7 +11469,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11538,7 +11527,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11593,18 +11582,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11662,10 +11651,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11688,14 +11677,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11750,7 +11739,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11805,7 +11794,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11862,7 +11851,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11917,11 +11906,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11931,7 +11920,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11957,7 +11946,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11984,7 +11973,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -12039,11 +12028,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12053,7 +12042,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12108,7 +12097,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12163,7 +12152,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12218,7 +12207,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12273,7 +12262,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12329,7 +12318,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12384,11 +12373,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12398,7 +12387,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12423,7 +12412,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12447,7 +12436,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12472,7 +12461,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12499,10 +12488,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12525,7 +12514,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12546,7 +12535,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12603,7 +12592,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12660,7 +12649,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12717,7 +12706,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12774,7 +12763,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12831,7 +12820,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12890,7 +12879,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12947,7 +12936,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -13004,7 +12993,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13061,7 +13050,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13118,7 +13107,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13176,7 +13165,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13233,7 +13222,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13259,7 +13248,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13283,7 +13272,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13340,18 +13329,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13407,7 +13396,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13463,7 +13452,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13518,27 +13507,27 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.7864293659621789E-2</v>
+        <v>7.7691453940066588E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.7864293659621789E-2</v>
+        <v>7.7691453940066588E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.9521690767519462E-2</v>
+        <v>6.9367369589345168E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>8.0645161290322578E-2</v>
+        <v>8.0466148723640399E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13573,11 +13562,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13598,7 +13587,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13655,7 +13644,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13712,10 +13701,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13738,7 +13727,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13748,7 +13737,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13805,7 +13794,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13862,7 +13851,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13919,7 +13908,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13976,7 +13965,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -14033,11 +14022,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14060,7 +14049,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14117,7 +14106,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14174,7 +14163,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14201,18 +14190,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14264,7 +14253,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14316,11 +14305,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14374,7 +14363,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14429,7 +14418,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14483,7 +14472,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14539,7 +14528,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14596,7 +14585,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14615,7 +14604,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14638,7 +14627,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14659,7 +14648,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14667,845 +14656,845 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.0597495633312501</v>
+        <v>2.060759192054145</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.2385076110308262</v>
+        <v>3.2400950323181612</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>2.8272819111824892</v>
+        <v>2.828667761713092</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>3.2237224695830511</v>
+        <v>3.2253026436284187</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>1.7419286853177269</v>
+        <v>1.7427825275834281</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>0.64058495201147347</v>
+        <v>0.64089894793530766</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>1.374278761334996</v>
+        <v>1.3749523924090885</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>1.164685467278386</v>
+        <v>1.1652563618773395</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
-        <v>6.8582622046011696</v>
+        <v>6.8616239232460865</v>
       </c>
       <c r="O124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4509699809979937</v>
+        <v>6.454132056960673</v>
       </c>
       <c r="P124" s="177">
         <f t="shared" si="49"/>
-        <v>6.4974083507383256</v>
+        <v>6.5005931894255466</v>
       </c>
       <c r="Q124" s="177" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11455781776035873</v>
+        <v>0.1143595556078882</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.18011721974587463</v>
+        <v>0.17980549568913215</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.15724593499346434</v>
+        <v>0.15697379365777425</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.17929490932052564</v>
+        <v>0.17898460841445166</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.6881461919784584E-2</v>
+        <v>9.671379176378625E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.5627639155254361E-2</v>
+        <v>3.5565979352680778E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>7.643374645912103E-2</v>
+        <v>7.6301464617596473E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.4776722318041491E-2</v>
+        <v>6.4664614976544924E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.38143838735267904</v>
+        <v>0.38077824213352313</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.35878587213559476</v>
+        <v>0.35816493101890529</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.3613686513202628</v>
+        <v>0.36074324025668963</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16146015102329908</v>
+        <v>0.16110174891225959</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1452043755017407</v>
+        <v>0.1448820572431353</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16578386903022094</v>
+        <v>0.16541586932094188</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2269997811273129E-2</v>
+        <v>8.208737850425589E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9201967121010145E-2</v>
+        <v>2.913714588433754E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1432571128311029E-2</v>
+        <v>7.1274008262321456E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1638270141792725E-2</v>
+        <v>6.150144823248798E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2254785812872599E-2</v>
+        <v>8.2072200272777437E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9237995796905441E-2</v>
+        <v>6.9084304352295234E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0721483282282633E-2</v>
+        <v>5.060889397421986E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15527,16 +15516,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15548,7 +15537,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15561,7 +15550,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15582,7 +15571,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15593,7 +15582,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15611,7 +15600,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15627,7 +15616,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15643,7 +15632,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15659,7 +15648,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15673,13 +15662,13 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0889065499999999</v>
+        <v>1.0894403000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15687,13 +15676,13 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>27.783322809501016</v>
+        <v>27.796941378100474</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15701,10 +15690,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15714,13 +15703,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15730,7 +15719,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15740,13 +15729,13 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>29.503568643893267</v>
+        <v>29.518030426461923</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15754,10 +15743,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15775,7 +15764,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15797,7 +15786,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15819,7 +15808,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15851,7 +15840,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15883,7 +15872,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15915,7 +15904,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15937,7 +15926,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15959,7 +15948,7 @@
       </c>
       <c r="H27" s="120"/>
   